--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5244,13 +5244,13 @@
         <v>63.1</v>
       </c>
       <c r="E57" t="n">
-        <v>65.19</v>
+        <v>64.55</v>
       </c>
       <c r="F57" t="n">
-        <v>-0.86</v>
+        <v>-1.49</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.013</v>
+        <v>-0.0226</v>
       </c>
       <c r="H57" t="n">
         <v>5.01</v>
@@ -5284,62 +5284,144 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>64.79000000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>64.98</v>
+      </c>
+      <c r="D58" t="n">
+        <v>62.8</v>
+      </c>
+      <c r="E58" t="n">
+        <v>63.76</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0124</v>
+      </c>
+      <c r="H58" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="I58" t="n">
+        <v>58.09</v>
+      </c>
+      <c r="J58" t="n">
+        <v>59.02</v>
+      </c>
+      <c r="K58" t="n">
+        <v>62.05</v>
+      </c>
+      <c r="L58" t="n">
+        <v>65.08</v>
+      </c>
+      <c r="M58" t="n">
+        <v>67.06</v>
+      </c>
+      <c r="N58" t="n">
+        <v>69.03</v>
+      </c>
+      <c r="O58" t="n">
+        <v>73.11</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
       </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="12" t="inlineStr">
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I58" s="13" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="J58" s="13" t="n">
-        <v>59.98</v>
-      </c>
-      <c r="K58" s="13" t="n">
-        <v>62.69</v>
-      </c>
-      <c r="L58" s="13" t="n">
-        <v>65.40000000000001</v>
-      </c>
-      <c r="M58" s="13" t="n">
-        <v>67.69</v>
-      </c>
-      <c r="N58" s="13" t="n">
-        <v>69.98999999999999</v>
-      </c>
-      <c r="O58" s="13" t="n">
-        <v>73.11</v>
+      <c r="I59" s="13" t="n">
+        <v>60.62</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>61.51</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>62.66</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>63.82</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>64.84999999999999</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>65.87</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>67.16</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5321,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>64.79000000000001</v>
+        <v>63.76</v>
       </c>
       <c r="C58" t="n">
-        <v>64.98</v>
+        <v>64.08</v>
       </c>
       <c r="D58" t="n">
-        <v>62.8</v>
+        <v>63.39</v>
       </c>
       <c r="E58" t="n">
-        <v>63.76</v>
+        <v/>
       </c>
       <c r="F58" t="n">
-        <v>-0.8</v>
+        <v/>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0124</v>
+        <v/>
       </c>
       <c r="H58" t="n">
-        <v>2.18</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5362,8 +5365,10 @@
       <c r="O58" t="n">
         <v>73.11</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5371,9 +5376,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5392,36 +5397,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="12" t="inlineStr">
+      <c r="A59" s="13" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="13" t="n">
-        <v>60.62</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>61.51</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>62.66</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>63.82</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>65.87</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>67.16</v>
+      <c r="I59" s="14" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="J59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="K59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="L59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="M59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="N59" s="14" t="n">
+        <v/>
+      </c>
+      <c r="O59" s="14" t="n">
+        <v>64.77</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -91,7 +91,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -5324,25 +5321,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>63.76</v>
+        <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>64.08</v>
+        <v>63.7</v>
       </c>
       <c r="D58" t="n">
-        <v>63.39</v>
+        <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>63.51</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>-1.04</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>-0.0161</v>
       </c>
       <c r="H58" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.68</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5365,20 +5362,20 @@
       <c r="O58" t="n">
         <v>73.11</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5397,36 +5394,36 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="13" t="inlineStr">
+      <c r="A59" s="12" t="inlineStr">
         <is>
           <t>下週預測</t>
         </is>
       </c>
-      <c r="I59" s="14" t="n">
-        <v>62.7</v>
-      </c>
-      <c r="J59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="K59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="14" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="14" t="n">
-        <v>64.77</v>
+      <c r="I59" s="13" t="n">
+        <v>62.34</v>
+      </c>
+      <c r="J59" s="13" t="n">
+        <v>62.91</v>
+      </c>
+      <c r="K59" s="13" t="n">
+        <v>63.17</v>
+      </c>
+      <c r="L59" s="13" t="n">
+        <v>63.44</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>63.85</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>64.27</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>64.38</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5324,22 +5324,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>63.7</v>
+        <v>64.08</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>63.51</v>
+        <v>63.81</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.04</v>
+        <v>-0.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0161</v>
+        <v>-0.0116</v>
       </c>
       <c r="H58" t="n">
-        <v>0.68</v>
+        <v>1.06</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5368,14 +5368,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5405,25 +5403,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>62.34</v>
+        <v>61.96</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.91</v>
+        <v>62.87</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63.17</v>
+        <v>63.27</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.44</v>
+        <v>63.68</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>63.85</v>
+        <v>64.34</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64.27</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>64.38</v>
+        <v>65.14</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5324,22 +5324,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>64.08</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>63.81</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.75</v>
+        <v>-0.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0116</v>
+        <v>-0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>1.06</v>
+        <v>1.44</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5403,25 +5403,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61.96</v>
+        <v>61.58</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.87</v>
+        <v>62.96</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63.27</v>
+        <v>63.46</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.68</v>
+        <v>63.96</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64.34</v>
+        <v>64.91</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64.98999999999999</v>
+        <v>65.84999999999999</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>65.14</v>
+        <v>65.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -666,28 +666,30 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>36.6</v>
+        <v>37.26</v>
       </c>
       <c r="J2" t="n">
-        <v>36.88</v>
+        <v>37.12</v>
       </c>
       <c r="K2" t="n">
-        <v>37.42</v>
+        <v>37.58</v>
       </c>
       <c r="L2" t="n">
-        <v>37.96</v>
+        <v>38.04</v>
       </c>
       <c r="M2" t="n">
+        <v>38.21</v>
+      </c>
+      <c r="N2" t="n">
         <v>38.37</v>
       </c>
-      <c r="N2" t="n">
-        <v>38.78</v>
-      </c>
       <c r="O2" t="n">
-        <v>39.46</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
+        <v>39.13</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="Q2" s="6" t="n">
         <v/>
@@ -709,11 +711,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5324,22 +5328,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>64.45999999999999</v>
+        <v>64.48</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>64.18000000000001</v>
+        <v>64.19</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.37</v>
+        <v>-0.36</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0057</v>
+        <v>-0.0056</v>
       </c>
       <c r="H58" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5403,25 +5407,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61.58</v>
+        <v>61.56</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.96</v>
+        <v>62.95</v>
       </c>
       <c r="K59" s="13" t="n">
         <v>63.46</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.96</v>
+        <v>63.97</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64.91</v>
+        <v>64.92</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>65.84999999999999</v>
+        <v>65.87</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>65.91</v>
+        <v>65.94</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>64.48</v>
+        <v>65.39</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>64.19</v>
+        <v>65.20999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.36</v>
+        <v>0.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0056</v>
+        <v>0.0102</v>
       </c>
       <c r="H58" t="n">
-        <v>1.46</v>
+        <v>2.37</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5375,9 +5375,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5407,25 +5407,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>61.56</v>
+        <v>60.65</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.95</v>
+        <v>63.34</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63.46</v>
+        <v>64.03</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.97</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64.92</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>65.87</v>
+        <v>68.09</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>65.94</v>
+        <v>67.77</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>65.39</v>
+        <v>65.42</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.20999999999999</v>
+        <v>65.36</v>
       </c>
       <c r="F58" t="n">
-        <v>0.66</v>
+        <v>0.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0102</v>
+        <v>0.0124</v>
       </c>
       <c r="H58" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5407,25 +5407,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>60.65</v>
+        <v>60.62</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>63.34</v>
+        <v>63.53</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>64.03</v>
+        <v>64.16</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>64.70999999999999</v>
+        <v>64.79000000000001</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>66.40000000000001</v>
+        <v>66.55</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>68.09</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>67.77</v>
+        <v>67.81</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>65.42</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.36</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="F58" t="n">
         <v>0.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0124</v>
+        <v>0.0123</v>
       </c>
       <c r="H58" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5407,25 +5407,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>60.62</v>
+        <v>60.58</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>63.53</v>
+        <v>63.46</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>64.16</v>
+        <v>64.13</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>64.79000000000001</v>
+        <v>64.8</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>66.55</v>
+        <v>66.56999999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>68.31999999999999</v>
+        <v>68.34999999999999</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>67.81</v>
+        <v>67.91</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5334,13 +5334,13 @@
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.34999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.71</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0123</v>
+        <v>0.0109</v>
       </c>
       <c r="H58" t="n">
         <v>2.44</v>
@@ -5410,19 +5410,19 @@
         <v>60.58</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>63.46</v>
+        <v>63.32</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>64.13</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>64.8</v>
+        <v>64.75</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>66.56999999999999</v>
+        <v>66.48</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>68.34999999999999</v>
+        <v>68.20999999999999</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>67.91</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5328,22 +5328,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>65.45999999999999</v>
+        <v>63.7</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.26000000000001</v>
+        <v>63.37</v>
       </c>
       <c r="F58" t="n">
-        <v>0.71</v>
+        <v>-1.19</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0109</v>
+        <v>-0.0184</v>
       </c>
       <c r="H58" t="n">
-        <v>2.44</v>
+        <v>0.68</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5372,12 +5372,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5396,7 +5398,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5407,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>60.58</v>
+        <v>62.34</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>63.32</v>
+        <v>62.69</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>64.04000000000001</v>
+        <v>63.03</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>64.75</v>
+        <v>63.36</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>66.48</v>
+        <v>63.71</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>68.20999999999999</v>
+        <v>64.05</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>67.91</v>
+        <v>64.38</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -666,33 +666,35 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>37.26</v>
+        <v>37.78</v>
       </c>
       <c r="J2" t="n">
-        <v>37.12</v>
+        <v>37.77</v>
       </c>
       <c r="K2" t="n">
-        <v>37.58</v>
+        <v>37.84</v>
       </c>
       <c r="L2" t="n">
-        <v>38.04</v>
+        <v>37.91</v>
       </c>
       <c r="M2" t="n">
-        <v>38.21</v>
+        <v>37.94</v>
       </c>
       <c r="N2" t="n">
-        <v>38.37</v>
+        <v>37.98</v>
       </c>
       <c r="O2" t="n">
-        <v>39.13</v>
+        <v>38.08</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -5328,22 +5330,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>63.7</v>
+        <v>63.94</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>63.37</v>
+        <v>63.66</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.19</v>
+        <v>-0.89</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0184</v>
+        <v>-0.0138</v>
       </c>
       <c r="H58" t="n">
-        <v>0.68</v>
+        <v>0.92</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5372,14 +5374,12 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R58" s="6" t="n">
+        <v/>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5409,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>62.34</v>
+        <v>62.1</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.69</v>
+        <v>62.82</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63.03</v>
+        <v>63.2</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.36</v>
+        <v>63.57</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>63.71</v>
+        <v>64.12</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64.05</v>
+        <v>64.67</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>64.38</v>
+        <v>64.87</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5330,22 +5330,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>63.94</v>
+        <v>65.93000000000001</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>63.66</v>
+        <v>65.79000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.89</v>
+        <v>1.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0191</v>
       </c>
       <c r="H58" t="n">
-        <v>0.92</v>
+        <v>2.91</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5377,9 +5377,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5398,7 +5398,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5409,25 +5409,25 @@
         </is>
       </c>
       <c r="I59" s="13" t="n">
-        <v>62.1</v>
+        <v>60.11</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>62.82</v>
+        <v>63.54</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>63.2</v>
+        <v>64.34</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>63.57</v>
+        <v>65.13</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>64.12</v>
+        <v>67.25</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>64.67</v>
+        <v>69.36</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>64.87</v>
+        <v>68.84</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5336,13 +5336,13 @@
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.79000000000001</v>
+        <v>65.86</v>
       </c>
       <c r="F58" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0191</v>
+        <v>0.0203</v>
       </c>
       <c r="H58" t="n">
         <v>2.91</v>
@@ -5412,19 +5412,19 @@
         <v>60.11</v>
       </c>
       <c r="J59" s="13" t="n">
-        <v>63.54</v>
+        <v>63.65</v>
       </c>
       <c r="K59" s="13" t="n">
-        <v>64.34</v>
+        <v>64.41</v>
       </c>
       <c r="L59" s="13" t="n">
-        <v>65.13</v>
+        <v>65.17</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>67.25</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="N59" s="13" t="n">
-        <v>69.36</v>
+        <v>69.47</v>
       </c>
       <c r="O59" s="13" t="n">
         <v>68.84</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X59"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -666,25 +659,25 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>37.78</v>
+        <v>37.87</v>
       </c>
       <c r="J2" t="n">
-        <v>37.77</v>
+        <v>37.88</v>
       </c>
       <c r="K2" t="n">
-        <v>37.84</v>
+        <v>37.89</v>
       </c>
       <c r="L2" t="n">
+        <v>37.89</v>
+      </c>
+      <c r="M2" t="n">
+        <v>37.9</v>
+      </c>
+      <c r="N2" t="n">
         <v>37.91</v>
       </c>
-      <c r="M2" t="n">
-        <v>37.94</v>
-      </c>
-      <c r="N2" t="n">
-        <v>37.98</v>
-      </c>
       <c r="O2" t="n">
-        <v>38.08</v>
+        <v>37.91</v>
       </c>
       <c r="P2" s="6" t="inlineStr">
         <is>
@@ -713,12 +706,12 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5330,22 +5323,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>65.93000000000001</v>
+        <v>66.20999999999999</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>65.86</v>
+        <v>66.04000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>1.31</v>
+        <v>1.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0203</v>
+        <v>0.0231</v>
       </c>
       <c r="H58" t="n">
-        <v>2.91</v>
+        <v>3.19</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5400,34 +5393,6 @@
         <is>
           <t>中警訊</t>
         </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="12" t="inlineStr">
-        <is>
-          <t>下週預測</t>
-        </is>
-      </c>
-      <c r="I59" s="13" t="n">
-        <v>60.11</v>
-      </c>
-      <c r="J59" s="13" t="n">
-        <v>63.65</v>
-      </c>
-      <c r="K59" s="13" t="n">
-        <v>64.41</v>
-      </c>
-      <c r="L59" s="13" t="n">
-        <v>65.17</v>
-      </c>
-      <c r="M59" s="13" t="n">
-        <v>67.31999999999999</v>
-      </c>
-      <c r="N59" s="13" t="n">
-        <v>69.47</v>
-      </c>
-      <c r="O59" s="13" t="n">
-        <v>68.84</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5323,22 +5323,22 @@
         <v>63.51</v>
       </c>
       <c r="C58" t="n">
-        <v>66.20999999999999</v>
+        <v>66.22</v>
       </c>
       <c r="D58" t="n">
         <v>63.02</v>
       </c>
       <c r="E58" t="n">
-        <v>66.04000000000001</v>
+        <v>66.2</v>
       </c>
       <c r="F58" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0231</v>
+        <v>0.0255</v>
       </c>
       <c r="H58" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="I58" t="n">
         <v>58.09</v>
@@ -5372,11 +5372,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,65 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-18</t>
+          <t>2025-08-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>37.95</v>
+        <v>38.76</v>
       </c>
       <c r="C2" t="n">
-        <v>39</v>
+        <v>40.31</v>
       </c>
       <c r="D2" t="n">
-        <v>37.21</v>
+        <v>38.51</v>
       </c>
       <c r="E2" t="n">
-        <v>39</v>
+        <v>40.2</v>
       </c>
       <c r="F2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0293</v>
+        <v>0.0307</v>
       </c>
       <c r="H2" t="n">
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>37.87</v>
+        <v>35.41</v>
       </c>
       <c r="J2" t="n">
-        <v>37.88</v>
+        <v>37.65</v>
       </c>
       <c r="K2" t="n">
-        <v>37.89</v>
+        <v>38.1</v>
       </c>
       <c r="L2" t="n">
-        <v>37.89</v>
+        <v>38.55</v>
       </c>
       <c r="M2" t="n">
-        <v>37.9</v>
+        <v>39.9</v>
       </c>
       <c r="N2" t="n">
-        <v>37.91</v>
+        <v>41.25</v>
       </c>
       <c r="O2" t="n">
-        <v>37.91</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>40.8</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -701,77 +695,69 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38.76</v>
+        <v>40.19</v>
       </c>
       <c r="C3" t="n">
-        <v>40.31</v>
+        <v>41.72</v>
       </c>
       <c r="D3" t="n">
-        <v>38.51</v>
+        <v>40.19</v>
       </c>
       <c r="E3" t="n">
-        <v>40.2</v>
+        <v>41.07</v>
       </c>
       <c r="F3" t="n">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0217</v>
       </c>
       <c r="H3" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="I3" t="n">
-        <v>35.41</v>
+        <v>36.71</v>
       </c>
       <c r="J3" t="n">
-        <v>37.65</v>
+        <v>38.8</v>
       </c>
       <c r="K3" t="n">
-        <v>38.1</v>
+        <v>39.3</v>
       </c>
       <c r="L3" t="n">
-        <v>38.55</v>
+        <v>39.8</v>
       </c>
       <c r="M3" t="n">
-        <v>39.9</v>
+        <v>41.1</v>
       </c>
       <c r="N3" t="n">
-        <v>41.25</v>
+        <v>42.39</v>
       </c>
       <c r="O3" t="n">
-        <v>40.8</v>
+        <v>42.1</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -808,50 +794,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.19</v>
+        <v>41.15</v>
       </c>
       <c r="C4" t="n">
-        <v>41.72</v>
+        <v>42.39</v>
       </c>
       <c r="D4" t="n">
-        <v>40.19</v>
+        <v>40.88</v>
       </c>
       <c r="E4" t="n">
-        <v>41.07</v>
+        <v>42.39</v>
       </c>
       <c r="F4" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0217</v>
+        <v>0.032</v>
       </c>
       <c r="H4" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I4" t="n">
-        <v>36.71</v>
+        <v>38.66</v>
       </c>
       <c r="J4" t="n">
-        <v>38.8</v>
+        <v>39.61</v>
       </c>
       <c r="K4" t="n">
-        <v>39.3</v>
+        <v>40.31</v>
       </c>
       <c r="L4" t="n">
-        <v>39.8</v>
+        <v>41.01</v>
       </c>
       <c r="M4" t="n">
-        <v>41.1</v>
+        <v>41.84</v>
       </c>
       <c r="N4" t="n">
-        <v>42.39</v>
+        <v>42.67</v>
       </c>
       <c r="O4" t="n">
-        <v>42.1</v>
+        <v>43.24</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -869,11 +855,13 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -888,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>41.15</v>
+        <v>42.21</v>
       </c>
       <c r="C5" t="n">
-        <v>42.39</v>
+        <v>42.87</v>
       </c>
       <c r="D5" t="n">
-        <v>40.88</v>
+        <v>41.49</v>
       </c>
       <c r="E5" t="n">
-        <v>42.39</v>
+        <v>42.54</v>
       </c>
       <c r="F5" t="n">
-        <v>1.31</v>
+        <v>0.15</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0035</v>
       </c>
       <c r="H5" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I5" t="n">
-        <v>38.66</v>
+        <v>39.37</v>
       </c>
       <c r="J5" t="n">
-        <v>39.61</v>
+        <v>41.26</v>
       </c>
       <c r="K5" t="n">
-        <v>40.31</v>
+        <v>41.63</v>
       </c>
       <c r="L5" t="n">
-        <v>41.01</v>
+        <v>42.01</v>
       </c>
       <c r="M5" t="n">
-        <v>41.84</v>
+        <v>43.14</v>
       </c>
       <c r="N5" t="n">
-        <v>42.67</v>
+        <v>44.27</v>
       </c>
       <c r="O5" t="n">
-        <v>43.24</v>
+        <v>43.9</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,23 +927,21 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -970,50 +956,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42.21</v>
+        <v>43.67</v>
       </c>
       <c r="C6" t="n">
-        <v>42.87</v>
+        <v>46.22</v>
       </c>
       <c r="D6" t="n">
-        <v>41.49</v>
+        <v>43.3</v>
       </c>
       <c r="E6" t="n">
-        <v>42.54</v>
+        <v>46.22</v>
       </c>
       <c r="F6" t="n">
-        <v>0.15</v>
+        <v>3.69</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0866</v>
       </c>
       <c r="H6" t="n">
-        <v>1.37</v>
+        <v>2.92</v>
       </c>
       <c r="I6" t="n">
-        <v>39.37</v>
+        <v>40.12</v>
       </c>
       <c r="J6" t="n">
-        <v>41.26</v>
+        <v>41.34</v>
       </c>
       <c r="K6" t="n">
-        <v>41.63</v>
+        <v>41.85</v>
       </c>
       <c r="L6" t="n">
-        <v>42.01</v>
+        <v>42.36</v>
       </c>
       <c r="M6" t="n">
-        <v>43.14</v>
+        <v>43.22</v>
       </c>
       <c r="N6" t="n">
-        <v>44.27</v>
+        <v>44.08</v>
       </c>
       <c r="O6" t="n">
-        <v>43.9</v>
+        <v>44.24</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,24 +1007,28 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1050,50 +1040,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C7" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D7" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E7" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F7" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H7" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I7" t="n">
-        <v>40.12</v>
+        <v>40.38</v>
       </c>
       <c r="J7" t="n">
-        <v>41.34</v>
+        <v>44.03</v>
       </c>
       <c r="K7" t="n">
-        <v>41.85</v>
+        <v>44.76</v>
       </c>
       <c r="L7" t="n">
-        <v>42.36</v>
+        <v>45.49</v>
       </c>
       <c r="M7" t="n">
-        <v>43.22</v>
+        <v>47.68</v>
       </c>
       <c r="N7" t="n">
-        <v>44.08</v>
+        <v>49.87</v>
       </c>
       <c r="O7" t="n">
-        <v>44.24</v>
+        <v>49.14</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,18 +1101,14 @@
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
@@ -1134,50 +1120,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C8" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D8" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E8" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F8" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H8" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I8" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J8" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K8" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L8" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M8" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N8" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O8" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,14 +1174,14 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U8" s="8" t="n">
@@ -1209,55 +1195,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C9" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D9" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E9" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H9" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I9" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J9" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K9" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L9" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M9" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N9" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O9" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1268,9 +1258,9 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
@@ -1278,70 +1268,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C10" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D10" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E10" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F10" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H10" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I10" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J10" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K10" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L10" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M10" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N10" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O10" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1349,83 +1339,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C11" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D11" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E11" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H11" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I11" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J11" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K11" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L11" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M11" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N11" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O11" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1435,12 +1425,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1466,50 +1456,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C12" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D12" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E12" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H12" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I12" t="n">
         <v>43.01</v>
       </c>
       <c r="J12" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K12" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L12" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M12" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N12" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O12" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,14 +1507,12 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1543,57 +1531,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C13" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D13" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E13" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F13" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H13" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J13" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K13" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L13" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M13" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N13" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O13" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,76 +1594,78 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C14" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D14" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E14" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F14" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I14" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J14" t="n">
         <v>45.26</v>
       </c>
-      <c r="J14" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K14" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L14" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M14" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N14" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O14" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1683,83 +1673,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C15" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D15" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E15" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H15" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I15" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J15" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K15" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L15" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M15" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N15" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O15" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1767,83 +1757,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C16" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D16" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E16" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F16" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H16" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I16" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J16" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K16" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L16" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M16" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N16" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O16" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,18 +1851,14 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1884,50 +1870,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C17" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D17" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E17" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F17" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H17" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I17" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J17" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K17" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L17" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M17" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N17" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O17" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,14 +1931,18 @@
       </c>
       <c r="T17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1964,50 +1954,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C18" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E18" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I18" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J18" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K18" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L18" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M18" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N18" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O18" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2033,10 +2023,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2048,50 +2036,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C19" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D19" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E19" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H19" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I19" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J19" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K19" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M19" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O19" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,8 +2105,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="n">
-        <v/>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2130,50 +2120,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C20" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D20" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E20" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F20" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H20" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I20" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J20" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M20" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O20" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,83 +2171,83 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D21" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E21" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F21" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H21" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I21" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J21" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K21" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L21" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M21" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N21" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2265,22 +2255,24 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
@@ -2289,59 +2281,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C22" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D22" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E22" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F22" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H22" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I22" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J22" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L22" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M22" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N22" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O22" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2364,11 +2352,13 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2380,50 +2370,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D23" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E23" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F23" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H23" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I23" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J23" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K23" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L23" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M23" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N23" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O23" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2446,13 +2436,11 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2464,63 +2452,69 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C24" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D24" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E24" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H24" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I24" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J24" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K24" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M24" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N24" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O24" t="n">
-        <v>104</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2530,160 +2524,150 @@
       </c>
       <c r="U24" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C25" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D25" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H25" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I25" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J25" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K25" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L25" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M25" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N25" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O25" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C26" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D26" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E26" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H26" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J26" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K26" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M26" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N26" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O26" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2713,55 +2697,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D27" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E27" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F27" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H27" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I27" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J27" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K27" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L27" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M27" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N27" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O27" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2769,16 +2757,20 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2793,57 +2785,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C28" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D28" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E28" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H28" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I28" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J28" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K28" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L28" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M28" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N28" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O28" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2851,24 +2843,24 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2879,81 +2871,81 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C29" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D29" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E29" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I29" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J29" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K29" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L29" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M29" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N29" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O29" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2965,74 +2957,70 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C30" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D30" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E30" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F30" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H30" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I30" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J30" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K30" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L30" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M30" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N30" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O30" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3058,63 +3046,69 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C31" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D31" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E31" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F31" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H31" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I31" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J31" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K31" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L31" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M31" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N31" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O31" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3131,78 +3125,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D32" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E32" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F32" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H32" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I32" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J32" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K32" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L32" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M32" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N32" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O32" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
+        <v>97.48</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3219,55 +3205,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D33" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H33" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I33" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J33" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K33" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L33" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M33" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N33" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O33" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,18 +3265,18 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3301,57 +3291,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D34" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E34" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H34" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I34" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J34" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K34" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M34" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O34" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3392,50 +3382,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C35" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D35" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F35" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H35" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I35" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J35" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K35" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M35" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N35" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3476,50 +3466,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C36" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D36" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E36" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F36" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H36" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I36" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J36" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K36" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L36" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M36" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N36" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3527,19 +3517,19 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
@@ -3553,72 +3543,76 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D37" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E37" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F37" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H37" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I37" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J37" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K37" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L37" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M37" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N37" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3635,82 +3629,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C38" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D38" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E38" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H38" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I38" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J38" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L38" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M38" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N38" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O38" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
+        <v>82.87</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3723,55 +3711,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C39" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D39" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E39" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F39" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H39" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I39" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J39" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K39" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L39" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M39" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N39" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O39" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3781,19 +3773,19 @@
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3807,57 +3799,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F40" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H40" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I40" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J40" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K40" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L40" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M40" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O40" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3865,20 +3857,16 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3891,59 +3879,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C41" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D41" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E41" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H41" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I41" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J41" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K41" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L41" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N41" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O41" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3951,8 +3935,10 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
@@ -3978,56 +3964,58 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C42" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D42" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E42" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F42" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H42" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I42" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J42" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K42" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N42" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O42" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
@@ -4036,7 +4024,7 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4058,62 +4046,60 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C43" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D43" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E43" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F43" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H43" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I43" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J43" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K43" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L43" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M43" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N43" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O43" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
@@ -4140,50 +4126,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C44" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D44" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E44" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H44" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I44" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J44" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K44" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L44" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M44" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N44" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O44" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4191,18 +4177,18 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4215,74 +4201,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C45" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D45" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E45" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H45" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I45" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J45" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K45" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L45" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M45" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O45" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4295,83 +4289,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C46" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D46" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E46" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F46" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H46" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I46" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J46" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K46" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L46" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M46" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N46" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O46" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
@@ -4383,74 +4369,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C47" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D47" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E47" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F47" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H47" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I47" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J47" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K47" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L47" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M47" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N47" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O47" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4472,64 +4464,64 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C48" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D48" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E48" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F48" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H48" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I48" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J48" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K48" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L48" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M48" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N48" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O48" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
       <c r="Q48" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S48" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4549,84 +4541,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C49" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D49" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E49" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F49" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H49" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I49" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J49" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K49" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L49" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M49" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N49" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O49" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
+      <c r="U49" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
@@ -4635,55 +4623,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C50" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D50" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E50" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F50" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H50" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I50" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J50" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K50" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L50" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M50" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N50" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O50" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4694,20 +4686,16 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4719,57 +4707,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C51" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D51" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E51" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H51" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I51" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J51" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K51" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L51" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M51" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N51" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O51" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4780,78 +4768,80 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W51" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W51" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C52" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D52" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E52" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H52" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I52" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J52" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K52" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L52" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M52" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N52" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O52" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4869,18 +4859,14 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4892,50 +4878,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C53" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D53" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E53" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F53" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H53" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I53" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J53" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K53" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L53" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M53" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N53" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O53" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4943,8 +4929,10 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
@@ -4953,69 +4941,77 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C54" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D54" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E54" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F54" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H54" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I54" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J54" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K54" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M54" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N54" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O54" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5025,28 +5021,22 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
       </c>
       <c r="W54" s="9" t="inlineStr">
         <is>
@@ -5062,50 +5052,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D55" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E55" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H55" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I55" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J55" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K55" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L55" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M55" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O55" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5139,57 +5129,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C56" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D56" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E56" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F56" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H56" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I56" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J56" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K56" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L56" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M56" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N56" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O56" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5207,8 +5197,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5223,57 +5215,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C57" t="n">
-        <v>68.11</v>
+        <v>67</v>
       </c>
       <c r="D57" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E57" t="n">
-        <v>64.55</v>
+        <v>67.15000000000001</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.49</v>
+        <v>2.6</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.0402</v>
       </c>
       <c r="H57" t="n">
-        <v>5.01</v>
+        <v>3.98</v>
       </c>
       <c r="I57" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J57" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K57" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L57" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M57" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N57" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O57" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5281,21 +5273,19 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5308,90 +5298,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>63.51</v>
-      </c>
-      <c r="C58" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="D58" t="n">
-        <v>63.02</v>
-      </c>
-      <c r="E58" t="n">
-        <v>66.2</v>
-      </c>
-      <c r="F58" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0255</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="I58" t="n">
-        <v>58.09</v>
-      </c>
-      <c r="J58" t="n">
-        <v>59.02</v>
-      </c>
-      <c r="K58" t="n">
-        <v>62.05</v>
-      </c>
-      <c r="L58" t="n">
-        <v>65.08</v>
-      </c>
-      <c r="M58" t="n">
-        <v>67.06</v>
-      </c>
-      <c r="N58" t="n">
-        <v>69.03</v>
-      </c>
-      <c r="O58" t="n">
-        <v>73.11</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5229,22 +5229,22 @@
         <v>63.51</v>
       </c>
       <c r="C57" t="n">
-        <v>67</v>
+        <v>66.94</v>
       </c>
       <c r="D57" t="n">
         <v>63.02</v>
       </c>
       <c r="E57" t="n">
-        <v>67.15000000000001</v>
+        <v>66.56</v>
       </c>
       <c r="F57" t="n">
-        <v>2.6</v>
+        <v>2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0402</v>
+        <v>0.031</v>
       </c>
       <c r="H57" t="n">
-        <v>3.98</v>
+        <v>3.92</v>
       </c>
       <c r="I57" t="n">
         <v>58.09</v>
@@ -5300,6 +5300,88 @@
       <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>66.68000000000001</v>
+      </c>
+      <c r="C58" t="n">
+        <v>67.56</v>
+      </c>
+      <c r="D58" t="n">
+        <v>66.2</v>
+      </c>
+      <c r="E58" t="n">
+        <v>66.53</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0004</v>
+      </c>
+      <c r="H58" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="I58" t="n">
+        <v>59.1</v>
+      </c>
+      <c r="J58" t="n">
+        <v>63.42</v>
+      </c>
+      <c r="K58" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="L58" t="n">
+        <v>65.77</v>
+      </c>
+      <c r="M58" t="n">
+        <v>68.52</v>
+      </c>
+      <c r="N58" t="n">
+        <v>71.26000000000001</v>
+      </c>
+      <c r="O58" t="n">
+        <v>70.86</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5310,25 +5310,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>66.68000000000001</v>
+        <v>66.44</v>
       </c>
       <c r="C58" t="n">
-        <v>67.56</v>
+        <v>67.31999999999999</v>
       </c>
       <c r="D58" t="n">
-        <v>66.2</v>
+        <v>65.04000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>66.53</v>
+        <v>66.47</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.03</v>
+        <v>-0.08</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0004</v>
+        <v>-0.0012</v>
       </c>
       <c r="H58" t="n">
-        <v>1.36</v>
+        <v>2.28</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5319,13 +5319,13 @@
         <v>65.04000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>66.47</v>
+        <v>66.14</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.08</v>
+        <v>-0.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0012</v>
+        <v>-0.0063</v>
       </c>
       <c r="H58" t="n">
         <v>2.28</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5313,22 +5313,22 @@
         <v>66.44</v>
       </c>
       <c r="C58" t="n">
-        <v>67.31999999999999</v>
+        <v>67.75</v>
       </c>
       <c r="D58" t="n">
-        <v>65.04000000000001</v>
+        <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>66.14</v>
+        <v>67.70999999999999</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.42</v>
+        <v>1.15</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0063</v>
+        <v>0.0173</v>
       </c>
       <c r="H58" t="n">
-        <v>2.28</v>
+        <v>1.93</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>
@@ -5362,11 +5362,13 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5379,11 +5381,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>35.41</v>
+        <v>36.41</v>
       </c>
       <c r="J2" t="n">
-        <v>37.65</v>
+        <v>38.03</v>
       </c>
       <c r="K2" t="n">
-        <v>38.1</v>
+        <v>38.35</v>
       </c>
       <c r="L2" t="n">
-        <v>38.55</v>
+        <v>38.68</v>
       </c>
       <c r="M2" t="n">
-        <v>39.9</v>
+        <v>39.65</v>
       </c>
       <c r="N2" t="n">
-        <v>41.25</v>
+        <v>40.63</v>
       </c>
       <c r="O2" t="n">
-        <v>40.8</v>
+        <v>40.3</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,14 +695,16 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5313,22 +5315,22 @@
         <v>66.44</v>
       </c>
       <c r="C58" t="n">
-        <v>67.75</v>
+        <v>68.06</v>
       </c>
       <c r="D58" t="n">
         <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>67.70999999999999</v>
+        <v>67.36</v>
       </c>
       <c r="F58" t="n">
-        <v>1.15</v>
+        <v>0.8</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0173</v>
+        <v>0.012</v>
       </c>
       <c r="H58" t="n">
-        <v>1.93</v>
+        <v>2.23</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5321,13 +5321,13 @@
         <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>67.36</v>
+        <v>67.29000000000001</v>
       </c>
       <c r="F58" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.012</v>
+        <v>0.011</v>
       </c>
       <c r="H58" t="n">
         <v>2.23</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5321,13 +5321,13 @@
         <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>67.29000000000001</v>
+        <v>66.98</v>
       </c>
       <c r="F58" t="n">
-        <v>0.73</v>
+        <v>0.42</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.011</v>
+        <v>0.0064</v>
       </c>
       <c r="H58" t="n">
         <v>2.23</v>
@@ -5364,13 +5364,11 @@
       </c>
       <c r="S58" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5321,13 +5321,13 @@
         <v>65.81999999999999</v>
       </c>
       <c r="E58" t="n">
-        <v>66.98</v>
+        <v>67</v>
       </c>
       <c r="F58" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0064</v>
+        <v>0.0067</v>
       </c>
       <c r="H58" t="n">
         <v>2.23</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5318,19 +5318,19 @@
         <v>68.06</v>
       </c>
       <c r="D58" t="n">
-        <v>65.81999999999999</v>
+        <v>65.29000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>67</v>
+        <v>65.5</v>
       </c>
       <c r="F58" t="n">
-        <v>0.44</v>
+        <v>-1.06</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0067</v>
+        <v>-0.0159</v>
       </c>
       <c r="H58" t="n">
-        <v>2.23</v>
+        <v>2.76</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>
@@ -5362,9 +5362,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5381,7 +5381,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5315,22 +5315,22 @@
         <v>66.44</v>
       </c>
       <c r="C58" t="n">
-        <v>68.06</v>
+        <v>66.67</v>
       </c>
       <c r="D58" t="n">
-        <v>65.29000000000001</v>
+        <v>64.89</v>
       </c>
       <c r="E58" t="n">
-        <v>65.5</v>
+        <v>64.95</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.06</v>
+        <v>-1.61</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0159</v>
+        <v>-0.0241</v>
       </c>
       <c r="H58" t="n">
-        <v>2.76</v>
+        <v>1.77</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>
@@ -5359,12 +5359,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5383,7 +5385,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.8</v>
       </c>
       <c r="I2" t="n">
-        <v>36.41</v>
+        <v>37.05</v>
       </c>
       <c r="J2" t="n">
-        <v>38.03</v>
+        <v>38.27</v>
       </c>
       <c r="K2" t="n">
-        <v>38.35</v>
+        <v>38.51</v>
       </c>
       <c r="L2" t="n">
-        <v>38.68</v>
+        <v>38.76</v>
       </c>
       <c r="M2" t="n">
-        <v>39.65</v>
+        <v>39.49</v>
       </c>
       <c r="N2" t="n">
-        <v>40.63</v>
+        <v>40.22</v>
       </c>
       <c r="O2" t="n">
-        <v>40.3</v>
+        <v>39.98</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -698,12 +700,14 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V2" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
@@ -5318,19 +5322,19 @@
         <v>66.67</v>
       </c>
       <c r="D58" t="n">
-        <v>64.89</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="E58" t="n">
-        <v>64.95</v>
+        <v>64.19</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.61</v>
+        <v>-2.36</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0241</v>
+        <v>-0.0355</v>
       </c>
       <c r="H58" t="n">
-        <v>1.77</v>
+        <v>2.49</v>
       </c>
       <c r="I58" t="n">
         <v>59.1</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-08-25</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>38.76</v>
+        <v>40.19</v>
       </c>
       <c r="C2" t="n">
-        <v>40.31</v>
+        <v>41.72</v>
       </c>
       <c r="D2" t="n">
-        <v>38.51</v>
+        <v>40.19</v>
       </c>
       <c r="E2" t="n">
-        <v>40.2</v>
+        <v>41.07</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>0.87</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0307</v>
+        <v>0.0217</v>
       </c>
       <c r="H2" t="n">
-        <v>1.8</v>
+        <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>37.05</v>
+        <v>36.71</v>
       </c>
       <c r="J2" t="n">
-        <v>38.27</v>
+        <v>38.8</v>
       </c>
       <c r="K2" t="n">
-        <v>38.51</v>
+        <v>39.3</v>
       </c>
       <c r="L2" t="n">
-        <v>38.76</v>
+        <v>39.8</v>
       </c>
       <c r="M2" t="n">
-        <v>39.49</v>
+        <v>41.1</v>
       </c>
       <c r="N2" t="n">
-        <v>40.22</v>
+        <v>42.39</v>
       </c>
       <c r="O2" t="n">
-        <v>39.98</v>
+        <v>42.1</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,10 +685,8 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -697,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -720,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>40.19</v>
+        <v>41.15</v>
       </c>
       <c r="C3" t="n">
-        <v>41.72</v>
+        <v>42.39</v>
       </c>
       <c r="D3" t="n">
-        <v>40.19</v>
+        <v>40.88</v>
       </c>
       <c r="E3" t="n">
-        <v>41.07</v>
+        <v>42.39</v>
       </c>
       <c r="F3" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0217</v>
+        <v>0.032</v>
       </c>
       <c r="H3" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I3" t="n">
-        <v>36.71</v>
+        <v>38.66</v>
       </c>
       <c r="J3" t="n">
-        <v>38.8</v>
+        <v>39.61</v>
       </c>
       <c r="K3" t="n">
-        <v>39.3</v>
+        <v>40.31</v>
       </c>
       <c r="L3" t="n">
-        <v>39.8</v>
+        <v>41.01</v>
       </c>
       <c r="M3" t="n">
-        <v>41.1</v>
+        <v>41.84</v>
       </c>
       <c r="N3" t="n">
-        <v>42.39</v>
+        <v>42.67</v>
       </c>
       <c r="O3" t="n">
-        <v>42.1</v>
+        <v>43.24</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -781,11 +775,13 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.15</v>
+        <v>42.21</v>
       </c>
       <c r="C4" t="n">
-        <v>42.39</v>
+        <v>42.87</v>
       </c>
       <c r="D4" t="n">
-        <v>40.88</v>
+        <v>41.49</v>
       </c>
       <c r="E4" t="n">
-        <v>42.39</v>
+        <v>42.54</v>
       </c>
       <c r="F4" t="n">
-        <v>1.31</v>
+        <v>0.15</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0035</v>
       </c>
       <c r="H4" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I4" t="n">
-        <v>38.66</v>
+        <v>39.37</v>
       </c>
       <c r="J4" t="n">
-        <v>39.61</v>
+        <v>41.26</v>
       </c>
       <c r="K4" t="n">
-        <v>40.31</v>
+        <v>41.63</v>
       </c>
       <c r="L4" t="n">
-        <v>41.01</v>
+        <v>42.01</v>
       </c>
       <c r="M4" t="n">
-        <v>41.84</v>
+        <v>43.14</v>
       </c>
       <c r="N4" t="n">
-        <v>42.67</v>
+        <v>44.27</v>
       </c>
       <c r="O4" t="n">
-        <v>43.24</v>
+        <v>43.9</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,23 +847,21 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -882,50 +876,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>42.21</v>
+        <v>43.67</v>
       </c>
       <c r="C5" t="n">
-        <v>42.87</v>
+        <v>46.22</v>
       </c>
       <c r="D5" t="n">
-        <v>41.49</v>
+        <v>43.3</v>
       </c>
       <c r="E5" t="n">
-        <v>42.54</v>
+        <v>46.22</v>
       </c>
       <c r="F5" t="n">
-        <v>0.15</v>
+        <v>3.69</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0866</v>
       </c>
       <c r="H5" t="n">
-        <v>1.37</v>
+        <v>2.92</v>
       </c>
       <c r="I5" t="n">
-        <v>39.37</v>
+        <v>40.12</v>
       </c>
       <c r="J5" t="n">
-        <v>41.26</v>
+        <v>41.34</v>
       </c>
       <c r="K5" t="n">
-        <v>41.63</v>
+        <v>41.85</v>
       </c>
       <c r="L5" t="n">
-        <v>42.01</v>
+        <v>42.36</v>
       </c>
       <c r="M5" t="n">
-        <v>43.14</v>
+        <v>43.22</v>
       </c>
       <c r="N5" t="n">
-        <v>44.27</v>
+        <v>44.08</v>
       </c>
       <c r="O5" t="n">
-        <v>43.9</v>
+        <v>44.24</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,24 +927,28 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -962,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C6" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D6" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E6" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F6" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H6" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I6" t="n">
-        <v>40.12</v>
+        <v>40.38</v>
       </c>
       <c r="J6" t="n">
-        <v>41.34</v>
+        <v>44.03</v>
       </c>
       <c r="K6" t="n">
-        <v>41.85</v>
+        <v>44.76</v>
       </c>
       <c r="L6" t="n">
-        <v>42.36</v>
+        <v>45.49</v>
       </c>
       <c r="M6" t="n">
-        <v>43.22</v>
+        <v>47.68</v>
       </c>
       <c r="N6" t="n">
-        <v>44.08</v>
+        <v>49.87</v>
       </c>
       <c r="O6" t="n">
-        <v>44.24</v>
+        <v>49.14</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1023,18 +1021,14 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
@@ -1046,50 +1040,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C7" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D7" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E7" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F7" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H7" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I7" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J7" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K7" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L7" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M7" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N7" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O7" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1100,14 +1094,14 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U7" s="8" t="n">
@@ -1121,55 +1115,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C8" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D8" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E8" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I8" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J8" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K8" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L8" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M8" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N8" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O8" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1180,9 +1178,9 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T8" s="8" t="inlineStr">
@@ -1190,70 +1188,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C9" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D9" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E9" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F9" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H9" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I9" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J9" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K9" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L9" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M9" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N9" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O9" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1261,83 +1259,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C10" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D10" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E10" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H10" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I10" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J10" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K10" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L10" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M10" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N10" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O10" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1347,12 +1345,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1378,50 +1376,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C11" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D11" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E11" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H11" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I11" t="n">
         <v>43.01</v>
       </c>
       <c r="J11" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K11" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L11" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M11" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N11" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O11" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1429,14 +1427,12 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1455,57 +1451,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C12" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D12" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E12" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F12" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H12" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J12" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K12" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L12" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M12" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N12" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O12" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1518,76 +1514,78 @@
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C13" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D13" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E13" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F13" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I13" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J13" t="n">
         <v>45.26</v>
       </c>
-      <c r="J13" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K13" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L13" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M13" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N13" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O13" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1595,83 +1593,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C14" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D14" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E14" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H14" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I14" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J14" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K14" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L14" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M14" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N14" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O14" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1679,83 +1677,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C15" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D15" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E15" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F15" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H15" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I15" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J15" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K15" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L15" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M15" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N15" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O15" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,18 +1771,14 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1796,50 +1790,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C16" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D16" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E16" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F16" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H16" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I16" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J16" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K16" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L16" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M16" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N16" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O16" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,14 +1851,18 @@
       </c>
       <c r="T16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1876,50 +1874,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C17" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D17" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E17" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H17" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I17" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J17" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K17" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L17" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M17" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O17" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1945,10 +1943,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1960,50 +1956,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C18" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D18" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E18" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H18" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I18" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J18" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K18" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M18" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O18" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2029,8 +2025,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="n">
-        <v/>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2042,50 +2040,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C19" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D19" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E19" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F19" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H19" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I19" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J19" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M19" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N19" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2093,83 +2091,83 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C20" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D20" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E20" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F20" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H20" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I20" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J20" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K20" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L20" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M20" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N20" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2177,22 +2175,24 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
@@ -2201,59 +2201,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C21" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D21" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E21" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F21" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H21" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I21" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L21" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N21" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,11 +2272,13 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2292,50 +2290,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D22" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E22" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F22" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H22" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I22" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J22" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K22" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L22" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M22" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N22" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O22" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,13 +2356,11 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="9" t="inlineStr">
         <is>
@@ -2376,63 +2372,69 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C23" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D23" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E23" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H23" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I23" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J23" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K23" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M23" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N23" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O23" t="n">
-        <v>104</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2442,160 +2444,150 @@
       </c>
       <c r="U23" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C24" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D24" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E24" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H24" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I24" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J24" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K24" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L24" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M24" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N24" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O24" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C25" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D25" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E25" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H25" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J25" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K25" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L25" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M25" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N25" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O25" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2625,55 +2617,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D26" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E26" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F26" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H26" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I26" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J26" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K26" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L26" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M26" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N26" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O26" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,16 +2677,20 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2705,57 +2705,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C27" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D27" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E27" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H27" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I27" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J27" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K27" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L27" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M27" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O27" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2763,24 +2763,24 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2791,81 +2791,81 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C28" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D28" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E28" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I28" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J28" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K28" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L28" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M28" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N28" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O28" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2877,74 +2877,70 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C29" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D29" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E29" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F29" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H29" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I29" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J29" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K29" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L29" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M29" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N29" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O29" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2970,63 +2966,69 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C30" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E30" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F30" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H30" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I30" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J30" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K30" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L30" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M30" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N30" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O30" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3043,78 +3045,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E31" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F31" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H31" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I31" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J31" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K31" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L31" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M31" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N31" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O31" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
+        <v>97.48</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3131,55 +3125,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D32" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H32" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J32" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K32" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L32" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M32" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N32" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O32" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,18 +3185,18 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3213,57 +3211,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C33" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D33" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E33" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H33" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I33" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J33" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K33" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M33" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O33" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3304,50 +3302,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C34" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D34" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F34" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H34" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I34" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J34" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K34" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L34" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M34" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N34" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3388,50 +3386,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C35" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D35" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E35" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F35" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H35" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I35" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J35" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K35" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L35" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M35" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N35" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3439,19 +3437,19 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3465,72 +3463,76 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D36" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E36" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F36" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H36" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I36" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J36" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K36" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L36" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M36" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N36" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3547,82 +3549,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E37" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H37" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I37" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J37" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L37" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M37" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N37" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O37" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
+        <v>82.87</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3635,55 +3631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C38" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D38" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E38" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F38" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H38" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I38" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J38" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K38" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L38" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M38" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N38" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O38" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3693,19 +3693,19 @@
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3719,57 +3719,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F39" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H39" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I39" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J39" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K39" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L39" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M39" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O39" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3777,20 +3777,16 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3803,59 +3799,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C40" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D40" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E40" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H40" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I40" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J40" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L40" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N40" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O40" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3863,8 +3855,10 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
@@ -3890,56 +3884,58 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C41" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D41" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E41" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F41" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H41" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I41" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J41" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K41" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N41" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O41" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3948,7 +3944,7 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3970,62 +3966,60 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C42" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D42" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E42" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F42" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H42" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I42" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J42" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K42" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M42" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N42" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O42" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
@@ -4052,50 +4046,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C43" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D43" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E43" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H43" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I43" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J43" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K43" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L43" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M43" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N43" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O43" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4103,18 +4097,18 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4127,74 +4121,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C44" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D44" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E44" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F44" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H44" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I44" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J44" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K44" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L44" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M44" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O44" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4207,83 +4209,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C45" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D45" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E45" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F45" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H45" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I45" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J45" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K45" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L45" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M45" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N45" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O45" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
@@ -4295,74 +4289,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C46" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D46" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E46" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F46" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H46" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I46" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J46" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K46" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L46" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M46" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N46" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O46" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4384,64 +4384,64 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C47" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D47" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E47" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F47" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H47" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I47" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J47" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K47" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L47" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M47" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N47" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O47" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
       <c r="Q47" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4461,84 +4461,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C48" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D48" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E48" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F48" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H48" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I48" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J48" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K48" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L48" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M48" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N48" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O48" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
+      <c r="U48" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
@@ -4547,55 +4543,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C49" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D49" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E49" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F49" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H49" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I49" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J49" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K49" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L49" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M49" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N49" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O49" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,20 +4606,16 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
@@ -4631,57 +4627,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C50" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D50" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E50" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F50" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H50" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I50" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J50" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K50" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L50" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M50" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N50" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O50" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4692,78 +4688,80 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C51" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D51" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E51" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F51" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H51" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I51" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J51" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K51" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L51" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M51" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N51" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O51" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4781,18 +4779,14 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4804,50 +4798,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C52" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D52" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E52" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F52" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H52" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I52" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J52" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K52" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L52" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M52" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N52" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O52" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4855,8 +4849,10 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
@@ -4865,69 +4861,77 @@
       </c>
       <c r="T52" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C53" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D53" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E53" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F53" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H53" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I53" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J53" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K53" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M53" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N53" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O53" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4937,28 +4941,22 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
       </c>
       <c r="W53" s="9" t="inlineStr">
         <is>
@@ -4974,50 +4972,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C54" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D54" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E54" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H54" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I54" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J54" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K54" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L54" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M54" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N54" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O54" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5051,57 +5049,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C55" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D55" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E55" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F55" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H55" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I55" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J55" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K55" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L55" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M55" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N55" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O55" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5119,8 +5117,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5135,57 +5135,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C56" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D56" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E56" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F56" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H56" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I56" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J56" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K56" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L56" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M56" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N56" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O56" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5193,19 +5193,17 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U56" s="8" t="n">
@@ -5228,70 +5226,72 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C57" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D57" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E57" t="n">
-        <v>66.56</v>
+        <v>64.8</v>
       </c>
       <c r="F57" t="n">
-        <v>2</v>
+        <v>-1.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0264</v>
       </c>
       <c r="H57" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I57" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J57" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K57" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L57" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M57" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N57" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O57" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
@@ -5305,91 +5305,7 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-21</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>66.44</v>
-      </c>
-      <c r="C58" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="D58" t="n">
-        <v>64.18000000000001</v>
-      </c>
-      <c r="E58" t="n">
-        <v>64.19</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.36</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0355</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="I58" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="J58" t="n">
-        <v>63.42</v>
-      </c>
-      <c r="K58" t="n">
-        <v>64.59999999999999</v>
-      </c>
-      <c r="L58" t="n">
-        <v>65.77</v>
-      </c>
-      <c r="M58" t="n">
-        <v>68.52</v>
-      </c>
-      <c r="N58" t="n">
-        <v>71.26000000000001</v>
-      </c>
-      <c r="O58" t="n">
-        <v>70.86</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5239,13 +5239,13 @@
         <v>63</v>
       </c>
       <c r="E57" t="n">
-        <v>64.8</v>
+        <v>64.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-1.75</v>
+        <v>-2.31</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0264</v>
+        <v>-0.0347</v>
       </c>
       <c r="H57" t="n">
         <v>3.67</v>
@@ -5304,6 +5304,92 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>61.03</v>
+      </c>
+      <c r="C58" t="n">
+        <v>61.13</v>
+      </c>
+      <c r="D58" t="n">
+        <v>61.01</v>
+      </c>
+      <c r="E58" t="n">
+        <v>61.12</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-3.12</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.0486</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I58" t="n">
+        <v>59.33</v>
+      </c>
+      <c r="J58" t="n">
+        <v>60.29</v>
+      </c>
+      <c r="K58" t="n">
+        <v>62.41</v>
+      </c>
+      <c r="L58" t="n">
+        <v>64.54000000000001</v>
+      </c>
+      <c r="M58" t="n">
+        <v>66.08</v>
+      </c>
+      <c r="N58" t="n">
+        <v>67.62</v>
+      </c>
+      <c r="O58" t="n">
+        <v>70.33</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>36.71</v>
+        <v>36.75</v>
       </c>
       <c r="J2" t="n">
-        <v>38.8</v>
+        <v>38.81</v>
       </c>
       <c r="K2" t="n">
-        <v>39.3</v>
+        <v>39.31</v>
       </c>
       <c r="L2" t="n">
-        <v>39.8</v>
+        <v>39.81</v>
       </c>
       <c r="M2" t="n">
-        <v>41.1</v>
+        <v>41.09</v>
       </c>
       <c r="N2" t="n">
-        <v>42.39</v>
+        <v>42.37</v>
       </c>
       <c r="O2" t="n">
-        <v>42.1</v>
+        <v>42.08</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5316,25 +5316,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>61.03</v>
+        <v>61.38</v>
       </c>
       <c r="C58" t="n">
-        <v>61.13</v>
+        <v>61.97</v>
       </c>
       <c r="D58" t="n">
-        <v>61.01</v>
+        <v>61.22</v>
       </c>
       <c r="E58" t="n">
-        <v>61.12</v>
+        <v>61.97</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.12</v>
+        <v>-2.28</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0486</v>
+        <v>-0.0355</v>
       </c>
       <c r="H58" t="n">
-        <v>0.12</v>
+        <v>0.75</v>
       </c>
       <c r="I58" t="n">
         <v>59.33</v>
@@ -5360,14 +5360,12 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.53</v>
       </c>
       <c r="I2" t="n">
-        <v>36.75</v>
+        <v>37.06</v>
       </c>
       <c r="J2" t="n">
-        <v>38.81</v>
+        <v>38.93</v>
       </c>
       <c r="K2" t="n">
-        <v>39.31</v>
+        <v>39.39</v>
       </c>
       <c r="L2" t="n">
-        <v>39.81</v>
+        <v>39.85</v>
       </c>
       <c r="M2" t="n">
-        <v>41.09</v>
+        <v>41.01</v>
       </c>
       <c r="N2" t="n">
-        <v>42.37</v>
+        <v>42.18</v>
       </c>
       <c r="O2" t="n">
-        <v>42.08</v>
+        <v>41.93</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5319,22 +5319,22 @@
         <v>61.38</v>
       </c>
       <c r="C58" t="n">
-        <v>61.97</v>
+        <v>61.38</v>
       </c>
       <c r="D58" t="n">
-        <v>61.22</v>
+        <v>60.49</v>
       </c>
       <c r="E58" t="n">
-        <v>61.97</v>
+        <v>60.76</v>
       </c>
       <c r="F58" t="n">
-        <v>-2.28</v>
+        <v>-3.49</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0355</v>
+        <v>-0.0543</v>
       </c>
       <c r="H58" t="n">
-        <v>0.75</v>
+        <v>0.89</v>
       </c>
       <c r="I58" t="n">
         <v>59.33</v>
@@ -5360,12 +5360,14 @@
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5322,19 +5322,19 @@
         <v>61.38</v>
       </c>
       <c r="D58" t="n">
-        <v>60.49</v>
+        <v>60</v>
       </c>
       <c r="E58" t="n">
-        <v>60.76</v>
+        <v>61.31</v>
       </c>
       <c r="F58" t="n">
-        <v>-3.49</v>
+        <v>-2.94</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0543</v>
+        <v>-0.0458</v>
       </c>
       <c r="H58" t="n">
-        <v>0.89</v>
+        <v>1.38</v>
       </c>
       <c r="I58" t="n">
         <v>59.33</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>40.19</v>
+        <v>41.15</v>
       </c>
       <c r="C2" t="n">
-        <v>41.72</v>
+        <v>42.39</v>
       </c>
       <c r="D2" t="n">
-        <v>40.19</v>
+        <v>40.88</v>
       </c>
       <c r="E2" t="n">
-        <v>41.07</v>
+        <v>42.39</v>
       </c>
       <c r="F2" t="n">
-        <v>0.87</v>
+        <v>1.31</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0217</v>
+        <v>0.032</v>
       </c>
       <c r="H2" t="n">
-        <v>1.53</v>
+        <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>37.06</v>
+        <v>38.66</v>
       </c>
       <c r="J2" t="n">
-        <v>38.93</v>
+        <v>39.61</v>
       </c>
       <c r="K2" t="n">
-        <v>39.39</v>
+        <v>40.31</v>
       </c>
       <c r="L2" t="n">
-        <v>39.85</v>
+        <v>41.01</v>
       </c>
       <c r="M2" t="n">
-        <v>41.01</v>
+        <v>41.84</v>
       </c>
       <c r="N2" t="n">
-        <v>42.18</v>
+        <v>42.67</v>
       </c>
       <c r="O2" t="n">
-        <v>41.93</v>
+        <v>43.24</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,11 +695,13 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -714,50 +716,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>41.15</v>
+        <v>42.21</v>
       </c>
       <c r="C3" t="n">
-        <v>42.39</v>
+        <v>42.87</v>
       </c>
       <c r="D3" t="n">
-        <v>40.88</v>
+        <v>41.49</v>
       </c>
       <c r="E3" t="n">
-        <v>42.39</v>
+        <v>42.54</v>
       </c>
       <c r="F3" t="n">
-        <v>1.31</v>
+        <v>0.15</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0035</v>
       </c>
       <c r="H3" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I3" t="n">
-        <v>38.66</v>
+        <v>39.37</v>
       </c>
       <c r="J3" t="n">
-        <v>39.61</v>
+        <v>41.26</v>
       </c>
       <c r="K3" t="n">
-        <v>40.31</v>
+        <v>41.63</v>
       </c>
       <c r="L3" t="n">
-        <v>41.01</v>
+        <v>42.01</v>
       </c>
       <c r="M3" t="n">
-        <v>41.84</v>
+        <v>43.14</v>
       </c>
       <c r="N3" t="n">
-        <v>42.67</v>
+        <v>44.27</v>
       </c>
       <c r="O3" t="n">
-        <v>43.24</v>
+        <v>43.9</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,23 +767,21 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -796,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>42.21</v>
+        <v>43.67</v>
       </c>
       <c r="C4" t="n">
-        <v>42.87</v>
+        <v>46.22</v>
       </c>
       <c r="D4" t="n">
-        <v>41.49</v>
+        <v>43.3</v>
       </c>
       <c r="E4" t="n">
-        <v>42.54</v>
+        <v>46.22</v>
       </c>
       <c r="F4" t="n">
-        <v>0.15</v>
+        <v>3.69</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0866</v>
       </c>
       <c r="H4" t="n">
-        <v>1.37</v>
+        <v>2.92</v>
       </c>
       <c r="I4" t="n">
-        <v>39.37</v>
+        <v>40.12</v>
       </c>
       <c r="J4" t="n">
-        <v>41.26</v>
+        <v>41.34</v>
       </c>
       <c r="K4" t="n">
-        <v>41.63</v>
+        <v>41.85</v>
       </c>
       <c r="L4" t="n">
-        <v>42.01</v>
+        <v>42.36</v>
       </c>
       <c r="M4" t="n">
-        <v>43.14</v>
+        <v>43.22</v>
       </c>
       <c r="N4" t="n">
-        <v>44.27</v>
+        <v>44.08</v>
       </c>
       <c r="O4" t="n">
-        <v>43.9</v>
+        <v>44.24</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,24 +847,28 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -876,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C5" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D5" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E5" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F5" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H5" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I5" t="n">
-        <v>40.12</v>
+        <v>40.38</v>
       </c>
       <c r="J5" t="n">
-        <v>41.34</v>
+        <v>44.03</v>
       </c>
       <c r="K5" t="n">
-        <v>41.85</v>
+        <v>44.76</v>
       </c>
       <c r="L5" t="n">
-        <v>42.36</v>
+        <v>45.49</v>
       </c>
       <c r="M5" t="n">
-        <v>43.22</v>
+        <v>47.68</v>
       </c>
       <c r="N5" t="n">
-        <v>44.08</v>
+        <v>49.87</v>
       </c>
       <c r="O5" t="n">
-        <v>44.24</v>
+        <v>49.14</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -937,18 +941,14 @@
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
@@ -960,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C6" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D6" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E6" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F6" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H6" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I6" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J6" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K6" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L6" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M6" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N6" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O6" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1014,14 +1014,14 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U6" s="8" t="n">
@@ -1035,55 +1035,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C7" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D7" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E7" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H7" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I7" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J7" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K7" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L7" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M7" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N7" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O7" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1094,9 +1098,9 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
@@ -1104,70 +1108,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C8" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D8" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E8" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F8" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H8" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I8" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J8" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K8" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L8" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M8" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N8" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O8" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1175,83 +1179,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C9" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D9" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E9" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I9" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J9" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K9" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L9" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M9" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N9" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O9" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1261,12 +1265,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1292,50 +1296,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C10" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D10" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E10" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H10" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I10" t="n">
         <v>43.01</v>
       </c>
       <c r="J10" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K10" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L10" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M10" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N10" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O10" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1343,14 +1347,12 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1369,57 +1371,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C11" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D11" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E11" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F11" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H11" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I11" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J11" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K11" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L11" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M11" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N11" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O11" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,76 +1434,78 @@
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C12" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D12" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E12" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F12" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I12" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J12" t="n">
         <v>45.26</v>
       </c>
-      <c r="J12" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K12" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L12" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M12" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N12" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O12" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1509,83 +1513,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C13" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D13" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E13" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H13" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I13" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J13" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K13" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L13" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M13" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N13" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O13" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1593,83 +1597,83 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C14" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D14" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E14" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F14" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H14" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I14" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J14" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K14" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L14" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M14" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N14" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O14" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,18 +1691,14 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1710,50 +1710,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C15" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D15" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E15" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H15" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I15" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J15" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K15" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L15" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M15" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N15" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O15" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,14 +1771,18 @@
       </c>
       <c r="T15" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1790,50 +1794,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C16" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D16" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E16" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H16" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I16" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J16" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K16" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L16" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M16" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N16" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O16" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1859,10 +1863,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1874,50 +1876,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C17" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D17" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E17" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H17" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I17" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J17" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K17" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L17" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M17" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O17" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1943,8 +1945,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="n">
-        <v/>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1956,50 +1960,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C18" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E18" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F18" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H18" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I18" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J18" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M18" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N18" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O18" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2007,83 +2011,83 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C19" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E19" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F19" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H19" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I19" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J19" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K19" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L19" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M19" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N19" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2091,22 +2095,24 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
@@ -2115,59 +2121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C20" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D20" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E20" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F20" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H20" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I20" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J20" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L20" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M20" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N20" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O20" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2190,11 +2192,13 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2206,50 +2210,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D21" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E21" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F21" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H21" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I21" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J21" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K21" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L21" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M21" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N21" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O21" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2272,13 +2276,11 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
@@ -2290,63 +2292,69 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C22" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D22" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E22" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H22" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I22" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J22" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K22" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M22" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N22" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O22" t="n">
-        <v>104</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2356,160 +2364,150 @@
       </c>
       <c r="U22" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C23" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D23" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E23" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H23" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I23" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J23" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K23" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L23" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M23" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N23" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O23" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
       </c>
       <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C24" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D24" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E24" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H24" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I24" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J24" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K24" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M24" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N24" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O24" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2539,55 +2537,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C25" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D25" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E25" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F25" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H25" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I25" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J25" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K25" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L25" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M25" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N25" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O25" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2595,16 +2597,20 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2619,57 +2625,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C26" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D26" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E26" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H26" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I26" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J26" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K26" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L26" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M26" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N26" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O26" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2677,24 +2683,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2705,81 +2711,81 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C27" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D27" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E27" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I27" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J27" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K27" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L27" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M27" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N27" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O27" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2791,74 +2797,70 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C28" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D28" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E28" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H28" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I28" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J28" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L28" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M28" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N28" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O28" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2884,63 +2886,69 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C29" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D29" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E29" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F29" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H29" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I29" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J29" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K29" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L29" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M29" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N29" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O29" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2957,78 +2965,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D30" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E30" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H30" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I30" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J30" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K30" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L30" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M30" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N30" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O30" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P30" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q30" s="6" t="inlineStr">
+        <v>97.48</v>
+      </c>
+      <c r="P30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3045,55 +3045,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D31" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H31" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J31" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K31" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L31" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M31" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N31" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O31" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3101,18 +3105,18 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3127,57 +3131,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D32" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E32" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H32" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I32" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J32" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K32" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M32" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O32" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3218,50 +3222,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C33" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D33" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E33" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F33" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H33" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I33" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J33" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K33" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L33" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M33" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N33" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3302,50 +3306,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C34" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D34" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E34" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F34" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H34" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I34" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J34" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K34" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L34" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M34" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N34" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3353,19 +3357,19 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="R34" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3379,72 +3383,76 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D35" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E35" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F35" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H35" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I35" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J35" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K35" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L35" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M35" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N35" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3461,82 +3469,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D36" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E36" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H36" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I36" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J36" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L36" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M36" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N36" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O36" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
+        <v>82.87</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3549,55 +3551,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C37" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D37" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E37" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F37" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H37" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I37" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J37" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K37" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L37" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M37" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N37" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O37" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3607,19 +3613,19 @@
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
@@ -3633,57 +3639,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F38" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H38" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I38" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J38" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K38" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L38" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M38" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O38" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3691,20 +3697,16 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3717,59 +3719,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C39" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D39" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E39" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H39" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I39" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J39" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K39" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L39" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N39" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O39" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3777,8 +3775,10 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
@@ -3804,56 +3804,58 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C40" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D40" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E40" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F40" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H40" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I40" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J40" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K40" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N40" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O40" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3862,7 +3864,7 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3884,62 +3886,60 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C41" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D41" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E41" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F41" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H41" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I41" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J41" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K41" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L41" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M41" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N41" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O41" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
@@ -3966,50 +3966,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C42" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D42" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E42" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H42" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I42" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J42" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K42" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M42" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N42" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O42" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4017,18 +4017,18 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4041,74 +4041,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C43" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D43" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E43" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F43" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H43" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I43" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J43" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K43" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L43" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M43" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O43" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4121,83 +4129,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C44" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D44" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E44" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F44" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H44" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I44" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J44" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K44" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L44" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M44" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N44" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O44" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4209,74 +4209,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C45" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D45" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E45" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F45" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H45" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I45" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J45" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K45" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L45" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M45" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N45" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O45" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4298,64 +4304,64 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C46" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D46" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E46" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F46" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H46" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I46" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J46" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K46" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L46" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M46" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N46" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O46" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
       <c r="Q46" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4375,84 +4381,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C47" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D47" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E47" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F47" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H47" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I47" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J47" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K47" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L47" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M47" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N47" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O47" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
+      <c r="U47" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
@@ -4461,55 +4463,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C48" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D48" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E48" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F48" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H48" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I48" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J48" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K48" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L48" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M48" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N48" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O48" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4520,20 +4526,16 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
@@ -4545,57 +4547,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C49" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D49" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E49" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F49" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H49" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I49" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J49" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K49" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L49" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M49" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N49" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O49" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4606,78 +4608,80 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C50" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D50" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E50" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F50" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H50" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I50" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J50" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K50" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L50" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M50" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N50" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O50" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4695,18 +4699,14 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4718,50 +4718,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C51" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D51" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E51" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F51" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H51" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I51" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J51" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K51" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L51" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M51" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N51" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O51" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4769,8 +4769,10 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
@@ -4779,69 +4781,77 @@
       </c>
       <c r="T51" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
-      </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C52" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D52" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E52" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F52" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H52" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I52" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J52" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K52" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M52" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N52" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O52" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4851,28 +4861,22 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
@@ -4888,50 +4892,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C53" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D53" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E53" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H53" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I53" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J53" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K53" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L53" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M53" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N53" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O53" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4965,57 +4969,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C54" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D54" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E54" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F54" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H54" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I54" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J54" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K54" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L54" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M54" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N54" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O54" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5033,8 +5037,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5049,57 +5055,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C55" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D55" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E55" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F55" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H55" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I55" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J55" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K55" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L55" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M55" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N55" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O55" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5107,19 +5113,17 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U55" s="8" t="n">
@@ -5142,70 +5146,72 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C56" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D56" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E56" t="n">
-        <v>66.56</v>
+        <v>64.25</v>
       </c>
       <c r="F56" t="n">
-        <v>2</v>
+        <v>-2.31</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0347</v>
       </c>
       <c r="H56" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I56" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J56" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K56" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L56" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M56" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N56" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O56" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5219,71 +5225,71 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>66.44</v>
+        <v>61.38</v>
       </c>
       <c r="C57" t="n">
-        <v>66.67</v>
+        <v>61.56</v>
       </c>
       <c r="D57" t="n">
-        <v>63</v>
+        <v>59.98</v>
       </c>
       <c r="E57" t="n">
-        <v>64.25</v>
+        <v>60.42</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.31</v>
+        <v>-3.83</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0347</v>
+        <v>-0.0596</v>
       </c>
       <c r="H57" t="n">
-        <v>3.67</v>
+        <v>1.58</v>
       </c>
       <c r="I57" t="n">
-        <v>59.1</v>
+        <v>59.33</v>
       </c>
       <c r="J57" t="n">
-        <v>63.42</v>
+        <v>60.29</v>
       </c>
       <c r="K57" t="n">
-        <v>64.59999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="L57" t="n">
-        <v>65.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>68.52</v>
+        <v>66.08</v>
       </c>
       <c r="N57" t="n">
-        <v>71.26000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="O57" t="n">
-        <v>70.86</v>
+        <v>70.33</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5304,92 +5310,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-09-28</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>61.38</v>
-      </c>
-      <c r="C58" t="n">
-        <v>61.38</v>
-      </c>
-      <c r="D58" t="n">
-        <v>60</v>
-      </c>
-      <c r="E58" t="n">
-        <v>61.31</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.94</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0458</v>
-      </c>
-      <c r="H58" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="I58" t="n">
-        <v>59.33</v>
-      </c>
-      <c r="J58" t="n">
-        <v>60.29</v>
-      </c>
-      <c r="K58" t="n">
-        <v>62.41</v>
-      </c>
-      <c r="L58" t="n">
-        <v>64.54000000000001</v>
-      </c>
-      <c r="M58" t="n">
-        <v>66.08</v>
-      </c>
-      <c r="N58" t="n">
-        <v>67.62</v>
-      </c>
-      <c r="O58" t="n">
-        <v>70.33</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
         <is>
           <t>強警訊</t>
         </is>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5245,13 +5245,13 @@
         <v>59.98</v>
       </c>
       <c r="E57" t="n">
-        <v>60.42</v>
+        <v>59.98</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.83</v>
+        <v>-4.27</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0596</v>
+        <v>-0.0664</v>
       </c>
       <c r="H57" t="n">
         <v>1.58</v>
@@ -5304,14 +5304,96 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="C58" t="n">
+        <v>61.46</v>
+      </c>
+      <c r="D58" t="n">
+        <v>61.38</v>
+      </c>
+      <c r="E58" t="n">
+        <v>61.4</v>
+      </c>
+      <c r="F58" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.0238</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I58" t="n">
+        <v>58.4</v>
+      </c>
+      <c r="J58" t="n">
+        <v>58</v>
+      </c>
+      <c r="K58" t="n">
+        <v>59.19</v>
+      </c>
+      <c r="L58" t="n">
+        <v>60.37</v>
+      </c>
+      <c r="M58" t="n">
+        <v>60.77</v>
+      </c>
+      <c r="N58" t="n">
+        <v>61.16</v>
+      </c>
+      <c r="O58" t="n">
+        <v>63.13</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>強警訊</t>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>38.66</v>
+        <v>39.88</v>
       </c>
       <c r="J2" t="n">
-        <v>39.61</v>
+        <v>40.07</v>
       </c>
       <c r="K2" t="n">
-        <v>40.31</v>
+        <v>40.62</v>
       </c>
       <c r="L2" t="n">
-        <v>41.01</v>
+        <v>41.17</v>
       </c>
       <c r="M2" t="n">
-        <v>41.84</v>
+        <v>41.53</v>
       </c>
       <c r="N2" t="n">
-        <v>42.67</v>
+        <v>41.9</v>
       </c>
       <c r="O2" t="n">
-        <v>43.24</v>
+        <v>42.63</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -700,11 +700,13 @@
       </c>
       <c r="U2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5318,25 +5320,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>61.4</v>
+        <v>61.52</v>
       </c>
       <c r="C58" t="n">
-        <v>61.46</v>
+        <v>61.85</v>
       </c>
       <c r="D58" t="n">
-        <v>61.38</v>
+        <v>60.87</v>
       </c>
       <c r="E58" t="n">
-        <v>61.4</v>
+        <v>61.53</v>
       </c>
       <c r="F58" t="n">
-        <v>1.43</v>
+        <v>1.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0238</v>
+        <v>0.0258</v>
       </c>
       <c r="H58" t="n">
-        <v>0.08</v>
+        <v>0.98</v>
       </c>
       <c r="I58" t="n">
         <v>58.4</v>
@@ -5391,11 +5393,7 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>39.88</v>
+        <v>40.06</v>
       </c>
       <c r="J2" t="n">
-        <v>40.07</v>
+        <v>40.29</v>
       </c>
       <c r="K2" t="n">
-        <v>40.62</v>
+        <v>40.71</v>
       </c>
       <c r="L2" t="n">
-        <v>41.17</v>
+        <v>41.12</v>
       </c>
       <c r="M2" t="n">
-        <v>41.53</v>
+        <v>41.44</v>
       </c>
       <c r="N2" t="n">
-        <v>41.9</v>
+        <v>41.76</v>
       </c>
       <c r="O2" t="n">
-        <v>42.63</v>
+        <v>42.27</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5323,22 +5323,22 @@
         <v>61.52</v>
       </c>
       <c r="C58" t="n">
-        <v>61.85</v>
+        <v>61.62</v>
       </c>
       <c r="D58" t="n">
-        <v>60.87</v>
+        <v>59.96</v>
       </c>
       <c r="E58" t="n">
-        <v>61.53</v>
+        <v>59.98</v>
       </c>
       <c r="F58" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0258</v>
+        <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>0.98</v>
+        <v>1.66</v>
       </c>
       <c r="I58" t="n">
         <v>58.4</v>
@@ -5370,9 +5370,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
@@ -5382,18 +5382,22 @@
       </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5326,19 +5326,19 @@
         <v>61.62</v>
       </c>
       <c r="D58" t="n">
-        <v>59.96</v>
+        <v>59.91</v>
       </c>
       <c r="E58" t="n">
-        <v>59.98</v>
+        <v>60.53</v>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>0.55</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0</v>
+        <v>0.0091</v>
       </c>
       <c r="H58" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="I58" t="n">
         <v>58.4</v>
@@ -5370,9 +5370,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.51</v>
       </c>
       <c r="I2" t="n">
-        <v>40.06</v>
+        <v>40.2</v>
       </c>
       <c r="J2" t="n">
-        <v>40.29</v>
+        <v>40.34</v>
       </c>
       <c r="K2" t="n">
-        <v>40.71</v>
+        <v>40.74</v>
       </c>
       <c r="L2" t="n">
-        <v>41.12</v>
+        <v>41.14</v>
       </c>
       <c r="M2" t="n">
-        <v>41.44</v>
+        <v>41.41</v>
       </c>
       <c r="N2" t="n">
-        <v>41.76</v>
+        <v>41.67</v>
       </c>
       <c r="O2" t="n">
-        <v>42.27</v>
+        <v>42.2</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5326,19 +5326,19 @@
         <v>61.62</v>
       </c>
       <c r="D58" t="n">
-        <v>59.91</v>
+        <v>59.45</v>
       </c>
       <c r="E58" t="n">
-        <v>60.53</v>
+        <v>60.31</v>
       </c>
       <c r="F58" t="n">
-        <v>0.55</v>
+        <v>0.33</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0091</v>
+        <v>0.0056</v>
       </c>
       <c r="H58" t="n">
-        <v>1.71</v>
+        <v>2.17</v>
       </c>
       <c r="I58" t="n">
         <v>58.4</v>
@@ -5370,9 +5370,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>41.15</v>
+        <v>42.21</v>
       </c>
       <c r="C2" t="n">
-        <v>42.39</v>
+        <v>42.87</v>
       </c>
       <c r="D2" t="n">
-        <v>40.88</v>
+        <v>41.49</v>
       </c>
       <c r="E2" t="n">
-        <v>42.39</v>
+        <v>42.54</v>
       </c>
       <c r="F2" t="n">
-        <v>1.31</v>
+        <v>0.15</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.032</v>
+        <v>0.0035</v>
       </c>
       <c r="H2" t="n">
-        <v>1.51</v>
+        <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>40.2</v>
+        <v>39.37</v>
       </c>
       <c r="J2" t="n">
-        <v>40.34</v>
+        <v>41.26</v>
       </c>
       <c r="K2" t="n">
-        <v>40.74</v>
+        <v>41.63</v>
       </c>
       <c r="L2" t="n">
-        <v>41.14</v>
+        <v>42.01</v>
       </c>
       <c r="M2" t="n">
-        <v>41.41</v>
+        <v>43.14</v>
       </c>
       <c r="N2" t="n">
-        <v>41.67</v>
+        <v>44.27</v>
       </c>
       <c r="O2" t="n">
-        <v>42.2</v>
+        <v>43.9</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,28 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>42.21</v>
+        <v>43.67</v>
       </c>
       <c r="C3" t="n">
-        <v>42.87</v>
+        <v>46.22</v>
       </c>
       <c r="D3" t="n">
-        <v>41.49</v>
+        <v>43.3</v>
       </c>
       <c r="E3" t="n">
-        <v>42.54</v>
+        <v>46.22</v>
       </c>
       <c r="F3" t="n">
-        <v>0.15</v>
+        <v>3.69</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0866</v>
       </c>
       <c r="H3" t="n">
-        <v>1.37</v>
+        <v>2.92</v>
       </c>
       <c r="I3" t="n">
-        <v>39.37</v>
+        <v>40.12</v>
       </c>
       <c r="J3" t="n">
-        <v>41.26</v>
+        <v>41.34</v>
       </c>
       <c r="K3" t="n">
-        <v>41.63</v>
+        <v>41.85</v>
       </c>
       <c r="L3" t="n">
-        <v>42.01</v>
+        <v>42.36</v>
       </c>
       <c r="M3" t="n">
-        <v>43.14</v>
+        <v>43.22</v>
       </c>
       <c r="N3" t="n">
-        <v>44.27</v>
+        <v>44.08</v>
       </c>
       <c r="O3" t="n">
-        <v>43.9</v>
+        <v>44.24</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,24 +765,28 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R3" s="6" t="n">
+        <v/>
       </c>
       <c r="S3" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -798,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C4" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D4" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E4" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F4" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H4" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I4" t="n">
-        <v>40.12</v>
+        <v>40.38</v>
       </c>
       <c r="J4" t="n">
-        <v>41.34</v>
+        <v>44.03</v>
       </c>
       <c r="K4" t="n">
-        <v>41.85</v>
+        <v>44.76</v>
       </c>
       <c r="L4" t="n">
-        <v>42.36</v>
+        <v>45.49</v>
       </c>
       <c r="M4" t="n">
-        <v>43.22</v>
+        <v>47.68</v>
       </c>
       <c r="N4" t="n">
-        <v>44.08</v>
+        <v>49.87</v>
       </c>
       <c r="O4" t="n">
-        <v>44.24</v>
+        <v>49.14</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -859,18 +859,14 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
@@ -882,50 +878,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C5" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D5" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E5" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F5" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H5" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I5" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J5" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K5" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L5" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M5" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N5" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O5" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -936,14 +932,14 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U5" s="8" t="n">
@@ -957,55 +953,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C6" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D6" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E6" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I6" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J6" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K6" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L6" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M6" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N6" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O6" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1016,9 +1016,9 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T6" s="8" t="inlineStr">
@@ -1026,70 +1026,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V6" s="8" t="n">
-        <v/>
+      <c r="U6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C7" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D7" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E7" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F7" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H7" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I7" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J7" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K7" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L7" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M7" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N7" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O7" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1097,83 +1097,83 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V7" s="8" t="n">
+        <v/>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C8" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D8" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E8" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H8" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I8" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J8" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K8" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L8" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M8" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N8" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O8" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1214,50 +1214,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C9" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D9" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E9" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H9" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I9" t="n">
         <v>43.01</v>
       </c>
       <c r="J9" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K9" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L9" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M9" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N9" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O9" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1265,14 +1265,12 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1291,57 +1289,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C10" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D10" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E10" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F10" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H10" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I10" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J10" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K10" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L10" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M10" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N10" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O10" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1354,76 +1352,78 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C11" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D11" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E11" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F11" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H11" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I11" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J11" t="n">
         <v>45.26</v>
       </c>
-      <c r="J11" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K11" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L11" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M11" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N11" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O11" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1431,83 +1431,83 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C12" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D12" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E12" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H12" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I12" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J12" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K12" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L12" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M12" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N12" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O12" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1515,83 +1515,83 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C13" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D13" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E13" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F13" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H13" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I13" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J13" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K13" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L13" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M13" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N13" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O13" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,18 +1609,14 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1632,50 +1628,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C14" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D14" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E14" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H14" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I14" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J14" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K14" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L14" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M14" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N14" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O14" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,14 +1689,18 @@
       </c>
       <c r="T14" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1712,50 +1712,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C15" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D15" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E15" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I15" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J15" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K15" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L15" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M15" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N15" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O15" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,10 +1781,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1796,50 +1794,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C16" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D16" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E16" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F16" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H16" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I16" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J16" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K16" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M16" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O16" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1865,8 +1863,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="n">
-        <v/>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1878,50 +1878,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C17" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D17" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E17" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F17" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H17" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I17" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J17" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M17" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1929,83 +1929,83 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D18" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E18" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F18" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H18" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I18" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J18" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K18" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L18" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M18" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N18" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2013,22 +2013,24 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
@@ -2037,59 +2039,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C19" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D19" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E19" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F19" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H19" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I19" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J19" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L19" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N19" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,11 +2110,13 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2128,50 +2128,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C20" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D20" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E20" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F20" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H20" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I20" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J20" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K20" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L20" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M20" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N20" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O20" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2194,13 +2194,11 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2212,63 +2210,69 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C21" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D21" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E21" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F21" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H21" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I21" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J21" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K21" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M21" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N21" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O21" t="n">
-        <v>104</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2278,160 +2282,150 @@
       </c>
       <c r="U21" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C22" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D22" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E22" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H22" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I22" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J22" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K22" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L22" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M22" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N22" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O22" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C23" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D23" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E23" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H23" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I23" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J23" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K23" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L23" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M23" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N23" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O23" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2461,55 +2455,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C24" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D24" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E24" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F24" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H24" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I24" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J24" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K24" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L24" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M24" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N24" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O24" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2517,16 +2515,20 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U24" s="8" t="n">
         <v/>
@@ -2541,57 +2543,57 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C25" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D25" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E25" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H25" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I25" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J25" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K25" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L25" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M25" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O25" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2599,10 +2601,8 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
@@ -2611,12 +2611,14 @@
       </c>
       <c r="T25" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2627,82 +2629,82 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C26" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D26" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E26" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F26" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I26" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J26" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K26" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L26" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M26" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N26" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O26" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
+      <c r="Q26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2713,74 +2715,70 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C27" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D27" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E27" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F27" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H27" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I27" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J27" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L27" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M27" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N27" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O27" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2806,63 +2804,69 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C28" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D28" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E28" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F28" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H28" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I28" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J28" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K28" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L28" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M28" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N28" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O28" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2879,69 +2883,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D29" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E29" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F29" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H29" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I29" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J29" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K29" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L29" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M29" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N29" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O29" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P29" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>97.48</v>
+      </c>
+      <c r="P29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q29" s="6" t="n">
+        <v/>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
@@ -2950,7 +2946,7 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2967,55 +2963,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D30" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H30" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I30" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J30" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K30" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L30" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M30" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N30" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O30" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,18 +3023,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3049,57 +3049,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C31" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D31" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E31" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H31" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I31" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J31" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K31" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M31" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O31" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3140,50 +3140,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C32" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D32" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E32" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F32" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H32" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I32" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J32" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K32" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L32" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M32" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N32" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3224,50 +3224,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C33" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D33" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E33" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F33" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H33" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I33" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J33" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K33" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L33" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M33" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N33" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3275,19 +3275,19 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
@@ -3301,72 +3301,76 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D34" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E34" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F34" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H34" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I34" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J34" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K34" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L34" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M34" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N34" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3383,82 +3387,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D35" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E35" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H35" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I35" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J35" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L35" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M35" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N35" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O35" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>82.87</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3471,55 +3469,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C36" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D36" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E36" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F36" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H36" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I36" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J36" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K36" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L36" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M36" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N36" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O36" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3529,17 +3531,17 @@
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U36" s="8" t="n">
@@ -3555,57 +3557,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F37" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H37" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I37" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J37" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K37" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L37" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M37" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O37" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3613,20 +3615,16 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3639,59 +3637,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C38" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D38" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E38" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H38" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I38" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J38" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L38" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N38" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O38" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3699,8 +3693,10 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
@@ -3726,56 +3722,58 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C39" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D39" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E39" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F39" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H39" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I39" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J39" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K39" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N39" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O39" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R39" s="6" t="inlineStr">
         <is>
@@ -3784,7 +3782,7 @@
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3806,62 +3804,60 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C40" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D40" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E40" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F40" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H40" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I40" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J40" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K40" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M40" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N40" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O40" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
@@ -3888,50 +3884,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C41" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D41" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E41" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H41" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I41" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J41" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K41" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L41" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M41" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N41" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O41" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3939,18 +3935,18 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3963,74 +3959,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C42" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D42" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E42" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F42" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H42" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I42" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J42" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K42" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L42" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M42" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O42" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4043,83 +4047,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C43" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D43" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E43" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F43" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H43" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I43" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J43" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K43" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L43" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M43" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N43" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O43" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4131,74 +4127,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C44" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D44" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E44" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F44" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H44" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I44" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J44" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K44" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L44" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M44" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N44" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O44" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4220,62 +4222,62 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C45" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D45" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E45" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F45" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H45" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I45" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J45" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K45" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L45" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M45" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N45" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O45" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
       <c r="Q45" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
@@ -4297,83 +4299,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C46" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D46" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E46" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F46" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H46" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I46" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J46" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K46" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L46" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M46" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N46" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O46" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4383,55 +4381,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C47" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D47" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E47" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F47" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H47" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I47" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J47" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K47" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L47" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M47" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N47" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O47" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4442,20 +4444,16 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4467,57 +4465,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C48" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D48" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E48" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F48" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H48" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I48" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J48" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K48" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L48" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M48" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N48" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O48" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4528,78 +4526,80 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W48" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W48" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C49" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D49" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E49" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F49" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H49" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I49" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J49" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K49" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L49" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M49" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N49" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O49" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4617,18 +4617,14 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4640,50 +4636,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C50" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D50" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E50" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F50" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H50" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I50" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J50" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K50" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L50" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M50" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N50" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O50" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4691,8 +4687,10 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
@@ -4701,69 +4699,77 @@
       </c>
       <c r="T50" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
-      </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D51" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E51" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F51" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H51" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I51" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J51" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K51" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L51" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M51" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N51" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O51" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4773,28 +4779,22 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
@@ -4810,50 +4810,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C52" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D52" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E52" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F52" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H52" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I52" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J52" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K52" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L52" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M52" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N52" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O52" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4887,57 +4887,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C53" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D53" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E53" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F53" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H53" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I53" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J53" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K53" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L53" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M53" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N53" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O53" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4955,8 +4955,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4971,57 +4973,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C54" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D54" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E54" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F54" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H54" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I54" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J54" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K54" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L54" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M54" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N54" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O54" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5029,19 +5031,17 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U54" s="8" t="n">
@@ -5064,70 +5064,72 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C55" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D55" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E55" t="n">
-        <v>66.56</v>
+        <v>64.25</v>
       </c>
       <c r="F55" t="n">
-        <v>2</v>
+        <v>-2.31</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0347</v>
       </c>
       <c r="H55" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I55" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J55" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K55" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L55" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M55" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N55" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O55" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5141,69 +5143,69 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>66.44</v>
+        <v>61.38</v>
       </c>
       <c r="C56" t="n">
-        <v>66.67</v>
+        <v>61.56</v>
       </c>
       <c r="D56" t="n">
-        <v>63</v>
+        <v>59.98</v>
       </c>
       <c r="E56" t="n">
-        <v>64.25</v>
+        <v>59.98</v>
       </c>
       <c r="F56" t="n">
-        <v>-2.31</v>
+        <v>-4.27</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0347</v>
+        <v>-0.0664</v>
       </c>
       <c r="H56" t="n">
-        <v>3.67</v>
+        <v>1.58</v>
       </c>
       <c r="I56" t="n">
-        <v>59.1</v>
+        <v>59.33</v>
       </c>
       <c r="J56" t="n">
-        <v>63.42</v>
+        <v>60.29</v>
       </c>
       <c r="K56" t="n">
-        <v>64.59999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="L56" t="n">
-        <v>65.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M56" t="n">
-        <v>68.52</v>
+        <v>66.08</v>
       </c>
       <c r="N56" t="n">
-        <v>71.26000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="O56" t="n">
-        <v>70.86</v>
+        <v>70.33</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
       <c r="Q56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
@@ -5220,89 +5222,87 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>61.38</v>
+        <v>61.52</v>
       </c>
       <c r="C57" t="n">
-        <v>61.56</v>
+        <v>61.62</v>
       </c>
       <c r="D57" t="n">
-        <v>59.98</v>
+        <v>58.92</v>
       </c>
       <c r="E57" t="n">
-        <v>59.98</v>
+        <v>61.05</v>
       </c>
       <c r="F57" t="n">
-        <v>-4.27</v>
+        <v>1.07</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0664</v>
+        <v>0.0179</v>
       </c>
       <c r="H57" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="I57" t="n">
-        <v>59.33</v>
+        <v>58.4</v>
       </c>
       <c r="J57" t="n">
-        <v>60.29</v>
+        <v>58</v>
       </c>
       <c r="K57" t="n">
-        <v>62.41</v>
+        <v>59.19</v>
       </c>
       <c r="L57" t="n">
-        <v>64.54000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="M57" t="n">
-        <v>66.08</v>
+        <v>60.77</v>
       </c>
       <c r="N57" t="n">
-        <v>67.62</v>
+        <v>61.16</v>
       </c>
       <c r="O57" t="n">
-        <v>70.33</v>
+        <v>63.13</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
@@ -5311,89 +5311,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-05</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>61.52</v>
-      </c>
-      <c r="C58" t="n">
-        <v>61.62</v>
-      </c>
-      <c r="D58" t="n">
-        <v>59.45</v>
-      </c>
-      <c r="E58" t="n">
-        <v>60.31</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>0.0056</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="I58" t="n">
-        <v>58.4</v>
-      </c>
-      <c r="J58" t="n">
-        <v>58</v>
-      </c>
-      <c r="K58" t="n">
-        <v>59.19</v>
-      </c>
-      <c r="L58" t="n">
-        <v>60.37</v>
-      </c>
-      <c r="M58" t="n">
-        <v>60.77</v>
-      </c>
-      <c r="N58" t="n">
-        <v>61.16</v>
-      </c>
-      <c r="O58" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
+      <c r="X57" t="inlineStr">
         <is>
           <t>中警訊</t>
         </is>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5239,22 +5239,22 @@
         <v>61.52</v>
       </c>
       <c r="C57" t="n">
-        <v>61.62</v>
+        <v>61.72</v>
       </c>
       <c r="D57" t="n">
         <v>58.92</v>
       </c>
       <c r="E57" t="n">
-        <v>61.05</v>
+        <v>61.54</v>
       </c>
       <c r="F57" t="n">
-        <v>1.07</v>
+        <v>1.57</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0179</v>
+        <v>0.0261</v>
       </c>
       <c r="H57" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="I57" t="n">
         <v>58.4</v>
@@ -5306,14 +5306,14 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5239,22 +5239,22 @@
         <v>61.52</v>
       </c>
       <c r="C57" t="n">
-        <v>61.72</v>
+        <v>61.74</v>
       </c>
       <c r="D57" t="n">
         <v>58.92</v>
       </c>
       <c r="E57" t="n">
-        <v>61.54</v>
+        <v>61.61</v>
       </c>
       <c r="F57" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0272</v>
       </c>
       <c r="H57" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="I57" t="n">
         <v>58.4</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5239,22 +5239,22 @@
         <v>61.52</v>
       </c>
       <c r="C57" t="n">
-        <v>61.74</v>
+        <v>61.62</v>
       </c>
       <c r="D57" t="n">
         <v>58.92</v>
       </c>
       <c r="E57" t="n">
-        <v>61.61</v>
+        <v>60.67</v>
       </c>
       <c r="F57" t="n">
-        <v>1.63</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0272</v>
+        <v>0.0116</v>
       </c>
       <c r="H57" t="n">
-        <v>2.83</v>
+        <v>2.7</v>
       </c>
       <c r="I57" t="n">
         <v>58.4</v>
@@ -5295,23 +5295,105 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="C58" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="D58" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="E58" t="n">
+        <v>60.14</v>
+      </c>
+      <c r="F58" t="n">
+        <v>-0.53</v>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>-0.008699999999999999</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="n">
+        <v>56.22</v>
+      </c>
+      <c r="J58" t="n">
+        <v>58.17</v>
+      </c>
+      <c r="K58" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="L58" t="n">
+        <v>60.47</v>
+      </c>
+      <c r="M58" t="n">
+        <v>62.02</v>
+      </c>
+      <c r="N58" t="n">
+        <v>63.57</v>
+      </c>
+      <c r="O58" t="n">
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
         <is>
           <t>弱警訊</t>
         </is>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>39.37</v>
+        <v>39.88</v>
       </c>
       <c r="J2" t="n">
-        <v>41.26</v>
+        <v>41.45</v>
       </c>
       <c r="K2" t="n">
-        <v>41.63</v>
+        <v>41.76</v>
       </c>
       <c r="L2" t="n">
-        <v>42.01</v>
+        <v>42.07</v>
       </c>
       <c r="M2" t="n">
-        <v>43.14</v>
+        <v>43.01</v>
       </c>
       <c r="N2" t="n">
-        <v>44.27</v>
+        <v>43.95</v>
       </c>
       <c r="O2" t="n">
-        <v>43.9</v>
+        <v>43.64</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5330,19 +5330,19 @@
         <v>60.14</v>
       </c>
       <c r="D58" t="n">
-        <v>60.14</v>
+        <v>59.01</v>
       </c>
       <c r="E58" t="n">
-        <v>60.14</v>
+        <v>59.47</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.53</v>
+        <v>-1.2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008699999999999999</v>
+        <v>-0.0199</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="I58" t="n">
         <v>56.22</v>
@@ -5371,12 +5371,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,31 +659,33 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>39.88</v>
+        <v>40.31</v>
       </c>
       <c r="J2" t="n">
-        <v>41.45</v>
+        <v>41.61</v>
       </c>
       <c r="K2" t="n">
-        <v>41.76</v>
+        <v>41.87</v>
       </c>
       <c r="L2" t="n">
-        <v>42.07</v>
+        <v>42.13</v>
       </c>
       <c r="M2" t="n">
-        <v>43.01</v>
+        <v>42.91</v>
       </c>
       <c r="N2" t="n">
-        <v>43.95</v>
+        <v>43.68</v>
       </c>
       <c r="O2" t="n">
-        <v>43.64</v>
+        <v>43.42</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
@@ -692,11 +694,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -5330,19 +5334,19 @@
         <v>60.14</v>
       </c>
       <c r="D58" t="n">
-        <v>59.01</v>
+        <v>55.62</v>
       </c>
       <c r="E58" t="n">
-        <v>59.47</v>
+        <v>56.22</v>
       </c>
       <c r="F58" t="n">
-        <v>-1.2</v>
+        <v>-4.45</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0199</v>
+        <v>-0.07340000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>1.14</v>
+        <v>4.52</v>
       </c>
       <c r="I58" t="n">
         <v>56.22</v>
@@ -5365,15 +5369,19 @@
       <c r="O58" t="n">
         <v>64.31999999999999</v>
       </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5395,11 +5403,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5337,13 +5337,13 @@
         <v>55.62</v>
       </c>
       <c r="E58" t="n">
-        <v>56.22</v>
+        <v>56.33</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.45</v>
+        <v>-4.34</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.07340000000000001</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="H58" t="n">
         <v>4.52</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5337,13 +5337,13 @@
         <v>55.62</v>
       </c>
       <c r="E58" t="n">
-        <v>56.33</v>
+        <v>56.44</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.34</v>
+        <v>-4.23</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.07149999999999999</v>
+        <v>-0.0697</v>
       </c>
       <c r="H58" t="n">
         <v>4.52</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>1.37</v>
       </c>
       <c r="I2" t="n">
-        <v>40.31</v>
+        <v>40.81</v>
       </c>
       <c r="J2" t="n">
-        <v>41.61</v>
+        <v>41.8</v>
       </c>
       <c r="K2" t="n">
-        <v>41.87</v>
+        <v>41.99</v>
       </c>
       <c r="L2" t="n">
-        <v>42.13</v>
+        <v>42.19</v>
       </c>
       <c r="M2" t="n">
-        <v>42.91</v>
+        <v>42.78</v>
       </c>
       <c r="N2" t="n">
-        <v>43.68</v>
+        <v>43.37</v>
       </c>
       <c r="O2" t="n">
-        <v>43.42</v>
+        <v>43.17</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -713,7 +713,11 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5334,19 +5338,19 @@
         <v>60.14</v>
       </c>
       <c r="D58" t="n">
-        <v>55.62</v>
+        <v>55.5</v>
       </c>
       <c r="E58" t="n">
-        <v>56.44</v>
+        <v>57.38</v>
       </c>
       <c r="F58" t="n">
-        <v>-4.23</v>
+        <v>-3.29</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0697</v>
+        <v>-0.0542</v>
       </c>
       <c r="H58" t="n">
-        <v>4.52</v>
+        <v>4.64</v>
       </c>
       <c r="I58" t="n">
         <v>56.22</v>
@@ -5371,12 +5375,12 @@
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R58" s="6" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,63 +634,59 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>42.21</v>
+        <v>43.67</v>
       </c>
       <c r="C2" t="n">
-        <v>42.87</v>
+        <v>46.22</v>
       </c>
       <c r="D2" t="n">
-        <v>41.49</v>
+        <v>43.3</v>
       </c>
       <c r="E2" t="n">
-        <v>42.54</v>
+        <v>46.22</v>
       </c>
       <c r="F2" t="n">
-        <v>0.15</v>
+        <v>3.69</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0866</v>
       </c>
       <c r="H2" t="n">
-        <v>1.37</v>
+        <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>40.81</v>
+        <v>40.12</v>
       </c>
       <c r="J2" t="n">
-        <v>41.8</v>
+        <v>41.34</v>
       </c>
       <c r="K2" t="n">
-        <v>41.99</v>
+        <v>41.85</v>
       </c>
       <c r="L2" t="n">
-        <v>42.19</v>
+        <v>42.36</v>
       </c>
       <c r="M2" t="n">
-        <v>42.78</v>
+        <v>43.22</v>
       </c>
       <c r="N2" t="n">
-        <v>43.37</v>
+        <v>44.08</v>
       </c>
       <c r="O2" t="n">
-        <v>43.17</v>
+        <v>44.24</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -699,73 +695,73 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
-      </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C3" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D3" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E3" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F3" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H3" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I3" t="n">
-        <v>40.12</v>
+        <v>40.38</v>
       </c>
       <c r="J3" t="n">
-        <v>41.34</v>
+        <v>44.03</v>
       </c>
       <c r="K3" t="n">
-        <v>41.85</v>
+        <v>44.76</v>
       </c>
       <c r="L3" t="n">
-        <v>42.36</v>
+        <v>45.49</v>
       </c>
       <c r="M3" t="n">
-        <v>43.22</v>
+        <v>47.68</v>
       </c>
       <c r="N3" t="n">
-        <v>44.08</v>
+        <v>49.87</v>
       </c>
       <c r="O3" t="n">
-        <v>44.24</v>
+        <v>49.14</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -783,18 +779,14 @@
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -806,50 +798,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C4" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D4" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E4" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F4" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H4" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I4" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J4" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K4" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L4" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M4" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N4" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O4" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -860,14 +852,14 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U4" s="8" t="n">
@@ -881,55 +873,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C5" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D5" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E5" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H5" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I5" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J5" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K5" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L5" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M5" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N5" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O5" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,9 +936,9 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
@@ -950,70 +946,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V5" s="8" t="n">
-        <v/>
+      <c r="U5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C6" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D6" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E6" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F6" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H6" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I6" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J6" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K6" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L6" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M6" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N6" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O6" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,83 +1017,83 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V6" s="8" t="n">
+        <v/>
       </c>
       <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C7" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D7" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E7" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H7" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I7" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J7" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K7" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L7" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M7" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N7" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O7" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1107,12 +1103,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1138,50 +1134,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C8" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D8" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E8" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H8" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I8" t="n">
         <v>43.01</v>
       </c>
       <c r="J8" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K8" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L8" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M8" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N8" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O8" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,14 +1185,12 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1215,57 +1209,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C9" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D9" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E9" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F9" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H9" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I9" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J9" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K9" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L9" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M9" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N9" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O9" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1278,76 +1272,78 @@
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C10" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D10" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E10" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F10" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H10" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I10" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J10" t="n">
         <v>45.26</v>
       </c>
-      <c r="J10" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K10" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L10" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M10" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N10" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O10" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1355,83 +1351,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C11" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D11" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E11" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H11" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I11" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J11" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K11" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L11" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M11" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N11" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O11" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1439,83 +1435,83 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C12" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D12" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E12" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F12" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H12" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I12" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J12" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K12" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L12" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M12" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N12" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O12" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1533,18 +1529,14 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1556,50 +1548,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C13" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D13" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E13" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H13" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I13" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J13" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K13" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L13" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M13" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N13" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O13" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1617,14 +1609,18 @@
       </c>
       <c r="T13" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1636,50 +1632,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C14" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D14" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E14" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I14" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J14" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K14" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L14" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M14" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N14" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O14" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1705,10 +1701,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1720,50 +1714,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C15" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D15" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E15" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H15" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I15" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J15" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K15" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M15" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O15" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1789,8 +1783,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="n">
-        <v/>
+      <c r="V15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
@@ -1802,50 +1798,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C16" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E16" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F16" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H16" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I16" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J16" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L16" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M16" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N16" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O16" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,83 +1849,83 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V16" s="8" t="n">
+        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E17" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F17" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H17" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I17" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J17" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K17" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L17" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M17" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N17" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1937,22 +1933,24 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
@@ -1961,59 +1959,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C18" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D18" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E18" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F18" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H18" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I18" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K18" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L18" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N18" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2036,11 +2030,13 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2052,50 +2048,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C19" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D19" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E19" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F19" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H19" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I19" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J19" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K19" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L19" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M19" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N19" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O19" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2118,13 +2114,11 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="9" t="inlineStr">
         <is>
@@ -2136,63 +2130,69 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C20" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D20" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E20" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F20" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H20" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I20" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J20" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K20" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M20" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N20" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O20" t="n">
-        <v>104</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2202,160 +2202,150 @@
       </c>
       <c r="U20" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C21" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D21" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H21" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I21" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J21" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K21" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L21" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M21" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N21" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O21" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C22" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D22" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E22" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H22" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I22" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J22" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K22" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L22" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M22" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N22" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O22" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2385,55 +2375,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C23" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D23" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E23" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F23" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H23" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I23" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J23" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K23" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L23" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M23" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N23" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O23" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2441,16 +2435,20 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2465,57 +2463,57 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C24" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D24" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E24" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H24" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I24" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J24" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K24" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L24" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M24" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O24" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2523,10 +2521,8 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R24" s="6" t="n">
+        <v/>
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
@@ -2535,12 +2531,14 @@
       </c>
       <c r="T24" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
@@ -2551,82 +2549,82 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C25" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D25" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E25" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F25" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I25" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J25" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K25" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L25" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M25" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N25" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O25" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
+      <c r="Q25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
@@ -2637,74 +2635,70 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C26" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D26" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E26" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F26" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H26" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I26" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J26" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L26" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M26" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N26" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O26" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2730,63 +2724,69 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C27" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E27" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F27" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H27" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I27" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J27" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K27" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L27" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M27" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N27" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O27" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R27" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2803,69 +2803,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D28" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E28" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F28" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H28" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I28" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J28" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K28" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L28" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M28" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N28" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O28" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P28" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>97.48</v>
+      </c>
+      <c r="P28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q28" s="6" t="n">
+        <v/>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
@@ -2874,7 +2866,7 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2891,55 +2883,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C29" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D29" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E29" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H29" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I29" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J29" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K29" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L29" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M29" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N29" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O29" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2947,18 +2943,18 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2973,57 +2969,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C30" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D30" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E30" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H30" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I30" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J30" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K30" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M30" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O30" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3064,50 +3060,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C31" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D31" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E31" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F31" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H31" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I31" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J31" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K31" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L31" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M31" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N31" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3148,50 +3144,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C32" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D32" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E32" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F32" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H32" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I32" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J32" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K32" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L32" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M32" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N32" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3199,19 +3195,19 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="R32" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3225,72 +3221,76 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D33" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E33" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F33" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H33" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I33" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J33" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K33" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L33" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M33" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N33" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3307,82 +3307,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C34" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D34" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E34" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H34" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I34" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J34" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L34" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M34" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N34" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O34" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>82.87</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3395,55 +3389,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C35" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D35" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E35" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F35" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H35" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I35" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J35" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K35" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L35" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M35" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N35" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O35" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3453,17 +3451,17 @@
       </c>
       <c r="R35" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U35" s="8" t="n">
@@ -3479,57 +3477,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C36" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F36" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H36" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I36" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J36" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K36" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L36" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M36" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N36" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O36" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3537,20 +3535,16 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3563,59 +3557,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C37" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D37" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E37" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H37" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I37" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J37" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K37" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L37" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N37" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O37" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3623,8 +3613,10 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
@@ -3650,56 +3642,58 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C38" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D38" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E38" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H38" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I38" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J38" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K38" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M38" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N38" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O38" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R38" s="6" t="inlineStr">
         <is>
@@ -3708,7 +3702,7 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3730,62 +3724,60 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C39" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D39" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E39" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F39" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H39" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I39" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J39" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K39" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L39" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M39" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N39" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O39" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S39" s="10" t="inlineStr">
@@ -3812,50 +3804,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C40" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D40" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E40" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H40" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I40" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J40" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K40" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L40" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M40" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N40" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O40" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3863,18 +3855,18 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3887,74 +3879,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C41" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D41" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E41" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F41" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H41" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I41" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J41" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K41" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L41" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M41" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O41" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3967,83 +3967,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C42" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D42" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E42" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F42" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H42" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I42" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J42" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K42" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L42" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M42" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N42" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O42" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4055,74 +4047,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C43" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D43" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E43" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F43" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H43" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I43" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J43" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K43" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L43" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M43" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N43" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O43" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4144,62 +4142,62 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C44" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D44" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E44" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F44" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H44" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I44" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J44" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K44" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L44" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M44" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N44" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O44" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
       <c r="Q44" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
@@ -4221,83 +4219,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C45" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D45" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E45" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F45" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H45" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I45" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J45" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K45" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L45" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M45" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N45" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O45" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4307,55 +4301,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C46" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D46" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E46" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F46" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H46" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I46" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J46" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K46" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L46" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M46" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N46" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O46" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,20 +4364,16 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4391,57 +4385,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C47" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D47" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E47" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F47" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H47" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I47" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J47" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K47" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L47" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M47" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N47" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O47" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4452,78 +4446,80 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W47" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W47" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C48" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E48" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F48" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H48" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I48" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J48" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K48" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L48" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M48" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N48" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O48" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4541,18 +4537,14 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4564,50 +4556,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C49" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D49" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E49" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F49" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H49" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I49" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J49" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K49" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L49" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M49" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N49" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O49" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4615,8 +4607,10 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
@@ -4625,69 +4619,77 @@
       </c>
       <c r="T49" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
-      </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C50" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D50" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E50" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F50" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H50" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I50" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J50" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K50" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L50" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M50" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N50" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O50" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4697,28 +4699,22 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="9" t="inlineStr">
         <is>
@@ -4734,50 +4730,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C51" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D51" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E51" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F51" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H51" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I51" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J51" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K51" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L51" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M51" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N51" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O51" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4811,57 +4807,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C52" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D52" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E52" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F52" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H52" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I52" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J52" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K52" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L52" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M52" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N52" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O52" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4879,8 +4875,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4895,57 +4893,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C53" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D53" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E53" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F53" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H53" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I53" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J53" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K53" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L53" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M53" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N53" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O53" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4953,19 +4951,17 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U53" s="8" t="n">
@@ -4988,70 +4984,72 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C54" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D54" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E54" t="n">
-        <v>66.56</v>
+        <v>64.25</v>
       </c>
       <c r="F54" t="n">
-        <v>2</v>
+        <v>-2.31</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0347</v>
       </c>
       <c r="H54" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I54" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J54" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K54" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L54" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M54" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N54" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O54" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5065,69 +5063,69 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>66.44</v>
+        <v>61.38</v>
       </c>
       <c r="C55" t="n">
-        <v>66.67</v>
+        <v>61.56</v>
       </c>
       <c r="D55" t="n">
-        <v>63</v>
+        <v>59.98</v>
       </c>
       <c r="E55" t="n">
-        <v>64.25</v>
+        <v>59.98</v>
       </c>
       <c r="F55" t="n">
-        <v>-2.31</v>
+        <v>-4.27</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0347</v>
+        <v>-0.0664</v>
       </c>
       <c r="H55" t="n">
-        <v>3.67</v>
+        <v>1.58</v>
       </c>
       <c r="I55" t="n">
-        <v>59.1</v>
+        <v>59.33</v>
       </c>
       <c r="J55" t="n">
-        <v>63.42</v>
+        <v>60.29</v>
       </c>
       <c r="K55" t="n">
-        <v>64.59999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="L55" t="n">
-        <v>65.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M55" t="n">
-        <v>68.52</v>
+        <v>66.08</v>
       </c>
       <c r="N55" t="n">
-        <v>71.26000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="O55" t="n">
-        <v>70.86</v>
+        <v>70.33</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
       <c r="Q55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
@@ -5144,88 +5142,86 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>61.38</v>
+        <v>61.52</v>
       </c>
       <c r="C56" t="n">
-        <v>61.56</v>
+        <v>61.62</v>
       </c>
       <c r="D56" t="n">
-        <v>59.98</v>
+        <v>58.92</v>
       </c>
       <c r="E56" t="n">
-        <v>59.98</v>
+        <v>60.67</v>
       </c>
       <c r="F56" t="n">
-        <v>-4.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0664</v>
+        <v>0.0116</v>
       </c>
       <c r="H56" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="I56" t="n">
-        <v>59.33</v>
+        <v>58.4</v>
       </c>
       <c r="J56" t="n">
-        <v>60.29</v>
+        <v>58</v>
       </c>
       <c r="K56" t="n">
-        <v>62.41</v>
+        <v>59.19</v>
       </c>
       <c r="L56" t="n">
-        <v>64.54000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="M56" t="n">
-        <v>66.08</v>
+        <v>60.77</v>
       </c>
       <c r="N56" t="n">
-        <v>67.62</v>
+        <v>61.16</v>
       </c>
       <c r="O56" t="n">
-        <v>70.33</v>
+        <v>63.13</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5235,81 +5231,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>61.52</v>
+        <v>60.14</v>
       </c>
       <c r="C57" t="n">
-        <v>61.62</v>
+        <v>60.14</v>
       </c>
       <c r="D57" t="n">
-        <v>58.92</v>
+        <v>55.5</v>
       </c>
       <c r="E57" t="n">
-        <v>60.67</v>
+        <v>57.13</v>
       </c>
       <c r="F57" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.53</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0583</v>
       </c>
       <c r="H57" t="n">
-        <v>2.7</v>
+        <v>4.64</v>
       </c>
       <c r="I57" t="n">
-        <v>58.4</v>
+        <v>56.22</v>
       </c>
       <c r="J57" t="n">
-        <v>58</v>
+        <v>58.17</v>
       </c>
       <c r="K57" t="n">
-        <v>59.19</v>
+        <v>59.32</v>
       </c>
       <c r="L57" t="n">
-        <v>60.37</v>
+        <v>60.47</v>
       </c>
       <c r="M57" t="n">
-        <v>60.77</v>
+        <v>62.02</v>
       </c>
       <c r="N57" t="n">
-        <v>61.16</v>
+        <v>63.57</v>
       </c>
       <c r="O57" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5319,95 +5319,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-12</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="C58" t="n">
-        <v>60.14</v>
-      </c>
-      <c r="D58" t="n">
-        <v>55.5</v>
-      </c>
-      <c r="E58" t="n">
-        <v>57.38</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-3.29</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0542</v>
-      </c>
-      <c r="H58" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="I58" t="n">
-        <v>56.22</v>
-      </c>
-      <c r="J58" t="n">
-        <v>58.17</v>
-      </c>
-      <c r="K58" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="L58" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="M58" t="n">
-        <v>62.02</v>
-      </c>
-      <c r="N58" t="n">
-        <v>63.57</v>
-      </c>
-      <c r="O58" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X57" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5253,13 +5253,13 @@
         <v>55.5</v>
       </c>
       <c r="E57" t="n">
-        <v>57.13</v>
+        <v>57.31</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.53</v>
+        <v>-3.36</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0583</v>
+        <v>-0.0555</v>
       </c>
       <c r="H57" t="n">
         <v>4.64</v>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="R57" s="6" t="inlineStr">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5253,13 +5253,13 @@
         <v>55.5</v>
       </c>
       <c r="E57" t="n">
-        <v>57.31</v>
+        <v>57.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.36</v>
+        <v>-3.17</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0555</v>
+        <v>-0.0522</v>
       </c>
       <c r="H57" t="n">
         <v>4.64</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5253,13 +5253,13 @@
         <v>55.5</v>
       </c>
       <c r="E57" t="n">
-        <v>57.5</v>
+        <v>57.44</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.17</v>
+        <v>-3.23</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0522</v>
+        <v>-0.0533</v>
       </c>
       <c r="H57" t="n">
         <v>4.64</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5253,13 +5256,13 @@
         <v>55.5</v>
       </c>
       <c r="E57" t="n">
-        <v>57.44</v>
+        <v>56.99</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.23</v>
+        <v>-3.67</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0533</v>
+        <v>-0.0606</v>
       </c>
       <c r="H57" t="n">
         <v>4.64</v>
@@ -5287,39 +5290,123 @@
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="Q57" s="6" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>57.25</v>
+      </c>
+      <c r="C58" t="n">
+        <v>57.27</v>
+      </c>
+      <c r="D58" t="n">
+        <v>56.84</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="I58" t="n">
+        <v>50.86</v>
+      </c>
+      <c r="J58" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="K58" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L58" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="M58" t="n">
+        <v>59.32</v>
+      </c>
+      <c r="N58" t="n">
+        <v>61.22</v>
+      </c>
+      <c r="O58" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5337,7 +5337,7 @@
         <v>57.27</v>
       </c>
       <c r="D58" t="n">
-        <v>56.84</v>
+        <v>56.51</v>
       </c>
       <c r="E58" t="n">
         <v/>
@@ -5349,7 +5349,7 @@
         <v/>
       </c>
       <c r="H58" t="n">
-        <v>0.43</v>
+        <v>0.76</v>
       </c>
       <c r="I58" t="n">
         <v>50.86</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5331,25 +5328,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>57.25</v>
+        <v>57.01</v>
       </c>
       <c r="C58" t="n">
-        <v>57.27</v>
+        <v>58.42</v>
       </c>
       <c r="D58" t="n">
-        <v>56.51</v>
+        <v>56.97</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>57.65</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>0.66</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0116</v>
       </c>
       <c r="H58" t="n">
-        <v>0.76</v>
+        <v>1.44</v>
       </c>
       <c r="I58" t="n">
         <v>50.86</v>
@@ -5372,10 +5369,8 @@
       <c r="O58" t="n">
         <v>64.78</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5383,9 +5378,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5404,7 +5399,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5331,22 +5331,22 @@
         <v>57.01</v>
       </c>
       <c r="C58" t="n">
-        <v>58.42</v>
+        <v>58.1</v>
       </c>
       <c r="D58" t="n">
-        <v>56.97</v>
+        <v>56.74</v>
       </c>
       <c r="E58" t="n">
-        <v>57.65</v>
+        <v>57.32</v>
       </c>
       <c r="F58" t="n">
-        <v>0.66</v>
+        <v>0.33</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="I58" t="n">
         <v>50.86</v>
@@ -5378,9 +5378,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5334,19 +5334,19 @@
         <v>58.1</v>
       </c>
       <c r="D58" t="n">
-        <v>56.74</v>
+        <v>56.46</v>
       </c>
       <c r="E58" t="n">
-        <v>57.32</v>
+        <v>56.62</v>
       </c>
       <c r="F58" t="n">
-        <v>0.33</v>
+        <v>-0.37</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0057</v>
+        <v>-0.0065</v>
       </c>
       <c r="H58" t="n">
-        <v>1.36</v>
+        <v>1.65</v>
       </c>
       <c r="I58" t="n">
         <v>50.86</v>
@@ -5399,7 +5399,7 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.92</v>
       </c>
       <c r="I2" t="n">
-        <v>40.12</v>
+        <v>40.76</v>
       </c>
       <c r="J2" t="n">
-        <v>41.34</v>
+        <v>41.58</v>
       </c>
       <c r="K2" t="n">
-        <v>41.85</v>
+        <v>42.01</v>
       </c>
       <c r="L2" t="n">
-        <v>42.36</v>
+        <v>42.44</v>
       </c>
       <c r="M2" t="n">
-        <v>43.22</v>
+        <v>43.06</v>
       </c>
       <c r="N2" t="n">
-        <v>44.08</v>
+        <v>43.68</v>
       </c>
       <c r="O2" t="n">
-        <v>44.24</v>
+        <v>43.92</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5331,22 +5331,22 @@
         <v>57.01</v>
       </c>
       <c r="C58" t="n">
-        <v>58.1</v>
+        <v>57.71</v>
       </c>
       <c r="D58" t="n">
-        <v>56.46</v>
+        <v>54.17</v>
       </c>
       <c r="E58" t="n">
-        <v>56.62</v>
+        <v>54.37</v>
       </c>
       <c r="F58" t="n">
-        <v>-0.37</v>
+        <v>-2.63</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0065</v>
+        <v>-0.0461</v>
       </c>
       <c r="H58" t="n">
-        <v>1.65</v>
+        <v>3.53</v>
       </c>
       <c r="I58" t="n">
         <v>50.86</v>
@@ -5375,12 +5375,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5397,11 +5399,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-22</t>
+          <t>2025-09-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>43.67</v>
+        <v>46.14</v>
       </c>
       <c r="C2" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="D2" t="n">
-        <v>43.3</v>
+        <v>45.38</v>
       </c>
       <c r="E2" t="n">
-        <v>46.22</v>
+        <v>47.6</v>
       </c>
       <c r="F2" t="n">
-        <v>3.69</v>
+        <v>1.38</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0866</v>
+        <v>0.0298</v>
       </c>
       <c r="H2" t="n">
-        <v>2.92</v>
+        <v>2.21</v>
       </c>
       <c r="I2" t="n">
-        <v>40.76</v>
+        <v>40.38</v>
       </c>
       <c r="J2" t="n">
-        <v>41.58</v>
+        <v>44.03</v>
       </c>
       <c r="K2" t="n">
-        <v>42.01</v>
+        <v>44.76</v>
       </c>
       <c r="L2" t="n">
-        <v>42.44</v>
+        <v>45.49</v>
       </c>
       <c r="M2" t="n">
-        <v>43.06</v>
+        <v>47.68</v>
       </c>
       <c r="N2" t="n">
-        <v>43.68</v>
+        <v>49.87</v>
       </c>
       <c r="O2" t="n">
-        <v>43.92</v>
+        <v>49.14</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,18 +695,14 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -718,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C3" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D3" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E3" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F3" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H3" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I3" t="n">
-        <v>40.38</v>
+        <v>43.17</v>
       </c>
       <c r="J3" t="n">
-        <v>44.03</v>
+        <v>45.94</v>
       </c>
       <c r="K3" t="n">
-        <v>44.76</v>
+        <v>46.49</v>
       </c>
       <c r="L3" t="n">
-        <v>45.49</v>
+        <v>47.04</v>
       </c>
       <c r="M3" t="n">
-        <v>47.68</v>
+        <v>48.7</v>
       </c>
       <c r="N3" t="n">
-        <v>49.87</v>
+        <v>50.36</v>
       </c>
       <c r="O3" t="n">
-        <v>49.14</v>
+        <v>49.81</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,14 +768,14 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U3" s="8" t="n">
@@ -793,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C4" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D4" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E4" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H4" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I4" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J4" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K4" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L4" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M4" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N4" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O4" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -852,9 +852,9 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
@@ -862,70 +862,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C5" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D5" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E5" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F5" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H5" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I5" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J5" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K5" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L5" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M5" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N5" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O5" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -933,83 +933,83 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C6" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D6" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E6" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I6" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J6" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K6" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L6" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M6" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N6" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O6" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1019,12 +1019,12 @@
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1050,50 +1050,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C7" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D7" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E7" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I7" t="n">
         <v>43.01</v>
       </c>
       <c r="J7" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K7" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L7" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M7" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N7" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O7" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1101,14 +1101,12 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1127,57 +1125,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C8" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D8" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E8" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F8" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H8" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I8" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J8" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K8" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L8" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M8" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N8" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O8" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1190,76 +1188,78 @@
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V8" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C9" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D9" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E9" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F9" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H9" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I9" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J9" t="n">
         <v>45.26</v>
       </c>
-      <c r="J9" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K9" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L9" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M9" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N9" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O9" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1267,83 +1267,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V9" s="8" t="n">
+        <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C10" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D10" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E10" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H10" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I10" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J10" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K10" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L10" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M10" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N10" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O10" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1351,83 +1351,83 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U10" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C11" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D11" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E11" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F11" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H11" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I11" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J11" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K11" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L11" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M11" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N11" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O11" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1445,18 +1445,14 @@
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V11" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V11" s="8" t="n">
+        <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1468,50 +1464,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C12" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D12" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E12" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H12" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I12" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J12" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K12" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L12" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M12" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N12" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O12" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1529,14 +1525,18 @@
       </c>
       <c r="T12" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V12" s="8" t="n">
-        <v/>
+      <c r="V12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1548,50 +1548,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C13" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E13" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H13" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I13" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J13" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K13" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L13" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M13" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N13" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O13" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1617,10 +1617,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V13" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V13" s="8" t="n">
+        <v/>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1632,50 +1630,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C14" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D14" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E14" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H14" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I14" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J14" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K14" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M14" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O14" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1701,8 +1699,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V14" s="8" t="n">
-        <v/>
+      <c r="V14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
@@ -1714,50 +1714,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C15" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D15" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E15" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F15" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H15" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I15" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J15" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L15" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M15" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N15" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O15" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1765,83 +1765,83 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V15" s="8" t="n">
+        <v/>
       </c>
       <c r="W15" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C16" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D16" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E16" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F16" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H16" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I16" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J16" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K16" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L16" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M16" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N16" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,22 +1849,24 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
-      </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
@@ -1873,59 +1875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C17" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D17" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E17" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F17" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H17" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I17" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K17" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L17" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M17" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N17" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O17" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1948,11 +1946,13 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V17" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V17" s="8" t="n">
-        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1964,50 +1964,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C18" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E18" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F18" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H18" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I18" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J18" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K18" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L18" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M18" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N18" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O18" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2030,13 +2030,11 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V18" s="8" t="n">
+        <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
@@ -2048,63 +2046,69 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C19" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D19" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E19" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F19" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H19" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I19" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J19" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K19" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M19" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N19" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O19" t="n">
-        <v>104</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
+        <v>114.26</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2114,160 +2118,150 @@
       </c>
       <c r="U19" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C20" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D20" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H20" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I20" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J20" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K20" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L20" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M20" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N20" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O20" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V20" s="8" t="n">
+        <v/>
       </c>
       <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C21" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D21" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E21" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H21" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J21" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K21" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L21" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N21" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O21" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2297,55 +2291,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C22" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D22" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E22" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F22" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H22" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I22" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J22" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K22" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L22" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M22" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N22" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O22" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,16 +2351,20 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2377,57 +2379,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C23" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D23" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E23" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F23" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H23" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I23" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J23" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K23" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L23" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M23" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O23" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2435,24 +2437,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2463,81 +2465,81 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C24" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D24" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E24" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I24" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J24" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K24" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L24" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M24" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N24" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O24" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2549,74 +2551,70 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C25" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D25" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E25" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F25" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H25" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I25" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J25" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K25" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L25" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M25" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N25" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O25" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2642,63 +2640,69 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C26" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D26" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E26" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H26" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I26" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J26" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K26" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L26" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M26" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N26" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O26" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+        <v>99.73</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S26" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2715,78 +2719,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C27" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D27" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E27" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F27" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H27" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I27" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J27" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K27" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L27" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N27" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O27" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q27" s="6" t="inlineStr">
+        <v>97.48</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2803,55 +2799,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C28" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D28" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E28" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H28" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J28" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K28" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L28" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M28" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N28" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O28" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2859,18 +2859,18 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2885,57 +2885,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D29" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E29" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H29" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I29" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J29" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K29" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M29" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O29" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2976,50 +2976,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C30" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D30" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E30" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F30" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H30" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I30" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J30" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K30" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L30" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M30" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N30" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3060,50 +3060,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C31" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D31" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E31" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F31" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H31" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I31" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J31" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K31" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L31" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M31" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N31" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3111,19 +3111,19 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="R31" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
       <c r="U31" s="8" t="n">
         <v/>
       </c>
@@ -3137,72 +3137,76 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D32" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E32" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F32" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H32" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I32" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J32" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K32" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L32" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M32" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N32" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O32" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3219,82 +3223,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C33" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D33" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E33" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H33" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I33" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J33" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K33" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L33" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M33" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N33" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O33" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
+        <v>82.87</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3307,55 +3305,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C34" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D34" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E34" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F34" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H34" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I34" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J34" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K34" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L34" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M34" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N34" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O34" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3365,19 +3367,19 @@
       </c>
       <c r="R34" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="U34" s="8" t="n">
         <v/>
       </c>
@@ -3391,57 +3393,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C35" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E35" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F35" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H35" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I35" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J35" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K35" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L35" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M35" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N35" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O35" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3449,20 +3451,16 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3475,59 +3473,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C36" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D36" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E36" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H36" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I36" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J36" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K36" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L36" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N36" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O36" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3535,8 +3529,10 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
@@ -3562,56 +3558,58 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C37" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D37" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E37" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H37" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I37" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J37" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K37" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M37" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N37" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O37" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R37" s="6" t="inlineStr">
         <is>
@@ -3620,7 +3618,7 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3642,62 +3640,60 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C38" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D38" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E38" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F38" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H38" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I38" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J38" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K38" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M38" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N38" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O38" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
@@ -3724,50 +3720,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C39" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D39" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E39" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H39" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I39" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J39" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K39" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L39" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M39" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N39" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O39" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3775,18 +3771,18 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R39" s="6" t="n">
+        <v/>
       </c>
       <c r="S39" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3799,74 +3795,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C40" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D40" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E40" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H40" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I40" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J40" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K40" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L40" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M40" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N40" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O40" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>75.64</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3879,83 +3883,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C41" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D41" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E41" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F41" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H41" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I41" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J41" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K41" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L41" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M41" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N41" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O41" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3967,74 +3963,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C42" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D42" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E42" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F42" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H42" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I42" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J42" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K42" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L42" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M42" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O42" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4056,64 +4058,64 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C43" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D43" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E43" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F43" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H43" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I43" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J43" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K43" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L43" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M43" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N43" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O43" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
       <c r="Q43" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -4133,84 +4135,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C44" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D44" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E44" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F44" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H44" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I44" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J44" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K44" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L44" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M44" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N44" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O44" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
+      <c r="U44" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
@@ -4219,55 +4217,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C45" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D45" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E45" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F45" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H45" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I45" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J45" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K45" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L45" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M45" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N45" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O45" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4278,20 +4280,16 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4303,57 +4301,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C46" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D46" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E46" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F46" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H46" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I46" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J46" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K46" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L46" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M46" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N46" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O46" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4364,78 +4362,80 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C47" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D47" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E47" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F47" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H47" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I47" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J47" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K47" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L47" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M47" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N47" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O47" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4453,18 +4453,14 @@
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
@@ -4476,50 +4472,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C48" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D48" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E48" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F48" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H48" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I48" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J48" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K48" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L48" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M48" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N48" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O48" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4527,8 +4523,10 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
@@ -4537,69 +4535,77 @@
       </c>
       <c r="T48" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
-      </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C49" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D49" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E49" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F49" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H49" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I49" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J49" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K49" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L49" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M49" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N49" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O49" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4609,28 +4615,22 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="9" t="inlineStr">
         <is>
@@ -4646,50 +4646,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C50" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D50" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E50" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F50" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H50" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I50" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J50" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K50" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L50" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M50" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N50" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O50" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4723,57 +4723,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C51" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D51" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E51" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F51" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H51" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I51" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J51" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K51" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L51" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M51" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N51" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O51" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4791,8 +4791,10 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4807,57 +4809,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C52" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D52" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E52" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F52" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H52" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I52" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J52" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K52" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L52" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M52" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N52" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O52" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4865,19 +4867,17 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U52" s="8" t="n">
@@ -4900,70 +4900,72 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C53" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D53" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E53" t="n">
-        <v>66.56</v>
+        <v>64.25</v>
       </c>
       <c r="F53" t="n">
-        <v>2</v>
+        <v>-2.31</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0347</v>
       </c>
       <c r="H53" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I53" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J53" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K53" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L53" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M53" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N53" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O53" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4977,71 +4979,71 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>66.44</v>
+        <v>61.38</v>
       </c>
       <c r="C54" t="n">
-        <v>66.67</v>
+        <v>61.56</v>
       </c>
       <c r="D54" t="n">
-        <v>63</v>
+        <v>59.98</v>
       </c>
       <c r="E54" t="n">
-        <v>64.25</v>
+        <v>59.98</v>
       </c>
       <c r="F54" t="n">
-        <v>-2.31</v>
+        <v>-4.27</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0347</v>
+        <v>-0.0664</v>
       </c>
       <c r="H54" t="n">
-        <v>3.67</v>
+        <v>1.58</v>
       </c>
       <c r="I54" t="n">
-        <v>59.1</v>
+        <v>59.33</v>
       </c>
       <c r="J54" t="n">
-        <v>63.42</v>
+        <v>60.29</v>
       </c>
       <c r="K54" t="n">
-        <v>64.59999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="L54" t="n">
-        <v>65.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M54" t="n">
-        <v>68.52</v>
+        <v>66.08</v>
       </c>
       <c r="N54" t="n">
-        <v>71.26000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="O54" t="n">
-        <v>70.86</v>
+        <v>70.33</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
       <c r="Q54" s="6" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
       <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5056,89 +5058,87 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>61.38</v>
+        <v>61.52</v>
       </c>
       <c r="C55" t="n">
-        <v>61.56</v>
+        <v>61.62</v>
       </c>
       <c r="D55" t="n">
-        <v>59.98</v>
+        <v>58.92</v>
       </c>
       <c r="E55" t="n">
-        <v>59.98</v>
+        <v>60.67</v>
       </c>
       <c r="F55" t="n">
-        <v>-4.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0664</v>
+        <v>0.0116</v>
       </c>
       <c r="H55" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="I55" t="n">
-        <v>59.33</v>
+        <v>58.4</v>
       </c>
       <c r="J55" t="n">
-        <v>60.29</v>
+        <v>58</v>
       </c>
       <c r="K55" t="n">
-        <v>62.41</v>
+        <v>59.19</v>
       </c>
       <c r="L55" t="n">
-        <v>64.54000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="M55" t="n">
-        <v>66.08</v>
+        <v>60.77</v>
       </c>
       <c r="N55" t="n">
-        <v>67.62</v>
+        <v>61.16</v>
       </c>
       <c r="O55" t="n">
-        <v>70.33</v>
+        <v>63.13</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="U55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
@@ -5147,81 +5147,85 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>61.52</v>
+        <v>60.14</v>
       </c>
       <c r="C56" t="n">
-        <v>61.62</v>
+        <v>60.14</v>
       </c>
       <c r="D56" t="n">
-        <v>58.92</v>
+        <v>55.5</v>
       </c>
       <c r="E56" t="n">
-        <v>60.67</v>
+        <v>56.99</v>
       </c>
       <c r="F56" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.67</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0606</v>
       </c>
       <c r="H56" t="n">
-        <v>2.7</v>
+        <v>4.64</v>
       </c>
       <c r="I56" t="n">
-        <v>58.4</v>
+        <v>56.22</v>
       </c>
       <c r="J56" t="n">
-        <v>58</v>
+        <v>58.17</v>
       </c>
       <c r="K56" t="n">
-        <v>59.19</v>
+        <v>59.32</v>
       </c>
       <c r="L56" t="n">
-        <v>60.37</v>
+        <v>60.47</v>
       </c>
       <c r="M56" t="n">
-        <v>60.77</v>
+        <v>62.02</v>
       </c>
       <c r="N56" t="n">
-        <v>61.16</v>
+        <v>63.57</v>
       </c>
       <c r="O56" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="P56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5231,75 +5235,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>60.14</v>
+        <v>57.01</v>
       </c>
       <c r="C57" t="n">
-        <v>60.14</v>
+        <v>57.71</v>
       </c>
       <c r="D57" t="n">
-        <v>55.5</v>
+        <v>53.08</v>
       </c>
       <c r="E57" t="n">
-        <v>56.99</v>
+        <v>53.96</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.67</v>
+        <v>-3.03</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0606</v>
+        <v>-0.0533</v>
       </c>
       <c r="H57" t="n">
-        <v>4.64</v>
+        <v>4.63</v>
       </c>
       <c r="I57" t="n">
-        <v>56.22</v>
+        <v>50.86</v>
       </c>
       <c r="J57" t="n">
-        <v>58.17</v>
+        <v>51.94</v>
       </c>
       <c r="K57" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L57" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="M57" t="n">
         <v>59.32</v>
       </c>
-      <c r="L57" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="M57" t="n">
-        <v>62.02</v>
-      </c>
       <c r="N57" t="n">
-        <v>63.57</v>
+        <v>61.22</v>
       </c>
       <c r="O57" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="P57" s="6" t="inlineStr">
+        <v>64.78</v>
+      </c>
+      <c r="P57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↓</t>
@@ -5320,86 +5316,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-19</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>57.01</v>
-      </c>
-      <c r="C58" t="n">
-        <v>57.71</v>
-      </c>
-      <c r="D58" t="n">
-        <v>54.17</v>
-      </c>
-      <c r="E58" t="n">
-        <v>54.37</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.63</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0461</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.53</v>
-      </c>
-      <c r="I58" t="n">
-        <v>50.86</v>
-      </c>
-      <c r="J58" t="n">
-        <v>51.94</v>
-      </c>
-      <c r="K58" t="n">
-        <v>54.67</v>
-      </c>
-      <c r="L58" t="n">
-        <v>57.41</v>
-      </c>
-      <c r="M58" t="n">
-        <v>59.32</v>
-      </c>
-      <c r="N58" t="n">
-        <v>61.22</v>
-      </c>
-      <c r="O58" t="n">
-        <v>64.78</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -5250,19 +5250,19 @@
         <v>57.71</v>
       </c>
       <c r="D57" t="n">
-        <v>53.08</v>
+        <v>53.71</v>
       </c>
       <c r="E57" t="n">
-        <v>53.96</v>
+        <v>54</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.03</v>
+        <v>-2.99</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0533</v>
+        <v>-0.0525</v>
       </c>
       <c r="H57" t="n">
-        <v>4.63</v>
+        <v>4</v>
       </c>
       <c r="I57" t="n">
         <v>50.86</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,6 +115,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +483,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X57"/>
+  <dimension ref="A1:X58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -659,25 +662,25 @@
         <v>2.21</v>
       </c>
       <c r="I2" t="n">
-        <v>40.38</v>
+        <v>41.18</v>
       </c>
       <c r="J2" t="n">
-        <v>44.03</v>
+        <v>44.33</v>
       </c>
       <c r="K2" t="n">
-        <v>44.76</v>
+        <v>44.96</v>
       </c>
       <c r="L2" t="n">
-        <v>45.49</v>
+        <v>45.59</v>
       </c>
       <c r="M2" t="n">
-        <v>47.68</v>
+        <v>47.48</v>
       </c>
       <c r="N2" t="n">
-        <v>49.87</v>
+        <v>49.37</v>
       </c>
       <c r="O2" t="n">
-        <v>49.14</v>
+        <v>48.74</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5253,13 +5256,13 @@
         <v>53.71</v>
       </c>
       <c r="E57" t="n">
-        <v>54</v>
+        <v>53.71</v>
       </c>
       <c r="F57" t="n">
-        <v>-2.99</v>
+        <v>-3.28</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0525</v>
+        <v>-0.0576</v>
       </c>
       <c r="H57" t="n">
         <v>4</v>
@@ -5316,6 +5319,90 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B58" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="C58" t="n">
+        <v>54.28</v>
+      </c>
+      <c r="D58" t="n">
+        <v>53.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v/>
+      </c>
+      <c r="F58" t="n">
+        <v/>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v/>
+      </c>
+      <c r="H58" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="I58" t="n">
+        <v>49.72</v>
+      </c>
+      <c r="J58" t="n">
+        <v>48.72</v>
+      </c>
+      <c r="K58" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="L58" t="n">
+        <v>54.71</v>
+      </c>
+      <c r="M58" t="n">
+        <v>55.71</v>
+      </c>
+      <c r="N58" t="n">
+        <v>56.71</v>
+      </c>
+      <c r="O58" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="12" t="inlineStr">
+        <is>
+          <t>=</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W58" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -86,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -115,9 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -5327,25 +5324,25 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>54.08</v>
+        <v>54.11</v>
       </c>
       <c r="C58" t="n">
-        <v>54.28</v>
+        <v>54.6</v>
       </c>
       <c r="D58" t="n">
-        <v>53.9</v>
+        <v>53.65</v>
       </c>
       <c r="E58" t="n">
-        <v/>
+        <v>54.26</v>
       </c>
       <c r="F58" t="n">
-        <v/>
+        <v>0.54</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v/>
+        <v>0.0101</v>
       </c>
       <c r="H58" t="n">
-        <v>0.39</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="I58" t="n">
         <v>49.72</v>
@@ -5368,10 +5365,8 @@
       <c r="O58" t="n">
         <v>61.7</v>
       </c>
-      <c r="P58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="P58" s="6" t="n">
+        <v/>
       </c>
       <c r="Q58" s="6" t="n">
         <v/>
@@ -5379,9 +5374,9 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="12" t="inlineStr">
-        <is>
-          <t>=</t>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.21</v>
       </c>
       <c r="I2" t="n">
-        <v>41.18</v>
+        <v>41.35</v>
       </c>
       <c r="J2" t="n">
-        <v>44.33</v>
+        <v>44.39</v>
       </c>
       <c r="K2" t="n">
-        <v>44.96</v>
+        <v>45</v>
       </c>
       <c r="L2" t="n">
-        <v>45.59</v>
+        <v>45.61</v>
       </c>
       <c r="M2" t="n">
-        <v>47.48</v>
+        <v>47.44</v>
       </c>
       <c r="N2" t="n">
-        <v>49.37</v>
+        <v>49.27</v>
       </c>
       <c r="O2" t="n">
-        <v>48.74</v>
+        <v>48.66</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -5327,22 +5327,22 @@
         <v>54.11</v>
       </c>
       <c r="C58" t="n">
-        <v>54.6</v>
+        <v>54.44</v>
       </c>
       <c r="D58" t="n">
-        <v>53.65</v>
+        <v>53.35</v>
       </c>
       <c r="E58" t="n">
-        <v>54.26</v>
+        <v>53.95</v>
       </c>
       <c r="F58" t="n">
-        <v>0.54</v>
+        <v>0.24</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0101</v>
+        <v>0.0044</v>
       </c>
       <c r="H58" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.09</v>
       </c>
       <c r="I58" t="n">
         <v>49.72</v>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -659,25 +659,25 @@
         <v>2.21</v>
       </c>
       <c r="I2" t="n">
-        <v>41.35</v>
+        <v>43.52</v>
       </c>
       <c r="J2" t="n">
-        <v>44.39</v>
+        <v>45.21</v>
       </c>
       <c r="K2" t="n">
-        <v>45</v>
+        <v>45.55</v>
       </c>
       <c r="L2" t="n">
-        <v>45.61</v>
+        <v>45.88</v>
       </c>
       <c r="M2" t="n">
-        <v>47.44</v>
+        <v>46.9</v>
       </c>
       <c r="N2" t="n">
-        <v>49.27</v>
+        <v>47.91</v>
       </c>
       <c r="O2" t="n">
-        <v>48.66</v>
+        <v>47.57</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,8 +685,10 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
@@ -695,14 +697,16 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -5327,22 +5331,22 @@
         <v>54.11</v>
       </c>
       <c r="C58" t="n">
-        <v>54.44</v>
+        <v>54.29</v>
       </c>
       <c r="D58" t="n">
-        <v>53.35</v>
+        <v>51.15</v>
       </c>
       <c r="E58" t="n">
-        <v>53.95</v>
+        <v>51.69</v>
       </c>
       <c r="F58" t="n">
-        <v>0.24</v>
+        <v>-2.02</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0044</v>
+        <v>-0.0375</v>
       </c>
       <c r="H58" t="n">
-        <v>1.09</v>
+        <v>3.14</v>
       </c>
       <c r="I58" t="n">
         <v>49.72</v>
@@ -5371,12 +5375,14 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5393,11 +5399,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/SI_weekly.xlsx
+++ b/three_gate/analysis/SI_weekly.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X58"/>
+  <dimension ref="A1:X57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2025-09-29</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>46.14</v>
+        <v>47.9</v>
       </c>
       <c r="C2" t="n">
-        <v>47.6</v>
+        <v>49.49</v>
       </c>
       <c r="D2" t="n">
-        <v>45.38</v>
+        <v>46.74</v>
       </c>
       <c r="E2" t="n">
-        <v>47.6</v>
+        <v>46.94</v>
       </c>
       <c r="F2" t="n">
-        <v>1.38</v>
+        <v>-0.66</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0298</v>
+        <v>-0.0138</v>
       </c>
       <c r="H2" t="n">
-        <v>2.21</v>
+        <v>2.76</v>
       </c>
       <c r="I2" t="n">
-        <v>43.52</v>
+        <v>43.17</v>
       </c>
       <c r="J2" t="n">
-        <v>45.21</v>
+        <v>45.94</v>
       </c>
       <c r="K2" t="n">
-        <v>45.55</v>
+        <v>46.49</v>
       </c>
       <c r="L2" t="n">
-        <v>45.88</v>
+        <v>47.04</v>
       </c>
       <c r="M2" t="n">
-        <v>46.9</v>
+        <v>48.7</v>
       </c>
       <c r="N2" t="n">
-        <v>47.91</v>
+        <v>50.36</v>
       </c>
       <c r="O2" t="n">
-        <v>47.57</v>
+        <v>49.81</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,14 +685,12 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="inlineStr">
@@ -703,65 +701,67 @@
       <c r="U2" s="8" t="n">
         <v/>
       </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>47.9</v>
+        <v>49.34</v>
       </c>
       <c r="C3" t="n">
-        <v>49.49</v>
+        <v>53.34</v>
       </c>
       <c r="D3" t="n">
-        <v>46.74</v>
+        <v>48.53</v>
       </c>
       <c r="E3" t="n">
-        <v>46.94</v>
+        <v>49.86</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.66</v>
+        <v>2.93</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0138</v>
+        <v>0.0623</v>
       </c>
       <c r="H3" t="n">
-        <v>2.76</v>
+        <v>4.81</v>
       </c>
       <c r="I3" t="n">
-        <v>43.17</v>
+        <v>43.98</v>
       </c>
       <c r="J3" t="n">
-        <v>45.94</v>
+        <v>43.6</v>
       </c>
       <c r="K3" t="n">
-        <v>46.49</v>
+        <v>45.56</v>
       </c>
       <c r="L3" t="n">
-        <v>47.04</v>
+        <v>47.53</v>
       </c>
       <c r="M3" t="n">
-        <v>48.7</v>
+        <v>48.32</v>
       </c>
       <c r="N3" t="n">
-        <v>50.36</v>
+        <v>49.11</v>
       </c>
       <c r="O3" t="n">
-        <v>49.81</v>
+        <v>52.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -774,7 +774,7 @@
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
@@ -782,70 +782,70 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>49.34</v>
+        <v>50.42</v>
       </c>
       <c r="C4" t="n">
-        <v>53.34</v>
+        <v>51.43</v>
       </c>
       <c r="D4" t="n">
-        <v>48.53</v>
+        <v>47.22</v>
       </c>
       <c r="E4" t="n">
-        <v>49.86</v>
+        <v>48.38</v>
       </c>
       <c r="F4" t="n">
-        <v>2.93</v>
+        <v>-1.49</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0623</v>
+        <v>-0.0298</v>
       </c>
       <c r="H4" t="n">
-        <v>4.81</v>
+        <v>4.21</v>
       </c>
       <c r="I4" t="n">
-        <v>43.98</v>
+        <v>43.73</v>
       </c>
       <c r="J4" t="n">
-        <v>43.6</v>
+        <v>44.52</v>
       </c>
       <c r="K4" t="n">
-        <v>45.56</v>
+        <v>47.46</v>
       </c>
       <c r="L4" t="n">
-        <v>47.53</v>
+        <v>50.4</v>
       </c>
       <c r="M4" t="n">
-        <v>48.32</v>
+        <v>52.27</v>
       </c>
       <c r="N4" t="n">
-        <v>49.11</v>
+        <v>54.13</v>
       </c>
       <c r="O4" t="n">
-        <v>52.25</v>
+        <v>58.15</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,83 +853,83 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-27</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>50.42</v>
+        <v>47.81</v>
       </c>
       <c r="C5" t="n">
-        <v>51.43</v>
+        <v>48.68</v>
       </c>
       <c r="D5" t="n">
-        <v>47.22</v>
+        <v>45.85</v>
       </c>
       <c r="E5" t="n">
-        <v>48.38</v>
+        <v>47.99</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.49</v>
+        <v>-0.38</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0298</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="H5" t="n">
-        <v>4.21</v>
+        <v>2.83</v>
       </c>
       <c r="I5" t="n">
-        <v>43.73</v>
+        <v>43.01</v>
       </c>
       <c r="J5" t="n">
-        <v>44.52</v>
+        <v>43.69</v>
       </c>
       <c r="K5" t="n">
-        <v>47.46</v>
+        <v>46.27</v>
       </c>
       <c r="L5" t="n">
-        <v>50.4</v>
+        <v>48.85</v>
       </c>
       <c r="M5" t="n">
-        <v>52.27</v>
+        <v>50.48</v>
       </c>
       <c r="N5" t="n">
-        <v>54.13</v>
+        <v>52.11</v>
       </c>
       <c r="O5" t="n">
-        <v>58.15</v>
+        <v>55.64</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -939,12 +939,12 @@
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -970,50 +970,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-10-27</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>47.81</v>
+        <v>47.83</v>
       </c>
       <c r="C6" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="D6" t="n">
-        <v>45.85</v>
+        <v>46.81</v>
       </c>
       <c r="E6" t="n">
-        <v>47.99</v>
+        <v>48.02</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.38</v>
+        <v>0.02</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.007900000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>2.83</v>
+        <v>1.54</v>
       </c>
       <c r="I6" t="n">
         <v>43.01</v>
       </c>
       <c r="J6" t="n">
-        <v>43.69</v>
+        <v>45.52</v>
       </c>
       <c r="K6" t="n">
-        <v>46.27</v>
+        <v>46.58</v>
       </c>
       <c r="L6" t="n">
-        <v>48.85</v>
+        <v>47.63</v>
       </c>
       <c r="M6" t="n">
-        <v>50.48</v>
+        <v>49.41</v>
       </c>
       <c r="N6" t="n">
-        <v>52.11</v>
+        <v>51.19</v>
       </c>
       <c r="O6" t="n">
-        <v>55.64</v>
+        <v>51.51</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,14 +1021,12 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1047,57 +1045,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>47.83</v>
+        <v>49.5</v>
       </c>
       <c r="C7" t="n">
-        <v>48.35</v>
+        <v>54.2</v>
       </c>
       <c r="D7" t="n">
-        <v>46.81</v>
+        <v>49.5</v>
       </c>
       <c r="E7" t="n">
-        <v>48.02</v>
+        <v>50.59</v>
       </c>
       <c r="F7" t="n">
-        <v>0.02</v>
+        <v>2.57</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0005</v>
+        <v>0.0536</v>
       </c>
       <c r="H7" t="n">
-        <v>1.54</v>
+        <v>4.7</v>
       </c>
       <c r="I7" t="n">
-        <v>43.01</v>
+        <v>45.26</v>
       </c>
       <c r="J7" t="n">
-        <v>45.52</v>
+        <v>46.69</v>
       </c>
       <c r="K7" t="n">
-        <v>46.58</v>
+        <v>47.24</v>
       </c>
       <c r="L7" t="n">
-        <v>47.63</v>
+        <v>47.8</v>
       </c>
       <c r="M7" t="n">
-        <v>49.41</v>
+        <v>48.79</v>
       </c>
       <c r="N7" t="n">
-        <v>51.19</v>
+        <v>49.78</v>
       </c>
       <c r="O7" t="n">
-        <v>51.51</v>
+        <v>49.89</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1108,78 +1106,80 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V7" s="8" t="n">
-        <v/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>49.5</v>
+        <v>50.75</v>
       </c>
       <c r="C8" t="n">
-        <v>54.2</v>
+        <v>51.75</v>
       </c>
       <c r="D8" t="n">
-        <v>49.5</v>
+        <v>48.12</v>
       </c>
       <c r="E8" t="n">
-        <v>50.59</v>
+        <v>49.87</v>
       </c>
       <c r="F8" t="n">
-        <v>2.57</v>
+        <v>-0.72</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0536</v>
+        <v>-0.0142</v>
       </c>
       <c r="H8" t="n">
-        <v>4.7</v>
+        <v>3.62</v>
       </c>
       <c r="I8" t="n">
+        <v>44.8</v>
+      </c>
+      <c r="J8" t="n">
         <v>45.26</v>
       </c>
-      <c r="J8" t="n">
-        <v>46.69</v>
-      </c>
       <c r="K8" t="n">
-        <v>47.24</v>
+        <v>48.24</v>
       </c>
       <c r="L8" t="n">
-        <v>47.8</v>
+        <v>51.22</v>
       </c>
       <c r="M8" t="n">
-        <v>48.79</v>
+        <v>52.94</v>
       </c>
       <c r="N8" t="n">
-        <v>49.78</v>
+        <v>54.66</v>
       </c>
       <c r="O8" t="n">
-        <v>49.89</v>
+        <v>58.9</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,83 +1187,83 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V8" s="8" t="n">
+        <v/>
       </c>
       <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50.75</v>
+        <v>49.6</v>
       </c>
       <c r="C9" t="n">
-        <v>51.75</v>
+        <v>56.46</v>
       </c>
       <c r="D9" t="n">
-        <v>48.12</v>
+        <v>49.6</v>
       </c>
       <c r="E9" t="n">
-        <v>49.87</v>
+        <v>56.45</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.72</v>
+        <v>6.57</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0142</v>
+        <v>0.1318</v>
       </c>
       <c r="H9" t="n">
-        <v>3.62</v>
+        <v>6.86</v>
       </c>
       <c r="I9" t="n">
-        <v>44.8</v>
+        <v>44.5</v>
       </c>
       <c r="J9" t="n">
-        <v>45.26</v>
+        <v>46.22</v>
       </c>
       <c r="K9" t="n">
-        <v>48.24</v>
+        <v>48.06</v>
       </c>
       <c r="L9" t="n">
-        <v>51.22</v>
+        <v>49.91</v>
       </c>
       <c r="M9" t="n">
-        <v>52.94</v>
+        <v>51.69</v>
       </c>
       <c r="N9" t="n">
-        <v>54.66</v>
+        <v>53.47</v>
       </c>
       <c r="O9" t="n">
-        <v>58.9</v>
+        <v>55.38</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,83 +1271,83 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>49.6</v>
+        <v>56.22</v>
       </c>
       <c r="C10" t="n">
-        <v>56.46</v>
+        <v>58.9</v>
       </c>
       <c r="D10" t="n">
-        <v>49.6</v>
+        <v>56.14</v>
       </c>
       <c r="E10" t="n">
-        <v>56.45</v>
+        <v>58.42</v>
       </c>
       <c r="F10" t="n">
-        <v>6.57</v>
+        <v>1.98</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.1318</v>
+        <v>0.035</v>
       </c>
       <c r="H10" t="n">
-        <v>6.86</v>
+        <v>2.76</v>
       </c>
       <c r="I10" t="n">
-        <v>44.5</v>
+        <v>42.74</v>
       </c>
       <c r="J10" t="n">
-        <v>46.22</v>
+        <v>51.3</v>
       </c>
       <c r="K10" t="n">
-        <v>48.06</v>
+        <v>53.02</v>
       </c>
       <c r="L10" t="n">
-        <v>49.91</v>
+        <v>54.74</v>
       </c>
       <c r="M10" t="n">
-        <v>51.69</v>
+        <v>59.88</v>
       </c>
       <c r="N10" t="n">
-        <v>53.47</v>
+        <v>65.02</v>
       </c>
       <c r="O10" t="n">
-        <v>55.38</v>
+        <v>63.32</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,25 +1358,21 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="7" t="inlineStr">
+      <c r="S10" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V10" s="8" t="n">
+        <v/>
       </c>
       <c r="W10" s="9" t="inlineStr">
         <is>
@@ -1388,50 +1384,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>56.22</v>
+        <v>58.21</v>
       </c>
       <c r="C11" t="n">
-        <v>58.9</v>
+        <v>63.93</v>
       </c>
       <c r="D11" t="n">
-        <v>56.14</v>
+        <v>57.52</v>
       </c>
       <c r="E11" t="n">
-        <v>58.42</v>
+        <v>61.36</v>
       </c>
       <c r="F11" t="n">
-        <v>1.98</v>
+        <v>2.94</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.035</v>
+        <v>0.0503</v>
       </c>
       <c r="H11" t="n">
-        <v>2.76</v>
+        <v>6.41</v>
       </c>
       <c r="I11" t="n">
-        <v>42.74</v>
+        <v>53.38</v>
       </c>
       <c r="J11" t="n">
-        <v>51.3</v>
+        <v>56.11</v>
       </c>
       <c r="K11" t="n">
-        <v>53.02</v>
+        <v>57.04</v>
       </c>
       <c r="L11" t="n">
-        <v>54.74</v>
+        <v>57.97</v>
       </c>
       <c r="M11" t="n">
-        <v>59.88</v>
+        <v>59.8</v>
       </c>
       <c r="N11" t="n">
-        <v>65.02</v>
+        <v>61.63</v>
       </c>
       <c r="O11" t="n">
-        <v>63.32</v>
+        <v>61.66</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1442,21 +1438,25 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V11" s="8" t="n">
-        <v/>
+      <c r="V11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
@@ -1468,50 +1468,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>58.21</v>
+        <v>61.23</v>
       </c>
       <c r="C12" t="n">
-        <v>63.93</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="D12" t="n">
-        <v>57.52</v>
+        <v>61.23</v>
       </c>
       <c r="E12" t="n">
-        <v>61.36</v>
+        <v>66.84999999999999</v>
       </c>
       <c r="F12" t="n">
-        <v>2.94</v>
+        <v>5.48</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0503</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="H12" t="n">
-        <v>6.41</v>
+        <v>5.62</v>
       </c>
       <c r="I12" t="n">
-        <v>53.38</v>
+        <v>51.11</v>
       </c>
       <c r="J12" t="n">
-        <v>56.11</v>
+        <v>55.27</v>
       </c>
       <c r="K12" t="n">
-        <v>57.04</v>
+        <v>58.16</v>
       </c>
       <c r="L12" t="n">
-        <v>57.97</v>
+        <v>61.04</v>
       </c>
       <c r="M12" t="n">
-        <v>59.8</v>
+        <v>64.56999999999999</v>
       </c>
       <c r="N12" t="n">
-        <v>61.63</v>
+        <v>68.09</v>
       </c>
       <c r="O12" t="n">
-        <v>61.66</v>
+        <v>70.34</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,7 +1522,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="7" t="inlineStr">
+      <c r="S12" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1537,10 +1537,8 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="V12" s="8" t="n">
+        <v/>
       </c>
       <c r="W12" s="9" t="inlineStr">
         <is>
@@ -1552,50 +1550,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="C13" t="n">
-        <v>66.84999999999999</v>
+        <v>78.84</v>
       </c>
       <c r="D13" t="n">
-        <v>61.23</v>
+        <v>67</v>
       </c>
       <c r="E13" t="n">
-        <v>66.84999999999999</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.48</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.08939999999999999</v>
+        <v>0.1442</v>
       </c>
       <c r="H13" t="n">
-        <v>5.62</v>
+        <v>11.83</v>
       </c>
       <c r="I13" t="n">
-        <v>51.11</v>
+        <v>55.61</v>
       </c>
       <c r="J13" t="n">
-        <v>55.27</v>
+        <v>62.63</v>
       </c>
       <c r="K13" t="n">
-        <v>58.16</v>
+        <v>64.04000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>61.04</v>
+        <v>65.44</v>
       </c>
       <c r="M13" t="n">
-        <v>64.56999999999999</v>
+        <v>69.65000000000001</v>
       </c>
       <c r="N13" t="n">
-        <v>68.09</v>
+        <v>73.86</v>
       </c>
       <c r="O13" t="n">
-        <v>70.34</v>
+        <v>72.45999999999999</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1606,7 +1604,7 @@
       <c r="R13" s="6" t="n">
         <v/>
       </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1621,8 +1619,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V13" s="8" t="n">
-        <v/>
+      <c r="V13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W13" s="9" t="inlineStr">
         <is>
@@ -1634,50 +1634,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-12-22</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>67</v>
+        <v>79.7</v>
       </c>
       <c r="C14" t="n">
-        <v>78.84</v>
+        <v>79.7</v>
       </c>
       <c r="D14" t="n">
-        <v>67</v>
+        <v>69.86</v>
       </c>
       <c r="E14" t="n">
-        <v>76.48999999999999</v>
+        <v>70.56</v>
       </c>
       <c r="F14" t="n">
-        <v>9.640000000000001</v>
+        <v>-5.93</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.1442</v>
+        <v>-0.0775</v>
       </c>
       <c r="H14" t="n">
-        <v>11.83</v>
+        <v>9.84</v>
       </c>
       <c r="I14" t="n">
-        <v>55.61</v>
+        <v>55.17</v>
       </c>
       <c r="J14" t="n">
-        <v>62.63</v>
+        <v>66.43000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>64.04000000000001</v>
+        <v>70.56999999999999</v>
       </c>
       <c r="L14" t="n">
-        <v>65.44</v>
+        <v>74.7</v>
       </c>
       <c r="M14" t="n">
-        <v>69.65000000000001</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="N14" t="n">
-        <v>73.86</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="O14" t="n">
-        <v>72.45999999999999</v>
+        <v>90.67</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1685,83 +1685,83 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V14" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V14" s="8" t="n">
+        <v/>
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-12-29</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>79.7</v>
+        <v>74.18000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>79.7</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>69.86</v>
+        <v>73.17</v>
       </c>
       <c r="E15" t="n">
-        <v>70.56</v>
+        <v>78.88</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.93</v>
+        <v>8.33</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0775</v>
+        <v>0.118</v>
       </c>
       <c r="H15" t="n">
-        <v>9.84</v>
+        <v>7.74</v>
       </c>
       <c r="I15" t="n">
-        <v>55.17</v>
+        <v>60.01</v>
       </c>
       <c r="J15" t="n">
-        <v>66.43000000000001</v>
+        <v>58.6</v>
       </c>
       <c r="K15" t="n">
-        <v>70.56999999999999</v>
+        <v>65.63</v>
       </c>
       <c r="L15" t="n">
-        <v>74.7</v>
+        <v>72.67</v>
       </c>
       <c r="M15" t="n">
-        <v>82.40000000000001</v>
+        <v>75.48</v>
       </c>
       <c r="N15" t="n">
-        <v>90.09999999999999</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="O15" t="n">
-        <v>90.67</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,22 +1769,24 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
-      </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
@@ -1793,59 +1795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-01-05</t>
+          <t>2026-01-12</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>74.18000000000001</v>
+        <v>82</v>
       </c>
       <c r="C16" t="n">
-        <v>80.90000000000001</v>
+        <v>93</v>
       </c>
       <c r="D16" t="n">
-        <v>73.17</v>
+        <v>82</v>
       </c>
       <c r="E16" t="n">
-        <v>78.88</v>
+        <v>88.09</v>
       </c>
       <c r="F16" t="n">
-        <v>8.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.118</v>
+        <v>0.1167</v>
       </c>
       <c r="H16" t="n">
-        <v>7.74</v>
+        <v>11</v>
       </c>
       <c r="I16" t="n">
-        <v>60.01</v>
+        <v>65.43000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>58.6</v>
+        <v>72.06999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>65.63</v>
+        <v>75.02</v>
       </c>
       <c r="L16" t="n">
-        <v>72.67</v>
+        <v>77.95999999999999</v>
       </c>
       <c r="M16" t="n">
-        <v>75.48</v>
+        <v>82.75</v>
       </c>
       <c r="N16" t="n">
-        <v>78.29000000000001</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>89.54000000000001</v>
+        <v>88.64</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1856,7 +1854,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1868,11 +1866,13 @@
       </c>
       <c r="U16" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V16" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V16" s="8" t="n">
-        <v/>
       </c>
       <c r="W16" s="9" t="inlineStr">
         <is>
@@ -1884,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01-12</t>
+          <t>2026-01-19</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>82</v>
+        <v>92.31999999999999</v>
       </c>
       <c r="C17" t="n">
-        <v>93</v>
+        <v>102.93</v>
       </c>
       <c r="D17" t="n">
-        <v>82</v>
+        <v>91.59</v>
       </c>
       <c r="E17" t="n">
-        <v>88.09</v>
+        <v>100.93</v>
       </c>
       <c r="F17" t="n">
-        <v>9.210000000000001</v>
+        <v>12.83</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.1167</v>
+        <v>0.1457</v>
       </c>
       <c r="H17" t="n">
-        <v>11</v>
+        <v>11.34</v>
       </c>
       <c r="I17" t="n">
-        <v>65.43000000000001</v>
+        <v>71</v>
       </c>
       <c r="J17" t="n">
-        <v>72.06999999999999</v>
+        <v>77.39</v>
       </c>
       <c r="K17" t="n">
-        <v>75.02</v>
+        <v>82.59</v>
       </c>
       <c r="L17" t="n">
-        <v>77.95999999999999</v>
+        <v>87.8</v>
       </c>
       <c r="M17" t="n">
-        <v>82.75</v>
+        <v>93.59</v>
       </c>
       <c r="N17" t="n">
-        <v>87.54000000000001</v>
+        <v>99.39</v>
       </c>
       <c r="O17" t="n">
-        <v>88.64</v>
+        <v>104</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1938,7 +1938,7 @@
       <c r="R17" s="6" t="n">
         <v/>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1950,13 +1950,11 @@
       </c>
       <c r="U17" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V17" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="V17" s="8" t="n">
+        <v/>
       </c>
       <c r="W17" s="9" t="inlineStr">
         <is>
@@ -1968,63 +1966,69 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01-19</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>92.31999999999999</v>
+        <v>105.04</v>
       </c>
       <c r="C18" t="n">
-        <v>102.93</v>
+        <v>121.3</v>
       </c>
       <c r="D18" t="n">
-        <v>91.59</v>
+        <v>76.03</v>
       </c>
       <c r="E18" t="n">
-        <v>100.93</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="F18" t="n">
-        <v>12.83</v>
+        <v>-22.64</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.1457</v>
+        <v>-0.2243</v>
       </c>
       <c r="H18" t="n">
-        <v>11.34</v>
+        <v>45.28</v>
       </c>
       <c r="I18" t="n">
-        <v>71</v>
+        <v>80.25</v>
       </c>
       <c r="J18" t="n">
-        <v>77.39</v>
+        <v>91.42</v>
       </c>
       <c r="K18" t="n">
-        <v>82.59</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L18" t="n">
-        <v>87.8</v>
+        <v>99.09</v>
       </c>
       <c r="M18" t="n">
-        <v>93.59</v>
+        <v>106.59</v>
       </c>
       <c r="N18" t="n">
-        <v>99.39</v>
+        <v>114.09</v>
       </c>
       <c r="O18" t="n">
-        <v>104</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
+        <v>114.26</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S18" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2034,160 +2038,150 @@
       </c>
       <c r="U18" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr"/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>105.04</v>
+        <v>81</v>
       </c>
       <c r="C19" t="n">
-        <v>121.3</v>
+        <v>90.97</v>
       </c>
       <c r="D19" t="n">
-        <v>76.03</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>78.29000000000001</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="F19" t="n">
-        <v>-22.64</v>
+        <v>-1.56</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.2243</v>
+        <v>-0.0199</v>
       </c>
       <c r="H19" t="n">
-        <v>45.28</v>
+        <v>22.26</v>
       </c>
       <c r="I19" t="n">
-        <v>80.25</v>
+        <v>30.75</v>
       </c>
       <c r="J19" t="n">
-        <v>91.42</v>
+        <v>22.83</v>
       </c>
       <c r="K19" t="n">
-        <v>95.26000000000001</v>
+        <v>55.65</v>
       </c>
       <c r="L19" t="n">
-        <v>99.09</v>
+        <v>88.48</v>
       </c>
       <c r="M19" t="n">
-        <v>106.59</v>
+        <v>100.93</v>
       </c>
       <c r="N19" t="n">
-        <v>114.09</v>
+        <v>113.38</v>
       </c>
       <c r="O19" t="n">
-        <v>114.26</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>166.58</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V19" s="8" t="n">
+        <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>81</v>
+        <v>80.5</v>
       </c>
       <c r="C20" t="n">
-        <v>90.97</v>
+        <v>84.47</v>
       </c>
       <c r="D20" t="n">
-        <v>68.70999999999999</v>
+        <v>74.83</v>
       </c>
       <c r="E20" t="n">
-        <v>76.73999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.56</v>
+        <v>1.12</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0199</v>
+        <v>0.0145</v>
       </c>
       <c r="H20" t="n">
-        <v>22.26</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>30.75</v>
+        <v>46.44</v>
       </c>
       <c r="J20" t="n">
-        <v>22.83</v>
+        <v>52.92</v>
       </c>
       <c r="K20" t="n">
-        <v>55.65</v>
+        <v>65.59999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>88.48</v>
+        <v>78.29000000000001</v>
       </c>
       <c r="M20" t="n">
-        <v>100.93</v>
+        <v>87.87</v>
       </c>
       <c r="N20" t="n">
-        <v>113.38</v>
+        <v>97.45</v>
       </c>
       <c r="O20" t="n">
-        <v>166.58</v>
+        <v>113.24</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2198,7 +2192,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -2217,55 +2211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02-09</t>
+          <t>2026-02-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>80.5</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C21" t="n">
-        <v>84.47</v>
+        <v>84.42</v>
       </c>
       <c r="D21" t="n">
-        <v>74.83</v>
+        <v>72</v>
       </c>
       <c r="E21" t="n">
-        <v>77.84999999999999</v>
+        <v>82.28</v>
       </c>
       <c r="F21" t="n">
-        <v>1.12</v>
+        <v>4.43</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0145</v>
+        <v>0.0569</v>
       </c>
       <c r="H21" t="n">
-        <v>9.640000000000001</v>
+        <v>12.42</v>
       </c>
       <c r="I21" t="n">
-        <v>46.44</v>
+        <v>65.19</v>
       </c>
       <c r="J21" t="n">
-        <v>52.92</v>
+        <v>67.31</v>
       </c>
       <c r="K21" t="n">
-        <v>65.59999999999999</v>
+        <v>73.03</v>
       </c>
       <c r="L21" t="n">
-        <v>78.29000000000001</v>
+        <v>78.75</v>
       </c>
       <c r="M21" t="n">
-        <v>87.87</v>
+        <v>82.67</v>
       </c>
       <c r="N21" t="n">
-        <v>97.45</v>
+        <v>86.59</v>
       </c>
       <c r="O21" t="n">
-        <v>113.24</v>
+        <v>94.11</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,16 +2271,20 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2297,57 +2299,57 @@
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-02-16</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>75.34999999999999</v>
+        <v>86.5</v>
       </c>
       <c r="C22" t="n">
-        <v>84.42</v>
+        <v>93.88</v>
       </c>
       <c r="D22" t="n">
-        <v>72</v>
+        <v>84.98</v>
       </c>
       <c r="E22" t="n">
-        <v>82.28</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="F22" t="n">
-        <v>4.43</v>
+        <v>10.4</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0569</v>
+        <v>0.1264</v>
       </c>
       <c r="H22" t="n">
-        <v>12.42</v>
+        <v>8.9</v>
       </c>
       <c r="I22" t="n">
-        <v>65.19</v>
+        <v>59.58</v>
       </c>
       <c r="J22" t="n">
-        <v>67.31</v>
+        <v>71.91</v>
       </c>
       <c r="K22" t="n">
-        <v>73.03</v>
+        <v>76.08</v>
       </c>
       <c r="L22" t="n">
-        <v>78.75</v>
+        <v>80.25</v>
       </c>
       <c r="M22" t="n">
-        <v>82.67</v>
+        <v>88.48999999999999</v>
       </c>
       <c r="N22" t="n">
-        <v>86.59</v>
+        <v>96.73999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>94.11</v>
+        <v>96.83</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2355,24 +2357,24 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
@@ -2383,81 +2385,81 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-02-23</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>86.5</v>
+        <v>95.86</v>
       </c>
       <c r="C23" t="n">
-        <v>93.88</v>
+        <v>95.86</v>
       </c>
       <c r="D23" t="n">
-        <v>84.98</v>
+        <v>79</v>
       </c>
       <c r="E23" t="n">
-        <v>92.68000000000001</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="F23" t="n">
-        <v>10.4</v>
+        <v>-8.869999999999999</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.1264</v>
+        <v>-0.09569999999999999</v>
       </c>
       <c r="H23" t="n">
-        <v>8.9</v>
+        <v>16.86</v>
       </c>
       <c r="I23" t="n">
-        <v>59.58</v>
+        <v>76.08</v>
       </c>
       <c r="J23" t="n">
-        <v>71.91</v>
+        <v>85.41</v>
       </c>
       <c r="K23" t="n">
-        <v>76.08</v>
+        <v>88.23</v>
       </c>
       <c r="L23" t="n">
-        <v>80.25</v>
+        <v>91.06</v>
       </c>
       <c r="M23" t="n">
-        <v>88.48999999999999</v>
+        <v>97.13</v>
       </c>
       <c r="N23" t="n">
-        <v>96.73999999999999</v>
+        <v>103.21</v>
       </c>
       <c r="O23" t="n">
-        <v>96.83</v>
+        <v>102.78</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2469,74 +2471,70 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-09</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>95.86</v>
+        <v>82.5</v>
       </c>
       <c r="C24" t="n">
-        <v>95.86</v>
+        <v>89.59</v>
       </c>
       <c r="D24" t="n">
-        <v>79</v>
+        <v>79.45</v>
       </c>
       <c r="E24" t="n">
-        <v>83.81999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="F24" t="n">
-        <v>-8.869999999999999</v>
+        <v>-2.9</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.09569999999999999</v>
+        <v>-0.0346</v>
       </c>
       <c r="H24" t="n">
-        <v>16.86</v>
+        <v>10.14</v>
       </c>
       <c r="I24" t="n">
-        <v>76.08</v>
+        <v>62.14</v>
       </c>
       <c r="J24" t="n">
-        <v>85.41</v>
+        <v>65.15000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>88.23</v>
+        <v>75.39</v>
       </c>
       <c r="L24" t="n">
-        <v>91.06</v>
+        <v>85.62</v>
       </c>
       <c r="M24" t="n">
-        <v>97.13</v>
+        <v>92.25</v>
       </c>
       <c r="N24" t="n">
-        <v>103.21</v>
+        <v>98.87</v>
       </c>
       <c r="O24" t="n">
-        <v>102.78</v>
+        <v>112.72</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2562,63 +2560,69 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>82.5</v>
+        <v>79</v>
       </c>
       <c r="C25" t="n">
-        <v>89.59</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="D25" t="n">
-        <v>79.45</v>
+        <v>67</v>
       </c>
       <c r="E25" t="n">
-        <v>80.91</v>
+        <v>69.36</v>
       </c>
       <c r="F25" t="n">
-        <v>-2.9</v>
+        <v>-11.55</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0346</v>
+        <v>-0.1428</v>
       </c>
       <c r="H25" t="n">
-        <v>10.14</v>
+        <v>15.24</v>
       </c>
       <c r="I25" t="n">
-        <v>62.14</v>
+        <v>69.31</v>
       </c>
       <c r="J25" t="n">
-        <v>65.15000000000001</v>
+        <v>68.97</v>
       </c>
       <c r="K25" t="n">
-        <v>75.39</v>
+        <v>75.84</v>
       </c>
       <c r="L25" t="n">
-        <v>85.62</v>
+        <v>82.72</v>
       </c>
       <c r="M25" t="n">
-        <v>92.25</v>
+        <v>85.98</v>
       </c>
       <c r="N25" t="n">
-        <v>98.87</v>
+        <v>89.25</v>
       </c>
       <c r="O25" t="n">
-        <v>112.72</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+        <v>99.73</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2635,78 +2639,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>79</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="C26" t="n">
-        <v>82.23999999999999</v>
+        <v>73.17</v>
       </c>
       <c r="D26" t="n">
-        <v>67</v>
+        <v>61.09</v>
       </c>
       <c r="E26" t="n">
-        <v>69.36</v>
+        <v>69.54000000000001</v>
       </c>
       <c r="F26" t="n">
-        <v>-11.55</v>
+        <v>0.18</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.1428</v>
+        <v>0.0027</v>
       </c>
       <c r="H26" t="n">
-        <v>15.24</v>
+        <v>12.08</v>
       </c>
       <c r="I26" t="n">
-        <v>69.31</v>
+        <v>51.76</v>
       </c>
       <c r="J26" t="n">
-        <v>68.97</v>
+        <v>51.49</v>
       </c>
       <c r="K26" t="n">
-        <v>75.84</v>
+        <v>61.74</v>
       </c>
       <c r="L26" t="n">
-        <v>82.72</v>
+        <v>71.98999999999999</v>
       </c>
       <c r="M26" t="n">
-        <v>85.98</v>
+        <v>76.98</v>
       </c>
       <c r="N26" t="n">
-        <v>89.25</v>
+        <v>81.97</v>
       </c>
       <c r="O26" t="n">
-        <v>99.73</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>97.48</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2723,55 +2719,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>64.73999999999999</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="C27" t="n">
-        <v>73.17</v>
+        <v>75.87</v>
       </c>
       <c r="D27" t="n">
-        <v>61.09</v>
+        <v>67.81999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>69.54000000000001</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="F27" t="n">
-        <v>0.18</v>
+        <v>3.19</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0027</v>
+        <v>0.0459</v>
       </c>
       <c r="H27" t="n">
-        <v>12.08</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>51.76</v>
+        <v>49.01</v>
       </c>
       <c r="J27" t="n">
-        <v>51.49</v>
+        <v>58.67</v>
       </c>
       <c r="K27" t="n">
-        <v>61.74</v>
+        <v>63.5</v>
       </c>
       <c r="L27" t="n">
-        <v>71.98999999999999</v>
+        <v>68.34</v>
       </c>
       <c r="M27" t="n">
-        <v>76.98</v>
+        <v>75.58</v>
       </c>
       <c r="N27" t="n">
-        <v>81.97</v>
+        <v>82.83</v>
       </c>
       <c r="O27" t="n">
-        <v>97.48</v>
+        <v>85.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2779,18 +2779,18 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R27" s="6" t="n">
+        <v/>
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2805,57 +2805,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-03-30</t>
+          <t>2026-04-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>67.90000000000001</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="C28" t="n">
-        <v>75.87</v>
+        <v>77.45</v>
       </c>
       <c r="D28" t="n">
-        <v>67.81999999999999</v>
+        <v>70</v>
       </c>
       <c r="E28" t="n">
-        <v>72.73999999999999</v>
+        <v>76.31999999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>3.19</v>
+        <v>3.59</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0459</v>
+        <v>0.0493</v>
       </c>
       <c r="H28" t="n">
-        <v>8.050000000000001</v>
+        <v>7.45</v>
       </c>
       <c r="I28" t="n">
-        <v>49.01</v>
+        <v>59.77</v>
       </c>
       <c r="J28" t="n">
-        <v>58.67</v>
+        <v>65.13</v>
       </c>
       <c r="K28" t="n">
-        <v>63.5</v>
+        <v>68.70999999999999</v>
       </c>
       <c r="L28" t="n">
-        <v>68.34</v>
+        <v>72.29000000000001</v>
       </c>
       <c r="M28" t="n">
-        <v>75.58</v>
+        <v>76.76000000000001</v>
       </c>
       <c r="N28" t="n">
-        <v>82.83</v>
+        <v>81.23</v>
       </c>
       <c r="O28" t="n">
-        <v>85.25</v>
+        <v>83.91</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2866,7 +2866,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2896,50 +2896,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-04-06</t>
+          <t>2026-04-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>71.84999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="C29" t="n">
-        <v>77.45</v>
+        <v>82.83</v>
       </c>
       <c r="D29" t="n">
-        <v>70</v>
+        <v>72.79000000000001</v>
       </c>
       <c r="E29" t="n">
-        <v>76.31999999999999</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>3.59</v>
+        <v>5.41</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0493</v>
+        <v>0.0709</v>
       </c>
       <c r="H29" t="n">
-        <v>7.45</v>
+        <v>10.04</v>
       </c>
       <c r="I29" t="n">
-        <v>59.77</v>
+        <v>62.55</v>
       </c>
       <c r="J29" t="n">
-        <v>65.13</v>
+        <v>70.17</v>
       </c>
       <c r="K29" t="n">
-        <v>68.70999999999999</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="L29" t="n">
-        <v>72.29000000000001</v>
+        <v>75.02</v>
       </c>
       <c r="M29" t="n">
-        <v>76.76000000000001</v>
+        <v>80.05</v>
       </c>
       <c r="N29" t="n">
-        <v>81.23</v>
+        <v>85.06999999999999</v>
       </c>
       <c r="O29" t="n">
-        <v>83.91</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2950,7 +2950,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2980,50 +2980,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-04-13</t>
+          <t>2026-04-20</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>72.8</v>
+        <v>79.53</v>
       </c>
       <c r="C30" t="n">
-        <v>82.83</v>
+        <v>79.95</v>
       </c>
       <c r="D30" t="n">
-        <v>72.79000000000001</v>
+        <v>75.45999999999999</v>
       </c>
       <c r="E30" t="n">
-        <v>81.73999999999999</v>
+        <v>76.38</v>
       </c>
       <c r="F30" t="n">
-        <v>5.41</v>
+        <v>-5.35</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0709</v>
+        <v>-0.0655</v>
       </c>
       <c r="H30" t="n">
-        <v>10.04</v>
+        <v>4.49</v>
       </c>
       <c r="I30" t="n">
-        <v>62.55</v>
+        <v>62.76</v>
       </c>
       <c r="J30" t="n">
-        <v>70.17</v>
+        <v>73.67</v>
       </c>
       <c r="K30" t="n">
-        <v>72.59999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L30" t="n">
-        <v>75.02</v>
+        <v>79.78</v>
       </c>
       <c r="M30" t="n">
-        <v>80.05</v>
+        <v>86.76000000000001</v>
       </c>
       <c r="N30" t="n">
-        <v>85.06999999999999</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="O30" t="n">
-        <v>84.90000000000001</v>
+        <v>92.87</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3031,18 +3031,18 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3057,72 +3057,76 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-04-20</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>79.53</v>
+        <v>75.26000000000001</v>
       </c>
       <c r="C31" t="n">
-        <v>79.95</v>
+        <v>76.88</v>
       </c>
       <c r="D31" t="n">
-        <v>75.45999999999999</v>
+        <v>70.89</v>
       </c>
       <c r="E31" t="n">
-        <v>76.38</v>
+        <v>75.95</v>
       </c>
       <c r="F31" t="n">
-        <v>-5.35</v>
+        <v>-0.43</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0655</v>
+        <v>-0.0057</v>
       </c>
       <c r="H31" t="n">
-        <v>4.49</v>
+        <v>5.99</v>
       </c>
       <c r="I31" t="n">
-        <v>62.76</v>
+        <v>70.98</v>
       </c>
       <c r="J31" t="n">
-        <v>73.67</v>
+        <v>71.23</v>
       </c>
       <c r="K31" t="n">
-        <v>76.72</v>
+        <v>74.14</v>
       </c>
       <c r="L31" t="n">
-        <v>79.78</v>
+        <v>77.05</v>
       </c>
       <c r="M31" t="n">
-        <v>86.76000000000001</v>
+        <v>78.63</v>
       </c>
       <c r="N31" t="n">
-        <v>93.73999999999999</v>
+        <v>80.20999999999999</v>
       </c>
       <c r="O31" t="n">
-        <v>92.87</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
+        <v>84.44</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R31" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3139,69 +3143,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>75.26000000000001</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="C32" t="n">
-        <v>76.88</v>
+        <v>82.18000000000001</v>
       </c>
       <c r="D32" t="n">
-        <v>70.89</v>
+        <v>72.5</v>
       </c>
       <c r="E32" t="n">
-        <v>75.95</v>
+        <v>80.39</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.43</v>
+        <v>4.44</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0057</v>
+        <v>0.0585</v>
       </c>
       <c r="H32" t="n">
-        <v>5.99</v>
+        <v>9.68</v>
       </c>
       <c r="I32" t="n">
-        <v>70.98</v>
+        <v>64.89</v>
       </c>
       <c r="J32" t="n">
-        <v>71.23</v>
+        <v>70.98999999999999</v>
       </c>
       <c r="K32" t="n">
-        <v>74.14</v>
+        <v>72.95</v>
       </c>
       <c r="L32" t="n">
-        <v>77.05</v>
+        <v>74.92</v>
       </c>
       <c r="M32" t="n">
-        <v>78.63</v>
+        <v>78.95</v>
       </c>
       <c r="N32" t="n">
-        <v>80.20999999999999</v>
+        <v>82.98</v>
       </c>
       <c r="O32" t="n">
-        <v>84.44</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>82.87</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
       </c>
       <c r="R32" s="6" t="inlineStr">
         <is>
@@ -3210,11 +3206,13 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3227,55 +3225,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>75.40000000000001</v>
+        <v>85.61</v>
       </c>
       <c r="C33" t="n">
-        <v>82.18000000000001</v>
+        <v>88.89</v>
       </c>
       <c r="D33" t="n">
-        <v>72.5</v>
+        <v>76</v>
       </c>
       <c r="E33" t="n">
-        <v>80.39</v>
+        <v>77.16</v>
       </c>
       <c r="F33" t="n">
-        <v>4.44</v>
+        <v>-3.23</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0585</v>
+        <v>-0.0402</v>
       </c>
       <c r="H33" t="n">
-        <v>9.68</v>
+        <v>12.88</v>
       </c>
       <c r="I33" t="n">
-        <v>64.89</v>
+        <v>62.82</v>
       </c>
       <c r="J33" t="n">
-        <v>70.98999999999999</v>
+        <v>72.25</v>
       </c>
       <c r="K33" t="n">
-        <v>72.95</v>
+        <v>75.56</v>
       </c>
       <c r="L33" t="n">
-        <v>74.92</v>
+        <v>78.87</v>
       </c>
       <c r="M33" t="n">
-        <v>78.95</v>
+        <v>85.23</v>
       </c>
       <c r="N33" t="n">
-        <v>82.98</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="O33" t="n">
-        <v>82.87</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3285,17 +3287,17 @@
       </c>
       <c r="R33" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="U33" s="8" t="n">
@@ -3311,57 +3313,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>85.61</v>
+        <v>75.34999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>88.89</v>
+        <v>78.45999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>76</v>
+        <v>73.79000000000001</v>
       </c>
       <c r="E34" t="n">
-        <v>77.16</v>
+        <v>75.89</v>
       </c>
       <c r="F34" t="n">
-        <v>-3.23</v>
+        <v>-1.27</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0402</v>
+        <v>-0.0164</v>
       </c>
       <c r="H34" t="n">
-        <v>12.88</v>
+        <v>4.67</v>
       </c>
       <c r="I34" t="n">
-        <v>62.82</v>
+        <v>63.12</v>
       </c>
       <c r="J34" t="n">
-        <v>72.25</v>
+        <v>61.64</v>
       </c>
       <c r="K34" t="n">
-        <v>75.56</v>
+        <v>70.72</v>
       </c>
       <c r="L34" t="n">
-        <v>78.87</v>
+        <v>79.8</v>
       </c>
       <c r="M34" t="n">
-        <v>85.23</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="N34" t="n">
-        <v>91.59999999999999</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="O34" t="n">
-        <v>91.84999999999999</v>
+        <v>101.77</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3369,20 +3371,16 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3395,59 +3393,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>75.34999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="C35" t="n">
-        <v>78.45999999999999</v>
+        <v>77.5</v>
       </c>
       <c r="D35" t="n">
-        <v>73.79000000000001</v>
+        <v>71.97</v>
       </c>
       <c r="E35" t="n">
-        <v>75.89</v>
+        <v>75.62</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.27</v>
+        <v>-0.28</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0164</v>
+        <v>-0.0036</v>
       </c>
       <c r="H35" t="n">
-        <v>4.67</v>
+        <v>5.53</v>
       </c>
       <c r="I35" t="n">
-        <v>63.12</v>
+        <v>69.12</v>
       </c>
       <c r="J35" t="n">
-        <v>61.64</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="K35" t="n">
-        <v>70.72</v>
+        <v>73.56</v>
       </c>
       <c r="L35" t="n">
-        <v>79.8</v>
+        <v>76.01000000000001</v>
       </c>
       <c r="M35" t="n">
-        <v>83.59999999999999</v>
+        <v>78.23</v>
       </c>
       <c r="N35" t="n">
-        <v>87.40000000000001</v>
+        <v>80.45</v>
       </c>
       <c r="O35" t="n">
-        <v>101.77</v>
+        <v>83.14</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3455,10 +3449,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
         <is>
           <t>↓C</t>
         </is>
@@ -3482,65 +3478,67 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-05-25</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>77.5</v>
+        <v>74.38</v>
       </c>
       <c r="C36" t="n">
-        <v>77.5</v>
+        <v>76.03</v>
       </c>
       <c r="D36" t="n">
-        <v>71.97</v>
+        <v>68.65000000000001</v>
       </c>
       <c r="E36" t="n">
-        <v>75.62</v>
+        <v>68.94</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.28</v>
+        <v>-6.67</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0036</v>
+        <v>-0.0882</v>
       </c>
       <c r="H36" t="n">
-        <v>5.53</v>
+        <v>7.38</v>
       </c>
       <c r="I36" t="n">
-        <v>69.12</v>
+        <v>66.44</v>
       </c>
       <c r="J36" t="n">
-        <v>71.09999999999999</v>
+        <v>70.52</v>
       </c>
       <c r="K36" t="n">
-        <v>73.56</v>
+        <v>72.84999999999999</v>
       </c>
       <c r="L36" t="n">
-        <v>76.01000000000001</v>
+        <v>75.18000000000001</v>
       </c>
       <c r="M36" t="n">
-        <v>78.23</v>
+        <v>78.38</v>
       </c>
       <c r="N36" t="n">
-        <v>80.45</v>
+        <v>81.59</v>
       </c>
       <c r="O36" t="n">
-        <v>83.14</v>
+        <v>83.04000000000001</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R36" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3562,65 +3560,63 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>74.38</v>
+        <v>67.45</v>
       </c>
       <c r="C37" t="n">
-        <v>76.03</v>
+        <v>68.81999999999999</v>
       </c>
       <c r="D37" t="n">
-        <v>68.65000000000001</v>
+        <v>63.74</v>
       </c>
       <c r="E37" t="n">
-        <v>68.94</v>
+        <v>67.86</v>
       </c>
       <c r="F37" t="n">
-        <v>-6.67</v>
+        <v>-1.08</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0882</v>
+        <v>-0.0157</v>
       </c>
       <c r="H37" t="n">
-        <v>7.38</v>
+        <v>5.07</v>
       </c>
       <c r="I37" t="n">
-        <v>66.44</v>
+        <v>61.28</v>
       </c>
       <c r="J37" t="n">
-        <v>70.52</v>
+        <v>59.87</v>
       </c>
       <c r="K37" t="n">
-        <v>72.84999999999999</v>
+        <v>65.26000000000001</v>
       </c>
       <c r="L37" t="n">
-        <v>75.18000000000001</v>
+        <v>70.64</v>
       </c>
       <c r="M37" t="n">
-        <v>78.38</v>
+        <v>72.63</v>
       </c>
       <c r="N37" t="n">
-        <v>81.59</v>
+        <v>74.62</v>
       </c>
       <c r="O37" t="n">
-        <v>83.04000000000001</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
+      <c r="S37" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -3644,50 +3640,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-15</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>67.45</v>
+        <v>70.06999999999999</v>
       </c>
       <c r="C38" t="n">
-        <v>68.81999999999999</v>
+        <v>70.95</v>
       </c>
       <c r="D38" t="n">
-        <v>63.74</v>
+        <v>66.25</v>
       </c>
       <c r="E38" t="n">
-        <v>67.86</v>
+        <v>66.25</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.08</v>
+        <v>-1.6</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0236</v>
       </c>
       <c r="H38" t="n">
-        <v>5.07</v>
+        <v>4.69</v>
       </c>
       <c r="I38" t="n">
-        <v>61.28</v>
+        <v>58.67</v>
       </c>
       <c r="J38" t="n">
-        <v>59.87</v>
+        <v>63.58</v>
       </c>
       <c r="K38" t="n">
-        <v>65.26000000000001</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>70.64</v>
+        <v>67.06999999999999</v>
       </c>
       <c r="M38" t="n">
-        <v>72.63</v>
+        <v>70.39</v>
       </c>
       <c r="N38" t="n">
-        <v>74.62</v>
+        <v>73.72</v>
       </c>
       <c r="O38" t="n">
-        <v>83.40000000000001</v>
+        <v>73.89</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3695,18 +3691,18 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3719,74 +3715,82 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-06-15</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>70.06999999999999</v>
+        <v>65.53</v>
       </c>
       <c r="C39" t="n">
-        <v>70.95</v>
+        <v>65.53</v>
       </c>
       <c r="D39" t="n">
-        <v>66.25</v>
+        <v>57.25</v>
       </c>
       <c r="E39" t="n">
-        <v>66.25</v>
+        <v>59.22</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6</v>
+        <v>-7.04</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0236</v>
+        <v>-0.1062</v>
       </c>
       <c r="H39" t="n">
-        <v>4.69</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>58.67</v>
+        <v>61.56</v>
       </c>
       <c r="J39" t="n">
-        <v>63.58</v>
+        <v>60.39</v>
       </c>
       <c r="K39" t="n">
-        <v>65.31999999999999</v>
+        <v>63.91</v>
       </c>
       <c r="L39" t="n">
-        <v>67.06999999999999</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="M39" t="n">
-        <v>70.39</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="N39" t="n">
-        <v>73.72</v>
+        <v>69.78</v>
       </c>
       <c r="O39" t="n">
-        <v>73.89</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>75.64</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3799,83 +3803,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>65.53</v>
+        <v>58.68</v>
       </c>
       <c r="C40" t="n">
-        <v>65.53</v>
+        <v>62.88</v>
       </c>
       <c r="D40" t="n">
-        <v>57.25</v>
+        <v>57.03</v>
       </c>
       <c r="E40" t="n">
-        <v>59.22</v>
+        <v>62.4</v>
       </c>
       <c r="F40" t="n">
-        <v>-7.04</v>
+        <v>3.18</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.1062</v>
+        <v>0.0538</v>
       </c>
       <c r="H40" t="n">
-        <v>8.279999999999999</v>
+        <v>5.85</v>
       </c>
       <c r="I40" t="n">
-        <v>61.56</v>
+        <v>48.97</v>
       </c>
       <c r="J40" t="n">
-        <v>60.39</v>
+        <v>49.85</v>
       </c>
       <c r="K40" t="n">
-        <v>63.91</v>
+        <v>55.08</v>
       </c>
       <c r="L40" t="n">
-        <v>67.43000000000001</v>
+        <v>60.3</v>
       </c>
       <c r="M40" t="n">
-        <v>68.59999999999999</v>
+        <v>63.36</v>
       </c>
       <c r="N40" t="n">
-        <v>69.78</v>
+        <v>66.41</v>
       </c>
       <c r="O40" t="n">
-        <v>75.64</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
+        <v>73.8</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3887,74 +3883,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>58.68</v>
+        <v>62.62</v>
       </c>
       <c r="C41" t="n">
-        <v>62.88</v>
+        <v>62.62</v>
       </c>
       <c r="D41" t="n">
-        <v>57.03</v>
+        <v>57.76</v>
       </c>
       <c r="E41" t="n">
-        <v>62.4</v>
+        <v>59.81</v>
       </c>
       <c r="F41" t="n">
-        <v>3.18</v>
+        <v>-2.59</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0538</v>
+        <v>-0.0415</v>
       </c>
       <c r="H41" t="n">
-        <v>5.85</v>
+        <v>4.86</v>
       </c>
       <c r="I41" t="n">
-        <v>48.97</v>
+        <v>51.19</v>
       </c>
       <c r="J41" t="n">
-        <v>49.85</v>
+        <v>57.78</v>
       </c>
       <c r="K41" t="n">
-        <v>55.08</v>
+        <v>59.48</v>
       </c>
       <c r="L41" t="n">
-        <v>60.3</v>
+        <v>61.18</v>
       </c>
       <c r="M41" t="n">
-        <v>63.36</v>
+        <v>65.31999999999999</v>
       </c>
       <c r="N41" t="n">
-        <v>66.41</v>
+        <v>69.47</v>
       </c>
       <c r="O41" t="n">
-        <v>73.8</v>
+        <v>68.73</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3976,65 +3978,65 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>62.62</v>
+        <v>58.94</v>
       </c>
       <c r="C42" t="n">
-        <v>62.62</v>
+        <v>59.6</v>
       </c>
       <c r="D42" t="n">
-        <v>57.76</v>
+        <v>55.01</v>
       </c>
       <c r="E42" t="n">
-        <v>59.81</v>
+        <v>56.04</v>
       </c>
       <c r="F42" t="n">
-        <v>-2.59</v>
+        <v>-3.77</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0415</v>
+        <v>-0.0631</v>
       </c>
       <c r="H42" t="n">
-        <v>4.86</v>
+        <v>4.59</v>
       </c>
       <c r="I42" t="n">
-        <v>51.19</v>
+        <v>52.9</v>
       </c>
       <c r="J42" t="n">
-        <v>57.78</v>
+        <v>54.76</v>
       </c>
       <c r="K42" t="n">
-        <v>59.48</v>
+        <v>57.38</v>
       </c>
       <c r="L42" t="n">
-        <v>61.18</v>
+        <v>60</v>
       </c>
       <c r="M42" t="n">
-        <v>65.31999999999999</v>
+        <v>62.24</v>
       </c>
       <c r="N42" t="n">
-        <v>69.47</v>
+        <v>64.48</v>
       </c>
       <c r="O42" t="n">
-        <v>68.73</v>
+        <v>67.48</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
       <c r="Q42" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4053,83 +4055,79 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>58.94</v>
+        <v>55.65</v>
       </c>
       <c r="C43" t="n">
-        <v>59.6</v>
+        <v>60.02</v>
       </c>
       <c r="D43" t="n">
-        <v>55.01</v>
+        <v>55.65</v>
       </c>
       <c r="E43" t="n">
-        <v>56.04</v>
+        <v>58.66</v>
       </c>
       <c r="F43" t="n">
-        <v>-3.77</v>
+        <v>2.62</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0631</v>
+        <v>0.0467</v>
       </c>
       <c r="H43" t="n">
-        <v>4.59</v>
+        <v>4.36</v>
       </c>
       <c r="I43" t="n">
-        <v>52.9</v>
+        <v>50.42</v>
       </c>
       <c r="J43" t="n">
-        <v>54.76</v>
+        <v>50.81</v>
       </c>
       <c r="K43" t="n">
-        <v>57.38</v>
+        <v>53.74</v>
       </c>
       <c r="L43" t="n">
-        <v>60</v>
+        <v>56.67</v>
       </c>
       <c r="M43" t="n">
-        <v>62.24</v>
+        <v>58.33</v>
       </c>
       <c r="N43" t="n">
-        <v>64.48</v>
+        <v>59.99</v>
       </c>
       <c r="O43" t="n">
-        <v>67.48</v>
+        <v>64.19</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4139,55 +4137,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>55.65</v>
+        <v>58.47</v>
       </c>
       <c r="C44" t="n">
-        <v>60.02</v>
+        <v>59.25</v>
       </c>
       <c r="D44" t="n">
-        <v>55.65</v>
+        <v>57.22</v>
       </c>
       <c r="E44" t="n">
-        <v>58.66</v>
+        <v>57.59</v>
       </c>
       <c r="F44" t="n">
-        <v>2.62</v>
+        <v>-1.06</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0467</v>
+        <v>-0.0182</v>
       </c>
       <c r="H44" t="n">
-        <v>4.36</v>
+        <v>2.03</v>
       </c>
       <c r="I44" t="n">
-        <v>50.42</v>
+        <v>51.29</v>
       </c>
       <c r="J44" t="n">
-        <v>50.81</v>
+        <v>54.7</v>
       </c>
       <c r="K44" t="n">
-        <v>53.74</v>
+        <v>56.47</v>
       </c>
       <c r="L44" t="n">
-        <v>56.67</v>
+        <v>58.25</v>
       </c>
       <c r="M44" t="n">
-        <v>58.33</v>
+        <v>60.84</v>
       </c>
       <c r="N44" t="n">
-        <v>59.99</v>
+        <v>63.43</v>
       </c>
       <c r="O44" t="n">
-        <v>64.19</v>
+        <v>64.38</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4200,18 +4202,14 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4223,57 +4221,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>58.47</v>
+        <v>57.67</v>
       </c>
       <c r="C45" t="n">
-        <v>59.25</v>
+        <v>65.05</v>
       </c>
       <c r="D45" t="n">
-        <v>57.22</v>
+        <v>57.67</v>
       </c>
       <c r="E45" t="n">
-        <v>57.59</v>
+        <v>63.33</v>
       </c>
       <c r="F45" t="n">
-        <v>-1.06</v>
+        <v>5.74</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0182</v>
+        <v>0.0997</v>
       </c>
       <c r="H45" t="n">
-        <v>2.03</v>
+        <v>7.38</v>
       </c>
       <c r="I45" t="n">
-        <v>51.29</v>
+        <v>55.2</v>
       </c>
       <c r="J45" t="n">
-        <v>54.7</v>
+        <v>55.24</v>
       </c>
       <c r="K45" t="n">
-        <v>56.47</v>
+        <v>56.58</v>
       </c>
       <c r="L45" t="n">
-        <v>58.25</v>
+        <v>57.91</v>
       </c>
       <c r="M45" t="n">
-        <v>60.84</v>
+        <v>58.6</v>
       </c>
       <c r="N45" t="n">
-        <v>63.43</v>
+        <v>59.29</v>
       </c>
       <c r="O45" t="n">
-        <v>64.38</v>
+        <v>61.28</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4286,76 +4284,78 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="C46" t="n">
-        <v>65.05</v>
+        <v>66.65000000000001</v>
       </c>
       <c r="D46" t="n">
-        <v>57.67</v>
+        <v>63.9</v>
       </c>
       <c r="E46" t="n">
-        <v>63.33</v>
+        <v>64.98999999999999</v>
       </c>
       <c r="F46" t="n">
-        <v>5.74</v>
+        <v>1.66</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0997</v>
+        <v>0.0261</v>
       </c>
       <c r="H46" t="n">
-        <v>7.38</v>
+        <v>2.75</v>
       </c>
       <c r="I46" t="n">
-        <v>55.2</v>
+        <v>50.28</v>
       </c>
       <c r="J46" t="n">
-        <v>55.24</v>
+        <v>56.94</v>
       </c>
       <c r="K46" t="n">
-        <v>56.58</v>
+        <v>59.64</v>
       </c>
       <c r="L46" t="n">
-        <v>57.91</v>
+        <v>62.35</v>
       </c>
       <c r="M46" t="n">
-        <v>58.6</v>
+        <v>67.02</v>
       </c>
       <c r="N46" t="n">
-        <v>59.29</v>
+        <v>71.7</v>
       </c>
       <c r="O46" t="n">
-        <v>61.28</v>
+        <v>72.43000000000001</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4366,25 +4366,21 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
+      <c r="S46" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T46" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="9" t="inlineStr">
         <is>
@@ -4396,50 +4392,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>63.9</v>
+        <v>65.25</v>
       </c>
       <c r="C47" t="n">
-        <v>66.65000000000001</v>
+        <v>69.84999999999999</v>
       </c>
       <c r="D47" t="n">
-        <v>63.9</v>
+        <v>63.12</v>
       </c>
       <c r="E47" t="n">
-        <v>64.98999999999999</v>
+        <v>69.47</v>
       </c>
       <c r="F47" t="n">
-        <v>1.66</v>
+        <v>4.48</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0261</v>
+        <v>0.0689</v>
       </c>
       <c r="H47" t="n">
-        <v>2.75</v>
+        <v>6.73</v>
       </c>
       <c r="I47" t="n">
-        <v>50.28</v>
+        <v>61.16</v>
       </c>
       <c r="J47" t="n">
-        <v>56.94</v>
+        <v>62.1</v>
       </c>
       <c r="K47" t="n">
-        <v>59.64</v>
+        <v>63.62</v>
       </c>
       <c r="L47" t="n">
-        <v>62.35</v>
+        <v>65.13</v>
       </c>
       <c r="M47" t="n">
-        <v>67.02</v>
+        <v>66.36</v>
       </c>
       <c r="N47" t="n">
-        <v>71.7</v>
+        <v>67.59</v>
       </c>
       <c r="O47" t="n">
-        <v>72.43000000000001</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4447,79 +4443,89 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T47" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
-      </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>65.25</v>
+        <v>69.34999999999999</v>
       </c>
       <c r="C48" t="n">
-        <v>69.84999999999999</v>
+        <v>71.16</v>
       </c>
       <c r="D48" t="n">
-        <v>63.12</v>
+        <v>66.23</v>
       </c>
       <c r="E48" t="n">
-        <v>69.47</v>
+        <v>67</v>
       </c>
       <c r="F48" t="n">
-        <v>4.48</v>
+        <v>-2.47</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0689</v>
+        <v>-0.0356</v>
       </c>
       <c r="H48" t="n">
-        <v>6.73</v>
+        <v>4.93</v>
       </c>
       <c r="I48" t="n">
-        <v>61.16</v>
+        <v>56.39</v>
       </c>
       <c r="J48" t="n">
-        <v>62.1</v>
+        <v>64.23</v>
       </c>
       <c r="K48" t="n">
-        <v>63.62</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="L48" t="n">
-        <v>65.13</v>
+        <v>67.98</v>
       </c>
       <c r="M48" t="n">
-        <v>66.36</v>
+        <v>72.83</v>
       </c>
       <c r="N48" t="n">
-        <v>67.59</v>
+        <v>77.69</v>
       </c>
       <c r="O48" t="n">
-        <v>69.40000000000001</v>
+        <v>76.58</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4529,28 +4535,22 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="9" t="inlineStr">
         <is>
@@ -4566,50 +4566,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>69.34999999999999</v>
+        <v>66.01000000000001</v>
       </c>
       <c r="C49" t="n">
-        <v>71.16</v>
+        <v>67.3</v>
       </c>
       <c r="D49" t="n">
-        <v>66.23</v>
+        <v>63.36</v>
       </c>
       <c r="E49" t="n">
-        <v>67</v>
+        <v>66.05</v>
       </c>
       <c r="F49" t="n">
-        <v>-2.47</v>
+        <v>-0.95</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0356</v>
+        <v>-0.0142</v>
       </c>
       <c r="H49" t="n">
-        <v>4.93</v>
+        <v>3.94</v>
       </c>
       <c r="I49" t="n">
-        <v>56.39</v>
+        <v>61.3</v>
       </c>
       <c r="J49" t="n">
-        <v>64.23</v>
+        <v>61.22</v>
       </c>
       <c r="K49" t="n">
-        <v>66.09999999999999</v>
+        <v>64.53</v>
       </c>
       <c r="L49" t="n">
-        <v>67.98</v>
+        <v>67.84999999999999</v>
       </c>
       <c r="M49" t="n">
-        <v>72.83</v>
+        <v>69.45999999999999</v>
       </c>
       <c r="N49" t="n">
-        <v>77.69</v>
+        <v>71.08</v>
       </c>
       <c r="O49" t="n">
-        <v>76.58</v>
+        <v>76.09</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4622,7 +4622,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S49" s="10" t="inlineStr">
+      <c r="S49" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4643,57 +4643,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>66.01000000000001</v>
+        <v>65.97</v>
       </c>
       <c r="C50" t="n">
-        <v>67.3</v>
+        <v>68.11</v>
       </c>
       <c r="D50" t="n">
-        <v>63.36</v>
+        <v>63.1</v>
       </c>
       <c r="E50" t="n">
-        <v>66.05</v>
+        <v>64.55</v>
       </c>
       <c r="F50" t="n">
-        <v>-0.95</v>
+        <v>-1.49</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0142</v>
+        <v>-0.0226</v>
       </c>
       <c r="H50" t="n">
-        <v>3.94</v>
+        <v>5.01</v>
       </c>
       <c r="I50" t="n">
-        <v>61.3</v>
+        <v>59.42</v>
       </c>
       <c r="J50" t="n">
-        <v>61.22</v>
+        <v>62.47</v>
       </c>
       <c r="K50" t="n">
-        <v>64.53</v>
+        <v>64.08</v>
       </c>
       <c r="L50" t="n">
-        <v>67.84999999999999</v>
+        <v>65.69</v>
       </c>
       <c r="M50" t="n">
-        <v>69.45999999999999</v>
+        <v>68.02</v>
       </c>
       <c r="N50" t="n">
-        <v>71.08</v>
+        <v>70.34999999999999</v>
       </c>
       <c r="O50" t="n">
-        <v>76.09</v>
+        <v>71.23999999999999</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4706,13 +4706,15 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
+      <c r="S50" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4727,57 +4729,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-07</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>65.97</v>
+        <v>63.51</v>
       </c>
       <c r="C51" t="n">
-        <v>68.11</v>
+        <v>66.94</v>
       </c>
       <c r="D51" t="n">
-        <v>63.1</v>
+        <v>63.02</v>
       </c>
       <c r="E51" t="n">
-        <v>64.55</v>
+        <v>66.56</v>
       </c>
       <c r="F51" t="n">
-        <v>-1.49</v>
+        <v>2</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0226</v>
+        <v>0.031</v>
       </c>
       <c r="H51" t="n">
-        <v>5.01</v>
+        <v>3.92</v>
       </c>
       <c r="I51" t="n">
-        <v>59.42</v>
+        <v>58.09</v>
       </c>
       <c r="J51" t="n">
-        <v>62.47</v>
+        <v>59.02</v>
       </c>
       <c r="K51" t="n">
-        <v>64.08</v>
+        <v>62.05</v>
       </c>
       <c r="L51" t="n">
-        <v>65.69</v>
+        <v>65.08</v>
       </c>
       <c r="M51" t="n">
-        <v>68.02</v>
+        <v>67.06</v>
       </c>
       <c r="N51" t="n">
-        <v>70.34999999999999</v>
+        <v>69.03</v>
       </c>
       <c r="O51" t="n">
-        <v>71.23999999999999</v>
+        <v>73.11</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4785,19 +4787,17 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="inlineStr">
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="U51" s="8" t="n">
@@ -4820,69 +4820,71 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>63.51</v>
+        <v>66.44</v>
       </c>
       <c r="C52" t="n">
-        <v>66.94</v>
+        <v>66.67</v>
       </c>
       <c r="D52" t="n">
-        <v>63.02</v>
+        <v>63</v>
       </c>
       <c r="E52" t="n">
-        <v>66.56</v>
+        <v>64.25</v>
       </c>
       <c r="F52" t="n">
-        <v>2</v>
+        <v>-2.31</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.031</v>
+        <v>-0.0347</v>
       </c>
       <c r="H52" t="n">
-        <v>3.92</v>
+        <v>3.67</v>
       </c>
       <c r="I52" t="n">
-        <v>58.09</v>
+        <v>59.1</v>
       </c>
       <c r="J52" t="n">
-        <v>59.02</v>
+        <v>63.42</v>
       </c>
       <c r="K52" t="n">
-        <v>62.05</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>65.08</v>
+        <v>65.77</v>
       </c>
       <c r="M52" t="n">
-        <v>67.06</v>
+        <v>68.52</v>
       </c>
       <c r="N52" t="n">
-        <v>69.03</v>
+        <v>71.26000000000001</v>
       </c>
       <c r="O52" t="n">
-        <v>73.11</v>
+        <v>70.86</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4897,72 +4899,72 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>66.44</v>
+        <v>61.38</v>
       </c>
       <c r="C53" t="n">
-        <v>66.67</v>
+        <v>61.56</v>
       </c>
       <c r="D53" t="n">
-        <v>63</v>
+        <v>59.98</v>
       </c>
       <c r="E53" t="n">
-        <v>64.25</v>
+        <v>59.98</v>
       </c>
       <c r="F53" t="n">
-        <v>-2.31</v>
+        <v>-4.27</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0347</v>
+        <v>-0.0664</v>
       </c>
       <c r="H53" t="n">
-        <v>3.67</v>
+        <v>1.58</v>
       </c>
       <c r="I53" t="n">
-        <v>59.1</v>
+        <v>59.33</v>
       </c>
       <c r="J53" t="n">
-        <v>63.42</v>
+        <v>60.29</v>
       </c>
       <c r="K53" t="n">
-        <v>64.59999999999999</v>
+        <v>62.41</v>
       </c>
       <c r="L53" t="n">
-        <v>65.77</v>
+        <v>64.54000000000001</v>
       </c>
       <c r="M53" t="n">
-        <v>68.52</v>
+        <v>66.08</v>
       </c>
       <c r="N53" t="n">
-        <v>71.26000000000001</v>
+        <v>67.62</v>
       </c>
       <c r="O53" t="n">
-        <v>70.86</v>
+        <v>70.33</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
       <c r="Q53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4976,88 +4978,86 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-05</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>61.38</v>
+        <v>61.52</v>
       </c>
       <c r="C54" t="n">
-        <v>61.56</v>
+        <v>61.62</v>
       </c>
       <c r="D54" t="n">
-        <v>59.98</v>
+        <v>58.92</v>
       </c>
       <c r="E54" t="n">
-        <v>59.98</v>
+        <v>60.67</v>
       </c>
       <c r="F54" t="n">
-        <v>-4.27</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0664</v>
+        <v>0.0116</v>
       </c>
       <c r="H54" t="n">
-        <v>1.58</v>
+        <v>2.7</v>
       </c>
       <c r="I54" t="n">
-        <v>59.33</v>
+        <v>58.4</v>
       </c>
       <c r="J54" t="n">
-        <v>60.29</v>
+        <v>58</v>
       </c>
       <c r="K54" t="n">
-        <v>62.41</v>
+        <v>59.19</v>
       </c>
       <c r="L54" t="n">
-        <v>64.54000000000001</v>
+        <v>60.37</v>
       </c>
       <c r="M54" t="n">
-        <v>66.08</v>
+        <v>60.77</v>
       </c>
       <c r="N54" t="n">
-        <v>67.62</v>
+        <v>61.16</v>
       </c>
       <c r="O54" t="n">
-        <v>70.33</v>
+        <v>63.13</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5067,61 +5067,69 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-12</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>61.52</v>
+        <v>60.14</v>
       </c>
       <c r="C55" t="n">
-        <v>61.62</v>
+        <v>60.14</v>
       </c>
       <c r="D55" t="n">
-        <v>58.92</v>
+        <v>55.5</v>
       </c>
       <c r="E55" t="n">
-        <v>60.67</v>
+        <v>56.99</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6899999999999999</v>
+        <v>-3.67</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0116</v>
+        <v>-0.0606</v>
       </c>
       <c r="H55" t="n">
-        <v>2.7</v>
+        <v>4.64</v>
       </c>
       <c r="I55" t="n">
-        <v>58.4</v>
+        <v>56.22</v>
       </c>
       <c r="J55" t="n">
-        <v>58</v>
+        <v>58.17</v>
       </c>
       <c r="K55" t="n">
-        <v>59.19</v>
+        <v>59.32</v>
       </c>
       <c r="L55" t="n">
-        <v>60.37</v>
+        <v>60.47</v>
       </c>
       <c r="M55" t="n">
-        <v>60.77</v>
+        <v>62.02</v>
       </c>
       <c r="N55" t="n">
-        <v>61.16</v>
+        <v>63.57</v>
       </c>
       <c r="O55" t="n">
-        <v>63.13</v>
-      </c>
-      <c r="P55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+        <v>64.31999999999999</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5130,18 +5138,14 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5151,76 +5155,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-10-12</t>
+          <t>2026-10-19</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>60.14</v>
+        <v>57.01</v>
       </c>
       <c r="C56" t="n">
-        <v>60.14</v>
+        <v>57.71</v>
       </c>
       <c r="D56" t="n">
-        <v>55.5</v>
+        <v>53.71</v>
       </c>
       <c r="E56" t="n">
-        <v>56.99</v>
+        <v>53.71</v>
       </c>
       <c r="F56" t="n">
-        <v>-3.67</v>
+        <v>-3.28</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0606</v>
+        <v>-0.0576</v>
       </c>
       <c r="H56" t="n">
-        <v>4.64</v>
+        <v>4</v>
       </c>
       <c r="I56" t="n">
-        <v>56.22</v>
+        <v>50.86</v>
       </c>
       <c r="J56" t="n">
-        <v>58.17</v>
+        <v>51.94</v>
       </c>
       <c r="K56" t="n">
+        <v>54.67</v>
+      </c>
+      <c r="L56" t="n">
+        <v>57.41</v>
+      </c>
+      <c r="M56" t="n">
         <v>59.32</v>
       </c>
-      <c r="L56" t="n">
-        <v>60.47</v>
-      </c>
-      <c r="M56" t="n">
-        <v>62.02</v>
-      </c>
       <c r="N56" t="n">
-        <v>63.57</v>
+        <v>61.22</v>
       </c>
       <c r="O56" t="n">
-        <v>64.31999999999999</v>
-      </c>
-      <c r="P56" s="6" t="inlineStr">
+        <v>64.78</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5244,63 +5240,67 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-10-19</t>
+          <t>2026-10-26</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>57.01</v>
+        <v>54.11</v>
       </c>
       <c r="C57" t="n">
-        <v>57.71</v>
+        <v>54.29</v>
       </c>
       <c r="D57" t="n">
-        <v>53.71</v>
+        <v>48.88</v>
       </c>
       <c r="E57" t="n">
-        <v>53.71</v>
+        <v>49.13</v>
       </c>
       <c r="F57" t="n">
-        <v>-3.28</v>
+        <v>-4.58</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0576</v>
+        <v>-0.0852</v>
       </c>
       <c r="H57" t="n">
-        <v>4</v>
+        <v>5.41</v>
       </c>
       <c r="I57" t="n">
-        <v>50.86</v>
+        <v>49.72</v>
       </c>
       <c r="J57" t="n">
-        <v>51.94</v>
+        <v>48.72</v>
       </c>
       <c r="K57" t="n">
-        <v>54.67</v>
+        <v>51.71</v>
       </c>
       <c r="L57" t="n">
-        <v>57.41</v>
+        <v>54.71</v>
       </c>
       <c r="M57" t="n">
-        <v>59.32</v>
+        <v>55.71</v>
       </c>
       <c r="N57" t="n">
-        <v>61.22</v>
+        <v>56.71</v>
       </c>
       <c r="O57" t="n">
-        <v>64.78</v>
-      </c>
-      <c r="P57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+        <v>61.7</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5320,86 +5320,6 @@
         </is>
       </c>
       <c r="X57" t="inlineStr"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>54.11</v>
-      </c>
-      <c r="C58" t="n">
-        <v>54.29</v>
-      </c>
-      <c r="D58" t="n">
-        <v>51.15</v>
-      </c>
-      <c r="E58" t="n">
-        <v>51.69</v>
-      </c>
-      <c r="F58" t="n">
-        <v>-2.02</v>
-      </c>
-      <c r="G58" s="5" t="n">
-        <v>-0.0375</v>
-      </c>
-      <c r="H58" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="I58" t="n">
-        <v>49.72</v>
-      </c>
-      <c r="J58" t="n">
-        <v>48.72</v>
-      </c>
-      <c r="K58" t="n">
-        <v>51.71</v>
-      </c>
-      <c r="L58" t="n">
-        <v>54.71</v>
-      </c>
-      <c r="M58" t="n">
-        <v>55.71</v>
-      </c>
-      <c r="N58" t="n">
-        <v>56.71</v>
-      </c>
-      <c r="O58" t="n">
-        <v>61.7</v>
-      </c>
-      <c r="P58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
